--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -2095,7 +2095,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2209">
+  <cellXfs count="2216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -9546,6 +9546,30 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="4" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="171" fontId="44" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="47" fillId="0" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="20" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -10268,7 +10292,7 @@
       </c>
       <c r="I7" s="1075" t="n"/>
       <c r="J7" s="1076" t="n"/>
-      <c r="K7" s="1105" t="inlineStr">
+      <c r="K7" s="2209" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -14282,7 +14306,7 @@
       </c>
       <c r="L5" s="1075" t="n"/>
       <c r="M5" s="1076" t="n"/>
-      <c r="N5" s="1368" t="n"/>
+      <c r="N5" s="2210" t="n"/>
       <c r="O5" s="1107" t="n"/>
       <c r="P5" s="1369" t="inlineStr">
         <is>
@@ -17726,7 +17750,7 @@
         </is>
       </c>
       <c r="M50" s="1083" t="n"/>
-      <c r="N50" s="1623">
+      <c r="N50" s="2211">
         <f>S6</f>
         <v/>
       </c>
@@ -18166,7 +18190,7 @@
       <c r="J57" s="1631" t="n"/>
       <c r="K57" s="1638" t="n"/>
       <c r="L57" s="1638" t="n"/>
-      <c r="M57" s="1639">
+      <c r="M57" s="2212">
         <f>$S$6</f>
         <v/>
       </c>
@@ -18273,7 +18297,7 @@
       <c r="J58" s="1631" t="n"/>
       <c r="K58" s="1638" t="n"/>
       <c r="L58" s="1638" t="n"/>
-      <c r="M58" s="1639">
+      <c r="M58" s="2212">
         <f>$U$6</f>
         <v/>
       </c>
@@ -18377,7 +18401,7 @@
       <c r="J59" s="1631" t="n"/>
       <c r="K59" s="1638" t="n"/>
       <c r="L59" s="1638" t="n"/>
-      <c r="M59" s="1639">
+      <c r="M59" s="2212">
         <f>$W$6</f>
         <v/>
       </c>
@@ -18481,7 +18505,7 @@
       <c r="J60" s="1631" t="n"/>
       <c r="K60" s="1638" t="n"/>
       <c r="L60" s="1638" t="n"/>
-      <c r="M60" s="1639">
+      <c r="M60" s="2212">
         <f>$Y$6</f>
         <v/>
       </c>
@@ -18585,7 +18609,7 @@
       <c r="J61" s="1631" t="n"/>
       <c r="K61" s="1638" t="n"/>
       <c r="L61" s="1638" t="n"/>
-      <c r="M61" s="1639">
+      <c r="M61" s="2212">
         <f>$AA$6</f>
         <v/>
       </c>
@@ -18689,7 +18713,7 @@
       <c r="J62" s="1631" t="n"/>
       <c r="K62" s="1638" t="n"/>
       <c r="L62" s="1638" t="n"/>
-      <c r="M62" s="1639">
+      <c r="M62" s="2212">
         <f>$AC$6</f>
         <v/>
       </c>
@@ -18793,7 +18817,7 @@
       <c r="J63" s="1631" t="n"/>
       <c r="K63" s="1638" t="n"/>
       <c r="L63" s="1638" t="n"/>
-      <c r="M63" s="1639">
+      <c r="M63" s="2212">
         <f>$AE$6</f>
         <v/>
       </c>
@@ -18897,7 +18921,7 @@
       <c r="J64" s="1631" t="n"/>
       <c r="K64" s="1638" t="n"/>
       <c r="L64" s="1638" t="n"/>
-      <c r="M64" s="1639">
+      <c r="M64" s="2212">
         <f>$AG$6</f>
         <v/>
       </c>
@@ -19001,7 +19025,7 @@
       <c r="J65" s="1625" t="n"/>
       <c r="K65" s="1625" t="n"/>
       <c r="L65" s="1625" t="n"/>
-      <c r="M65" s="1639">
+      <c r="M65" s="2212">
         <f>$AG$6</f>
         <v/>
       </c>
@@ -20420,7 +20444,7 @@
         <v/>
       </c>
       <c r="E4" s="1679" t="n"/>
-      <c r="H4" s="1680">
+      <c r="H4" s="2213">
         <f>TODAY()</f>
         <v/>
       </c>
@@ -24117,7 +24141,7 @@
       </c>
       <c r="Q6" s="1075" t="n"/>
       <c r="R6" s="1076" t="n"/>
-      <c r="S6" s="1848" t="n"/>
+      <c r="S6" s="2214" t="n"/>
       <c r="T6" s="1849" t="inlineStr">
         <is>
           <t>- Cellar adds completed</t>
@@ -24173,7 +24197,7 @@
       </c>
       <c r="P7" s="1160" t="n"/>
       <c r="R7" s="1083" t="n"/>
-      <c r="S7" s="1848" t="n"/>
+      <c r="S7" s="2214" t="n"/>
       <c r="T7" s="1849" t="inlineStr">
         <is>
           <t>- CO2 spec bottle &amp; can both in SAME HBT =</t>
@@ -24228,7 +24252,7 @@
       </c>
       <c r="P8" s="1160" t="n"/>
       <c r="R8" s="1083" t="n"/>
-      <c r="S8" s="1848" t="n"/>
+      <c r="S8" s="2214" t="n"/>
       <c r="T8" s="1849" t="inlineStr">
         <is>
           <t xml:space="preserve"> middle between both specs </t>
@@ -24281,7 +24305,7 @@
       <c r="P9" s="1079" t="n"/>
       <c r="Q9" s="1080" t="n"/>
       <c r="R9" s="1081" t="n"/>
-      <c r="S9" s="1848" t="n"/>
+      <c r="S9" s="2214" t="n"/>
       <c r="T9" s="1849" t="n"/>
       <c r="U9" s="1849" t="n"/>
       <c r="V9" s="1602" t="n"/>
@@ -24442,7 +24466,7 @@
       </c>
       <c r="B14" s="1315" t="n"/>
       <c r="C14" s="1316" t="n"/>
-      <c r="D14" s="1105" t="n"/>
+      <c r="D14" s="2209" t="n"/>
       <c r="E14" s="1315" t="n"/>
       <c r="F14" s="1315" t="n"/>
       <c r="G14" s="1315" t="n"/>
@@ -24475,7 +24499,7 @@
       </c>
       <c r="B15" s="1876" t="n"/>
       <c r="C15" s="1876" t="n"/>
-      <c r="D15" s="1105" t="n"/>
+      <c r="D15" s="2209" t="n"/>
       <c r="E15" s="1315" t="n"/>
       <c r="F15" s="1315" t="n"/>
       <c r="G15" s="1315" t="n"/>
@@ -24512,7 +24536,7 @@
       </c>
       <c r="B16" s="1315" t="n"/>
       <c r="C16" s="1316" t="n"/>
-      <c r="D16" s="1105" t="n"/>
+      <c r="D16" s="2209" t="n"/>
       <c r="E16" s="1315" t="n"/>
       <c r="F16" s="1315" t="n"/>
       <c r="G16" s="1315" t="n"/>
@@ -33651,7 +33675,7 @@
           <t>datum:</t>
         </is>
       </c>
-      <c r="D99" s="2207" t="n"/>
+      <c r="D99" s="2215" t="n"/>
       <c r="E99" s="1115" t="n"/>
     </row>
     <row r="100" ht="15" customFormat="1" customHeight="1" s="1425">

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -12046,7 +12046,7 @@
       <c r="G58" s="1255" t="n"/>
       <c r="I58" s="1083" t="n"/>
       <c r="J58" s="1256">
-        <f>IF(G58="warm",SUMIF(G58:I60,"warm",E58:F60)/($C$9*100),SUMIF(G58:I60,"16C",E58:F60)/($C$9*100))</f>
+        <f>IF(G58="warm",SUMIF(G58:I60,"warm",E58:F60)/($C$9*100),SUMIF(G58:I60,"Cold*",E58:F60)/($C$9*100))</f>
         <v/>
       </c>
       <c r="K58" s="1082" t="inlineStr">
@@ -12129,7 +12129,7 @@
       <c r="G61" s="1255" t="n"/>
       <c r="I61" s="1083" t="n"/>
       <c r="J61" s="1256">
-        <f>IF(G61="warm",SUMIF(G61:I63,"warm",E61:F63)/($C$9*100),SUMIF(G61:I63,"16C",E61:F63)/($C$9*100))</f>
+        <f>IF(G61="warm",SUMIF(G61:I63,"warm",E61:F63)/($C$9*100),SUMIF(G61:I63,"Cold*",E61:F63)/($C$9*100))</f>
         <v/>
       </c>
       <c r="K61" s="1257" t="n"/>
@@ -13923,8 +13923,8 @@
     <cfRule type="containsText" rank="0" priority="14" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="2" text="0" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("0",G62)))</formula>
     </cfRule>
-    <cfRule type="containsText" rank="0" priority="15" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="16C" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("16C",G62)))</formula>
+    <cfRule type="containsText" rank="0" priority="15" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="Cold" percent="0" bottom="0">
+      <formula>NOT(ISERROR(SEARCH("Cold",G62)))</formula>
     </cfRule>
     <cfRule type="containsText" rank="0" priority="16" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="4" text="warm" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("warm",G62)))</formula>
@@ -13962,8 +13962,8 @@
     <cfRule type="containsText" rank="0" priority="25" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="2" text="0" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("0",G61)))</formula>
     </cfRule>
-    <cfRule type="containsText" rank="0" priority="26" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="16C" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("16C",G61)))</formula>
+    <cfRule type="containsText" rank="0" priority="26" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="Cold" percent="0" bottom="0">
+      <formula>NOT(ISERROR(SEARCH("Cold",G61)))</formula>
     </cfRule>
     <cfRule type="containsText" rank="0" priority="27" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="4" text="warm" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("warm",G61)))</formula>
@@ -13984,8 +13984,8 @@
     <cfRule type="containsText" rank="0" priority="31" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="2" text="0" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("0",G59)))</formula>
     </cfRule>
-    <cfRule type="containsText" rank="0" priority="32" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="16C" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("16C",G59)))</formula>
+    <cfRule type="containsText" rank="0" priority="32" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="Cold" percent="0" bottom="0">
+      <formula>NOT(ISERROR(SEARCH("Cold",G59)))</formula>
     </cfRule>
     <cfRule type="containsText" rank="0" priority="33" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="4" text="warm" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("warm",G59)))</formula>
@@ -13995,8 +13995,8 @@
     <cfRule type="containsText" rank="0" priority="34" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="2" text="0" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("0",G58)))</formula>
     </cfRule>
-    <cfRule type="containsText" rank="0" priority="35" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="koud" percent="0" bottom="0">
-      <formula>NOT(ISERROR(SEARCH("koud",G58)))</formula>
+    <cfRule type="containsText" rank="0" priority="35" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="3" text="Cold" percent="0" bottom="0">
+      <formula>NOT(ISERROR(SEARCH("Cold",G58)))</formula>
     </cfRule>
     <cfRule type="containsText" rank="0" priority="36" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="4" text="warm" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("warm",G58)))</formula>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -29689,7 +29689,7 @@
       </c>
       <c r="B59" s="2067" t="n"/>
       <c r="C59" s="2074">
-        <f>Afvulverslag!M49</f>
+        <f>Afvulverslag!M48</f>
         <v/>
       </c>
       <c r="D59" s="2068" t="n"/>
@@ -29737,12 +29737,12 @@
       </c>
       <c r="B60" s="2069" t="n"/>
       <c r="C60" s="2076">
-        <f>Afvulverslag!M77</f>
+        <f>Afvulverslag!M76</f>
         <v/>
       </c>
       <c r="D60" s="2070" t="n"/>
       <c r="E60" s="2077">
-        <f>IFERROR(Afvulverslag!M82/Afvulverslag!K82,"")</f>
+        <f>IFERROR(Afvulverslag!M81/Afvulverslag!K81,"")</f>
         <v/>
       </c>
       <c r="F60" s="2070" t="n"/>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="B61" s="2069" t="n"/>
       <c r="C61" s="2078">
-        <f>SUM(Afvulverslag!M86:M88)</f>
+        <f>SUM(Afvulverslag!M85:M87)</f>
         <v/>
       </c>
       <c r="D61" s="2070" t="n"/>
@@ -31093,7 +31093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.00390625" defaultRowHeight="15" zeroHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="2.5" customWidth="1" style="2094" min="1" max="1"/>
@@ -31457,7 +31457,7 @@
       <c r="K11" s="1521" t="n"/>
       <c r="L11" s="1521" t="n"/>
       <c r="M11" s="2135">
-        <f>SUM(M34:M42)</f>
+        <f>SUM(M34:M41)</f>
         <v/>
       </c>
       <c r="N11" s="1075" t="n"/>
@@ -31513,7 +31513,7 @@
       <c r="K13" s="1521" t="n"/>
       <c r="L13" s="1521" t="n"/>
       <c r="M13" s="2139">
-        <f>SUM(K45:K47)</f>
+        <f>SUM(K44:K46)</f>
         <v/>
       </c>
       <c r="N13" s="2140" t="n"/>
@@ -32084,7 +32084,7 @@
     <row r="35" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B35" s="2013" t="inlineStr">
         <is>
-          <t>20L Jopen/KU Fust</t>
+          <t>20L KU Fust</t>
         </is>
       </c>
       <c r="C35" s="2149" t="n"/>
@@ -32170,7 +32170,7 @@
     <row r="39" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B39" s="2013" t="inlineStr">
         <is>
-          <t>20L Gbr, Door Vrouwen fust</t>
+          <t>20L Gbr. Door Vrouwen fust</t>
         </is>
       </c>
       <c r="C39" s="1521" t="n"/>
@@ -32194,7 +32194,7 @@
     <row r="40" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B40" s="2013" t="inlineStr">
         <is>
-          <t>20L Global Keg (S)</t>
+          <t>20L Other kegs</t>
         </is>
       </c>
       <c r="C40" s="1521" t="n"/>
@@ -32215,19 +32215,19 @@
         <v/>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+    <row r="41" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B41" s="2013" t="inlineStr">
         <is>
-          <t>20L Global Keg</t>
+          <t>30L KeyKeg</t>
         </is>
       </c>
       <c r="C41" s="1521" t="n"/>
-      <c r="D41" s="2167" t="n"/>
-      <c r="E41" s="2151" t="n"/>
-      <c r="F41" s="2151" t="n"/>
-      <c r="G41" s="2151" t="n"/>
-      <c r="H41" s="2151" t="n"/>
-      <c r="I41" s="2150" t="n"/>
+      <c r="D41" s="2160" t="n"/>
+      <c r="E41" s="2160" t="n"/>
+      <c r="F41" s="2160" t="n"/>
+      <c r="G41" s="2160" t="n"/>
+      <c r="H41" s="2160" t="n"/>
+      <c r="I41" s="2161" t="n"/>
       <c r="J41" s="1521" t="n"/>
       <c r="K41" s="2152">
         <f>SUM(D41:I41)</f>
@@ -32235,102 +32235,102 @@
       </c>
       <c r="L41" s="2112" t="n"/>
       <c r="M41" s="2154">
-        <f>K41*20</f>
+        <f>K41*30</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B42" s="2013" t="inlineStr">
-        <is>
-          <t>30L KeyKeg</t>
-        </is>
-      </c>
-      <c r="C42" s="1521" t="n"/>
-      <c r="D42" s="2160" t="n"/>
-      <c r="E42" s="2160" t="n"/>
-      <c r="F42" s="2160" t="n"/>
-      <c r="G42" s="2160" t="n"/>
-      <c r="H42" s="2160" t="n"/>
-      <c r="I42" s="2161" t="n"/>
-      <c r="J42" s="1521" t="n"/>
-      <c r="K42" s="2152">
-        <f>SUM(D42:I42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="2112" t="n"/>
-      <c r="M42" s="2154">
-        <f>K42*30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B43" s="2168" t="n"/>
-      <c r="C43" s="1512" t="n"/>
-      <c r="D43" s="2169" t="n"/>
-      <c r="E43" s="2169" t="n"/>
-      <c r="F43" s="2169" t="n"/>
-      <c r="G43" s="2169" t="n"/>
-      <c r="H43" s="2169" t="n"/>
-      <c r="I43" s="2169" t="n"/>
-      <c r="J43" s="2170" t="n"/>
-      <c r="K43" s="2171" t="n"/>
-      <c r="L43" s="1521" t="n"/>
-      <c r="M43" s="1521" t="n"/>
-    </row>
-    <row r="44" outlineLevel="1" ht="55.5" customFormat="1" customHeight="1" s="1425">
-      <c r="B44" s="2172" t="inlineStr">
+      <c r="B42" s="2168" t="n"/>
+      <c r="C42" s="1512" t="n"/>
+      <c r="D42" s="2169" t="n"/>
+      <c r="E42" s="2169" t="n"/>
+      <c r="F42" s="2169" t="n"/>
+      <c r="G42" s="2169" t="n"/>
+      <c r="H42" s="2169" t="n"/>
+      <c r="I42" s="2169" t="n"/>
+      <c r="J42" s="2170" t="n"/>
+      <c r="K42" s="2171" t="n"/>
+      <c r="L42" s="1521" t="n"/>
+      <c r="M42" s="1521" t="n"/>
+    </row>
+    <row r="43" outlineLevel="1" ht="55.5" customFormat="1" customHeight="1" s="1425">
+      <c r="B43" s="2172" t="inlineStr">
         <is>
           <t>GEBRUIKT TBV SAMENVOEGEN / BARREL AGING</t>
         </is>
       </c>
-      <c r="C44" s="2147" t="inlineStr">
+      <c r="C43" s="2147" t="inlineStr">
         <is>
           <t>Opmerkingen</t>
         </is>
       </c>
-      <c r="D44" s="2010" t="inlineStr">
+      <c r="D43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
-      <c r="E44" s="2010" t="inlineStr">
+      <c r="E43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
-      <c r="F44" s="2010" t="inlineStr">
+      <c r="F43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
-      <c r="G44" s="2010" t="inlineStr">
+      <c r="G43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
-      <c r="H44" s="2010" t="inlineStr">
+      <c r="H43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
-      <c r="I44" s="2010" t="inlineStr">
+      <c r="I43" s="2010" t="inlineStr">
         <is>
           <t>Liters</t>
         </is>
       </c>
+      <c r="J43" s="1521" t="n"/>
+      <c r="K43" s="2010" t="inlineStr">
+        <is>
+          <t>TOTALEN Liters</t>
+        </is>
+      </c>
+      <c r="L43" s="1114" t="n"/>
+      <c r="M43" s="1115" t="n"/>
+    </row>
+    <row r="44" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B44" s="2013" t="inlineStr">
+        <is>
+          <t>TBV BATCH …,</t>
+        </is>
+      </c>
+      <c r="C44" s="2150" t="n"/>
+      <c r="D44" s="2150" t="n"/>
+      <c r="E44" s="2150" t="n"/>
+      <c r="F44" s="2150" t="n"/>
+      <c r="G44" s="2150" t="n"/>
+      <c r="H44" s="2150" t="n"/>
+      <c r="I44" s="2150" t="n"/>
       <c r="J44" s="1521" t="n"/>
-      <c r="K44" s="2010" t="inlineStr">
-        <is>
-          <t>TOTALEN Liters</t>
-        </is>
-      </c>
-      <c r="L44" s="1114" t="n"/>
-      <c r="M44" s="1115" t="n"/>
+      <c r="K44" s="2152">
+        <f>SUM(D44:I44)</f>
+        <v/>
+      </c>
+      <c r="L44" s="2112" t="n"/>
+      <c r="M44" s="2154">
+        <f>K44</f>
+        <v/>
+      </c>
     </row>
     <row r="45" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B45" s="2013" t="inlineStr">
         <is>
-          <t>TBV BATCH …,</t>
+          <t>TBV BARREL AGING BATCH…</t>
         </is>
       </c>
       <c r="C45" s="2150" t="n"/>
@@ -32352,172 +32352,176 @@
       </c>
     </row>
     <row r="46" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B46" s="2013" t="inlineStr">
-        <is>
-          <t>TBV BARREL AGING BATCH…</t>
-        </is>
-      </c>
-      <c r="C46" s="2150" t="n"/>
-      <c r="D46" s="2150" t="n"/>
-      <c r="E46" s="2150" t="n"/>
-      <c r="F46" s="2150" t="n"/>
-      <c r="G46" s="2150" t="n"/>
-      <c r="H46" s="2150" t="n"/>
-      <c r="I46" s="2150" t="n"/>
+      <c r="B46" s="2013" t="n"/>
+      <c r="C46" s="2160" t="n"/>
+      <c r="D46" s="2160" t="n"/>
+      <c r="E46" s="2161" t="n"/>
+      <c r="F46" s="2161" t="n"/>
+      <c r="G46" s="2161" t="n"/>
+      <c r="H46" s="2161" t="n"/>
+      <c r="I46" s="2161" t="n"/>
       <c r="J46" s="1521" t="n"/>
       <c r="K46" s="2152">
         <f>SUM(D46:I46)</f>
         <v/>
       </c>
       <c r="L46" s="2112" t="n"/>
-      <c r="M46" s="2154">
-        <f>K46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B47" s="2013" t="n"/>
-      <c r="C47" s="2160" t="n"/>
-      <c r="D47" s="2160" t="n"/>
-      <c r="E47" s="2161" t="n"/>
-      <c r="F47" s="2161" t="n"/>
-      <c r="G47" s="2161" t="n"/>
-      <c r="H47" s="2161" t="n"/>
-      <c r="I47" s="2161" t="n"/>
-      <c r="J47" s="1521" t="n"/>
-      <c r="K47" s="2152">
-        <f>SUM(D47:I47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="2112" t="n"/>
-      <c r="M47" s="2112" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="1339"/>
-    <row r="49" ht="23.25" customFormat="1" customHeight="1" s="1425">
-      <c r="B49" s="2173" t="inlineStr">
+      <c r="M46" s="2112" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="1339"/>
+    <row r="48" ht="23.25" customFormat="1" customHeight="1" s="1425">
+      <c r="B48" s="2173" t="inlineStr">
         <is>
           <t>VERBRUIKEN :</t>
         </is>
       </c>
-      <c r="C49" s="1114" t="n"/>
-      <c r="D49" s="1114" t="n"/>
-      <c r="E49" s="1114" t="n"/>
-      <c r="F49" s="1114" t="n"/>
-      <c r="G49" s="1114" t="n"/>
-      <c r="H49" s="1114" t="n"/>
-      <c r="I49" s="1115" t="n"/>
+      <c r="C48" s="1114" t="n"/>
+      <c r="D48" s="1114" t="n"/>
+      <c r="E48" s="1114" t="n"/>
+      <c r="F48" s="1114" t="n"/>
+      <c r="G48" s="1114" t="n"/>
+      <c r="H48" s="1114" t="n"/>
+      <c r="I48" s="1115" t="n"/>
+      <c r="J48" s="1521" t="n"/>
+      <c r="K48" s="2145" t="inlineStr">
+        <is>
+          <t>UITSCHRIJVEN (-)</t>
+        </is>
+      </c>
+      <c r="L48" s="1114" t="n"/>
+      <c r="M48" s="1115" t="n"/>
+      <c r="N48" s="1521" t="n"/>
+      <c r="O48" s="1521" t="n"/>
+      <c r="P48" s="1521" t="n"/>
+      <c r="Q48" s="1521" t="n"/>
+    </row>
+    <row r="49" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B49" s="2174" t="inlineStr">
+        <is>
+          <t>VERBRUIKEN FLES</t>
+        </is>
+      </c>
+      <c r="C49" s="2147" t="inlineStr">
+        <is>
+          <t>Opmerkingen</t>
+        </is>
+      </c>
+      <c r="D49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="E49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="F49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="G49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="H49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="I49" s="1137" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
       <c r="J49" s="1521" t="n"/>
-      <c r="K49" s="2145" t="inlineStr">
-        <is>
-          <t>UITSCHRIJVEN (-)</t>
-        </is>
-      </c>
-      <c r="L49" s="1114" t="n"/>
-      <c r="M49" s="1115" t="n"/>
+      <c r="K49" s="2175" t="inlineStr">
+        <is>
+          <t>TOTALEN</t>
+        </is>
+      </c>
+      <c r="L49" s="2036" t="n"/>
+      <c r="M49" s="2148" t="inlineStr">
+        <is>
+          <t>VERLIES</t>
+        </is>
+      </c>
       <c r="N49" s="1521" t="n"/>
       <c r="O49" s="1521" t="n"/>
       <c r="P49" s="1521" t="n"/>
       <c r="Q49" s="1521" t="n"/>
     </row>
-    <row r="50" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B50" s="2174" t="inlineStr">
-        <is>
-          <t>VERBRUIKEN FLES</t>
-        </is>
-      </c>
-      <c r="C50" s="2147" t="inlineStr">
-        <is>
-          <t>Opmerkingen</t>
-        </is>
-      </c>
-      <c r="D50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="E50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="F50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="G50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="H50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="I50" s="1137" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
+    <row r="50" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B50" s="2016" t="inlineStr">
+        <is>
+          <t>Fles 33cl</t>
+        </is>
+      </c>
+      <c r="C50" s="2176" t="n"/>
+      <c r="D50" s="2165" t="n"/>
+      <c r="E50" s="2166" t="n"/>
+      <c r="F50" s="2166" t="n"/>
+      <c r="G50" s="2166" t="n"/>
+      <c r="H50" s="2166" t="n"/>
+      <c r="I50" s="2166" t="n"/>
       <c r="J50" s="1521" t="n"/>
-      <c r="K50" s="2175" t="inlineStr">
-        <is>
-          <t>TOTALEN</t>
-        </is>
-      </c>
-      <c r="L50" s="2036" t="n"/>
-      <c r="M50" s="2148" t="inlineStr">
-        <is>
-          <t>VERLIES</t>
-        </is>
+      <c r="K50" s="2152">
+        <f>SUM(D50:I50)</f>
+        <v/>
+      </c>
+      <c r="L50" s="2112" t="n"/>
+      <c r="M50" s="2177">
+        <f>K50-SUM(K17:K18)*24-SUM(K20:K21)*12</f>
+        <v/>
       </c>
       <c r="N50" s="1521" t="n"/>
       <c r="O50" s="1521" t="n"/>
       <c r="P50" s="1521" t="n"/>
       <c r="Q50" s="1521" t="n"/>
     </row>
-    <row r="51" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B51" s="2016" t="inlineStr">
-        <is>
-          <t>Fles 33cl</t>
-        </is>
-      </c>
-      <c r="C51" s="2176" t="n"/>
-      <c r="D51" s="2165" t="n"/>
-      <c r="E51" s="2166" t="n"/>
-      <c r="F51" s="2166" t="n"/>
-      <c r="G51" s="2166" t="n"/>
-      <c r="H51" s="2166" t="n"/>
-      <c r="I51" s="2166" t="n"/>
+    <row r="51" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B51" s="2178" t="n"/>
+      <c r="C51" s="2163" t="n"/>
+      <c r="D51" s="2163" t="n"/>
+      <c r="E51" s="2163" t="n"/>
+      <c r="F51" s="2163" t="n"/>
+      <c r="G51" s="2163" t="n"/>
+      <c r="H51" s="2163" t="n"/>
+      <c r="I51" s="2163" t="n"/>
       <c r="J51" s="1521" t="n"/>
-      <c r="K51" s="2152">
-        <f>SUM(D51:I51)</f>
-        <v/>
-      </c>
+      <c r="K51" s="2152" t="n"/>
       <c r="L51" s="2112" t="n"/>
-      <c r="M51" s="2177">
-        <f>K51-SUM(K17:K18)*24-SUM(K20:K21)*12</f>
-        <v/>
-      </c>
+      <c r="M51" s="2177" t="n"/>
       <c r="N51" s="1521" t="n"/>
       <c r="O51" s="1521" t="n"/>
       <c r="P51" s="1521" t="n"/>
       <c r="Q51" s="1521" t="n"/>
     </row>
-    <row r="52" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B52" s="2178" t="n"/>
-      <c r="C52" s="2163" t="n"/>
-      <c r="D52" s="2163" t="n"/>
-      <c r="E52" s="2163" t="n"/>
-      <c r="F52" s="2163" t="n"/>
-      <c r="G52" s="2163" t="n"/>
-      <c r="H52" s="2163" t="n"/>
-      <c r="I52" s="2163" t="n"/>
+    <row r="52" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B52" s="2016" t="inlineStr">
+        <is>
+          <t>Stickerlabel 33cl - Main</t>
+        </is>
+      </c>
+      <c r="C52" s="2179" t="n"/>
+      <c r="D52" s="2165" t="n"/>
+      <c r="E52" s="2166" t="n"/>
+      <c r="F52" s="2166" t="n"/>
+      <c r="G52" s="2166" t="n"/>
+      <c r="H52" s="2166" t="n"/>
+      <c r="I52" s="2166" t="n"/>
       <c r="J52" s="1521" t="n"/>
-      <c r="K52" s="2152" t="n"/>
+      <c r="K52" s="2152">
+        <f>SUM(D52:I52)</f>
+        <v/>
+      </c>
       <c r="L52" s="2112" t="n"/>
-      <c r="M52" s="2177" t="n"/>
+      <c r="M52" s="2177">
+        <f>K52-$K$17*24-$K$20*12</f>
+        <v/>
+      </c>
       <c r="N52" s="1521" t="n"/>
       <c r="O52" s="1521" t="n"/>
       <c r="P52" s="1521" t="n"/>
@@ -32526,16 +32530,16 @@
     <row r="53" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B53" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 33cl - Main</t>
-        </is>
-      </c>
-      <c r="C53" s="2179" t="n"/>
-      <c r="D53" s="2165" t="n"/>
-      <c r="E53" s="2166" t="n"/>
-      <c r="F53" s="2166" t="n"/>
-      <c r="G53" s="2166" t="n"/>
-      <c r="H53" s="2166" t="n"/>
-      <c r="I53" s="2166" t="n"/>
+          <t>Stickerlabel 33cl - Neck</t>
+        </is>
+      </c>
+      <c r="C53" s="2161" t="n"/>
+      <c r="D53" s="2160" t="n"/>
+      <c r="E53" s="2161" t="n"/>
+      <c r="F53" s="2161" t="n"/>
+      <c r="G53" s="2161" t="n"/>
+      <c r="H53" s="2161" t="n"/>
+      <c r="I53" s="2161" t="n"/>
       <c r="J53" s="1521" t="n"/>
       <c r="K53" s="2152">
         <f>SUM(D53:I53)</f>
@@ -32551,47 +32555,47 @@
       <c r="P53" s="1521" t="n"/>
       <c r="Q53" s="1521" t="n"/>
     </row>
-    <row r="54" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B54" s="2016" t="inlineStr">
-        <is>
-          <t>Stickerlabel 33cl - Neck</t>
-        </is>
-      </c>
-      <c r="C54" s="2161" t="n"/>
-      <c r="D54" s="2160" t="n"/>
-      <c r="E54" s="2161" t="n"/>
-      <c r="F54" s="2161" t="n"/>
-      <c r="G54" s="2161" t="n"/>
-      <c r="H54" s="2161" t="n"/>
-      <c r="I54" s="2161" t="n"/>
+    <row r="54" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B54" s="1099" t="n"/>
+      <c r="C54" s="2170" t="n"/>
+      <c r="D54" s="1521" t="n"/>
+      <c r="E54" s="1521" t="n"/>
+      <c r="F54" s="1521" t="n"/>
+      <c r="G54" s="1521" t="n"/>
+      <c r="H54" s="1521" t="n"/>
+      <c r="I54" s="1521" t="n"/>
       <c r="J54" s="1521" t="n"/>
-      <c r="K54" s="2152">
-        <f>SUM(D54:I54)</f>
-        <v/>
-      </c>
+      <c r="K54" s="2152" t="n"/>
       <c r="L54" s="2112" t="n"/>
-      <c r="M54" s="2177">
-        <f>K54-$K$17*24-$K$20*12</f>
-        <v/>
-      </c>
+      <c r="M54" s="2177" t="n"/>
       <c r="N54" s="1521" t="n"/>
       <c r="O54" s="1521" t="n"/>
       <c r="P54" s="1521" t="n"/>
       <c r="Q54" s="1521" t="n"/>
     </row>
-    <row r="55" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B55" s="1099" t="n"/>
-      <c r="C55" s="2170" t="n"/>
-      <c r="D55" s="1521" t="n"/>
-      <c r="E55" s="1521" t="n"/>
-      <c r="F55" s="1521" t="n"/>
-      <c r="G55" s="1521" t="n"/>
-      <c r="H55" s="1521" t="n"/>
-      <c r="I55" s="1521" t="n"/>
+    <row r="55" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B55" s="2016" t="inlineStr">
+        <is>
+          <t>Omdozen 24x33cl - Bedrukt:</t>
+        </is>
+      </c>
+      <c r="C55" s="2179" t="n"/>
+      <c r="D55" s="2165" t="n"/>
+      <c r="E55" s="2166" t="n"/>
+      <c r="F55" s="2166" t="n"/>
+      <c r="G55" s="2166" t="n"/>
+      <c r="H55" s="2166" t="n"/>
+      <c r="I55" s="2166" t="n"/>
       <c r="J55" s="1521" t="n"/>
-      <c r="K55" s="2152" t="n"/>
+      <c r="K55" s="2152">
+        <f>SUM(D55:I55)</f>
+        <v/>
+      </c>
       <c r="L55" s="2112" t="n"/>
-      <c r="M55" s="2177" t="n"/>
+      <c r="M55" s="2152">
+        <f>K55-K17</f>
+        <v/>
+      </c>
       <c r="N55" s="1521" t="n"/>
       <c r="O55" s="1521" t="n"/>
       <c r="P55" s="1521" t="n"/>
@@ -32600,16 +32604,16 @@
     <row r="56" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B56" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 24x33cl - Bedrukt:</t>
-        </is>
-      </c>
-      <c r="C56" s="2179" t="n"/>
-      <c r="D56" s="2165" t="n"/>
-      <c r="E56" s="2166" t="n"/>
-      <c r="F56" s="2166" t="n"/>
-      <c r="G56" s="2166" t="n"/>
-      <c r="H56" s="2166" t="n"/>
-      <c r="I56" s="2166" t="n"/>
+          <t>Omdozen 24x33cl - Blanco</t>
+        </is>
+      </c>
+      <c r="C56" s="2180" t="n"/>
+      <c r="D56" s="2160" t="n"/>
+      <c r="E56" s="2161" t="n"/>
+      <c r="F56" s="2161" t="n"/>
+      <c r="G56" s="2161" t="n"/>
+      <c r="H56" s="2161" t="n"/>
+      <c r="I56" s="2161" t="n"/>
       <c r="J56" s="1521" t="n"/>
       <c r="K56" s="2152">
         <f>SUM(D56:I56)</f>
@@ -32617,7 +32621,7 @@
       </c>
       <c r="L56" s="2112" t="n"/>
       <c r="M56" s="2152">
-        <f>K56-K17</f>
+        <f>K56-K18</f>
         <v/>
       </c>
       <c r="N56" s="1521" t="n"/>
@@ -32626,46 +32630,46 @@
       <c r="Q56" s="1521" t="n"/>
     </row>
     <row r="57" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B57" s="2016" t="inlineStr">
-        <is>
-          <t>Omdozen 24x33cl - Blanco</t>
-        </is>
-      </c>
-      <c r="C57" s="2180" t="n"/>
-      <c r="D57" s="2160" t="n"/>
-      <c r="E57" s="2161" t="n"/>
-      <c r="F57" s="2161" t="n"/>
-      <c r="G57" s="2161" t="n"/>
-      <c r="H57" s="2161" t="n"/>
-      <c r="I57" s="2161" t="n"/>
+      <c r="B57" s="1099" t="n"/>
+      <c r="C57" s="1521" t="n"/>
+      <c r="D57" s="1521" t="n"/>
+      <c r="E57" s="1521" t="n"/>
+      <c r="F57" s="1521" t="n"/>
+      <c r="G57" s="1521" t="n"/>
+      <c r="H57" s="1521" t="n"/>
+      <c r="I57" s="1521" t="n"/>
       <c r="J57" s="1521" t="n"/>
-      <c r="K57" s="2152">
-        <f>SUM(D57:I57)</f>
-        <v/>
-      </c>
+      <c r="K57" s="2152" t="n"/>
       <c r="L57" s="2112" t="n"/>
-      <c r="M57" s="2152">
-        <f>K57-K18</f>
-        <v/>
-      </c>
+      <c r="M57" s="2177" t="n"/>
       <c r="N57" s="1521" t="n"/>
       <c r="O57" s="1521" t="n"/>
       <c r="P57" s="1521" t="n"/>
       <c r="Q57" s="1521" t="n"/>
     </row>
     <row r="58" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B58" s="1099" t="n"/>
-      <c r="C58" s="1521" t="n"/>
-      <c r="D58" s="1521" t="n"/>
-      <c r="E58" s="1521" t="n"/>
-      <c r="F58" s="1521" t="n"/>
-      <c r="G58" s="1521" t="n"/>
-      <c r="H58" s="1521" t="n"/>
-      <c r="I58" s="1521" t="n"/>
+      <c r="B58" s="2016" t="inlineStr">
+        <is>
+          <t>Omdozen 12x33cl - Bedrukt:</t>
+        </is>
+      </c>
+      <c r="C58" s="2179" t="n"/>
+      <c r="D58" s="2165" t="n"/>
+      <c r="E58" s="2166" t="n"/>
+      <c r="F58" s="2166" t="n"/>
+      <c r="G58" s="2166" t="n"/>
+      <c r="H58" s="2166" t="n"/>
+      <c r="I58" s="2166" t="n"/>
       <c r="J58" s="1521" t="n"/>
-      <c r="K58" s="2152" t="n"/>
+      <c r="K58" s="2152">
+        <f>SUM(D58:I58)</f>
+        <v/>
+      </c>
       <c r="L58" s="2112" t="n"/>
-      <c r="M58" s="2177" t="n"/>
+      <c r="M58" s="2152">
+        <f>K58-K20</f>
+        <v/>
+      </c>
       <c r="N58" s="1521" t="n"/>
       <c r="O58" s="1521" t="n"/>
       <c r="P58" s="1521" t="n"/>
@@ -32674,16 +32678,16 @@
     <row r="59" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B59" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 12x33cl - Bedrukt:</t>
-        </is>
-      </c>
-      <c r="C59" s="2179" t="n"/>
-      <c r="D59" s="2165" t="n"/>
-      <c r="E59" s="2166" t="n"/>
-      <c r="F59" s="2166" t="n"/>
-      <c r="G59" s="2166" t="n"/>
-      <c r="H59" s="2166" t="n"/>
-      <c r="I59" s="2166" t="n"/>
+          <t>Omdozen 12x33cl - Blanco</t>
+        </is>
+      </c>
+      <c r="C59" s="2180" t="n"/>
+      <c r="D59" s="2160" t="n"/>
+      <c r="E59" s="2161" t="n"/>
+      <c r="F59" s="2161" t="n"/>
+      <c r="G59" s="2161" t="n"/>
+      <c r="H59" s="2161" t="n"/>
+      <c r="I59" s="2161" t="n"/>
       <c r="J59" s="1521" t="n"/>
       <c r="K59" s="2152">
         <f>SUM(D59:I59)</f>
@@ -32691,7 +32695,7 @@
       </c>
       <c r="L59" s="2112" t="n"/>
       <c r="M59" s="2152">
-        <f>K59-K20</f>
+        <f>K59-K21</f>
         <v/>
       </c>
       <c r="N59" s="1521" t="n"/>
@@ -32700,122 +32704,122 @@
       <c r="Q59" s="1521" t="n"/>
     </row>
     <row r="60" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B60" s="2016" t="inlineStr">
-        <is>
-          <t>Omdozen 12x33cl - Blanco</t>
-        </is>
-      </c>
-      <c r="C60" s="2180" t="n"/>
-      <c r="D60" s="2160" t="n"/>
-      <c r="E60" s="2161" t="n"/>
-      <c r="F60" s="2161" t="n"/>
-      <c r="G60" s="2161" t="n"/>
-      <c r="H60" s="2161" t="n"/>
-      <c r="I60" s="2161" t="n"/>
+      <c r="B60" s="1099" t="n"/>
+      <c r="C60" s="2170" t="n"/>
+      <c r="D60" s="1521" t="n"/>
+      <c r="E60" s="1521" t="n"/>
+      <c r="F60" s="1521" t="n"/>
+      <c r="G60" s="1521" t="n"/>
+      <c r="H60" s="1521" t="n"/>
+      <c r="I60" s="1521" t="n"/>
       <c r="J60" s="1521" t="n"/>
-      <c r="K60" s="2152">
-        <f>SUM(D60:I60)</f>
-        <v/>
-      </c>
+      <c r="K60" s="2152" t="n"/>
       <c r="L60" s="2112" t="n"/>
-      <c r="M60" s="2152">
-        <f>K60-K21</f>
-        <v/>
-      </c>
+      <c r="M60" s="2177" t="n"/>
       <c r="N60" s="1521" t="n"/>
       <c r="O60" s="1521" t="n"/>
       <c r="P60" s="1521" t="n"/>
       <c r="Q60" s="1521" t="n"/>
     </row>
     <row r="61" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B61" s="1099" t="n"/>
-      <c r="C61" s="2170" t="n"/>
-      <c r="D61" s="1521" t="n"/>
-      <c r="E61" s="1521" t="n"/>
-      <c r="F61" s="1521" t="n"/>
-      <c r="G61" s="1521" t="n"/>
-      <c r="H61" s="1521" t="n"/>
-      <c r="I61" s="1521" t="n"/>
+      <c r="B61" s="2016" t="inlineStr">
+        <is>
+          <t>Kroonkurk:</t>
+        </is>
+      </c>
+      <c r="C61" s="2181" t="n"/>
+      <c r="D61" s="2137" t="n"/>
+      <c r="E61" s="2138" t="n"/>
+      <c r="F61" s="2138" t="n"/>
+      <c r="G61" s="2138" t="n"/>
+      <c r="H61" s="2138" t="n"/>
+      <c r="I61" s="2138" t="n"/>
       <c r="J61" s="1521" t="n"/>
-      <c r="K61" s="2152" t="n"/>
+      <c r="K61" s="2152">
+        <f>SUM(D61:I61)</f>
+        <v/>
+      </c>
       <c r="L61" s="2112" t="n"/>
-      <c r="M61" s="2177" t="n"/>
+      <c r="M61" s="2152">
+        <f>C61-SUM(K17:K18)*24-SUM(K20:K21)*12</f>
+        <v/>
+      </c>
       <c r="N61" s="1521" t="n"/>
-      <c r="O61" s="1521" t="n"/>
+      <c r="O61" s="1521" t="inlineStr">
+        <is>
+          <t>Doos á</t>
+        </is>
+      </c>
       <c r="P61" s="1521" t="n"/>
-      <c r="Q61" s="1521" t="n"/>
-    </row>
-    <row r="62" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B62" s="2016" t="inlineStr">
-        <is>
-          <t>Kroonkurk:</t>
-        </is>
-      </c>
-      <c r="C62" s="2181" t="n"/>
-      <c r="D62" s="2137" t="n"/>
-      <c r="E62" s="2138" t="n"/>
-      <c r="F62" s="2138" t="n"/>
-      <c r="G62" s="2138" t="n"/>
-      <c r="H62" s="2138" t="n"/>
-      <c r="I62" s="2138" t="n"/>
+      <c r="Q61" s="2137" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R61" s="2125">
+        <f>K61/Q61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B62" s="1099" t="n"/>
+      <c r="C62" s="1521" t="n"/>
+      <c r="D62" s="1521" t="n"/>
+      <c r="E62" s="1521" t="n"/>
+      <c r="F62" s="1521" t="n"/>
+      <c r="G62" s="1521" t="n"/>
+      <c r="H62" s="1521" t="n"/>
+      <c r="I62" s="1521" t="n"/>
       <c r="J62" s="1521" t="n"/>
-      <c r="K62" s="2152">
-        <f>SUM(D62:I62)</f>
-        <v/>
-      </c>
+      <c r="K62" s="2152" t="n"/>
       <c r="L62" s="2112" t="n"/>
-      <c r="M62" s="2152">
-        <f>C62-SUM(K17:K18)*24-SUM(K20:K21)*12</f>
-        <v/>
-      </c>
+      <c r="M62" s="2177" t="n"/>
       <c r="N62" s="1521" t="n"/>
-      <c r="O62" s="1521" t="inlineStr">
-        <is>
-          <t>Doos á</t>
-        </is>
-      </c>
-      <c r="P62" s="1521" t="n"/>
-      <c r="Q62" s="2137" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R62" s="2125">
-        <f>K62/Q62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B63" s="1099" t="n"/>
-      <c r="C63" s="1521" t="n"/>
-      <c r="D63" s="1521" t="n"/>
-      <c r="E63" s="1521" t="n"/>
-      <c r="F63" s="1521" t="n"/>
-      <c r="G63" s="1521" t="n"/>
-      <c r="H63" s="1521" t="n"/>
-      <c r="I63" s="1521" t="n"/>
+      <c r="O62" s="2182" t="inlineStr">
+        <is>
+          <t>Inhoud doos kan variëren!</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B63" s="2016" t="inlineStr">
+        <is>
+          <t>Fles 75cl</t>
+        </is>
+      </c>
+      <c r="C63" s="2179" t="n"/>
+      <c r="D63" s="2165" t="n"/>
+      <c r="E63" s="2166" t="n"/>
+      <c r="F63" s="2166" t="n"/>
+      <c r="G63" s="2166" t="n"/>
+      <c r="H63" s="2166" t="n"/>
+      <c r="I63" s="2166" t="n"/>
       <c r="J63" s="1521" t="n"/>
-      <c r="K63" s="2152" t="n"/>
+      <c r="K63" s="2152">
+        <f>SUM(D63:I63)</f>
+        <v/>
+      </c>
       <c r="L63" s="2112" t="n"/>
-      <c r="M63" s="2177" t="n"/>
+      <c r="M63" s="2177">
+        <f>K63-SUM(K23:K24)*6-K25*12</f>
+        <v/>
+      </c>
       <c r="N63" s="1521" t="n"/>
-      <c r="O63" s="2182" t="inlineStr">
-        <is>
-          <t>Inhoud doos kan variëren!</t>
-        </is>
-      </c>
+      <c r="O63" s="1521" t="n"/>
+      <c r="P63" s="1521" t="n"/>
+      <c r="Q63" s="1521" t="n"/>
     </row>
     <row r="64" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B64" s="2016" t="inlineStr">
         <is>
-          <t>Fles 75cl</t>
-        </is>
-      </c>
-      <c r="C64" s="2179" t="n"/>
-      <c r="D64" s="2165" t="n"/>
-      <c r="E64" s="2166" t="n"/>
-      <c r="F64" s="2166" t="n"/>
-      <c r="G64" s="2166" t="n"/>
-      <c r="H64" s="2166" t="n"/>
-      <c r="I64" s="2166" t="n"/>
+          <t>Stickerlabel 75cl - Main</t>
+        </is>
+      </c>
+      <c r="C64" s="2183" t="n"/>
+      <c r="D64" s="2151" t="n"/>
+      <c r="E64" s="2150" t="n"/>
+      <c r="F64" s="2150" t="n"/>
+      <c r="G64" s="2150" t="n"/>
+      <c r="H64" s="2150" t="n"/>
+      <c r="I64" s="2150" t="n"/>
       <c r="J64" s="1521" t="n"/>
       <c r="K64" s="2152">
         <f>SUM(D64:I64)</f>
@@ -32823,7 +32827,7 @@
       </c>
       <c r="L64" s="2112" t="n"/>
       <c r="M64" s="2177">
-        <f>K64-SUM(K23:K24)*6-K25*12</f>
+        <f>K64-K23*6</f>
         <v/>
       </c>
       <c r="N64" s="1521" t="n"/>
@@ -32834,16 +32838,16 @@
     <row r="65" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B65" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 75cl - Main</t>
+          <t>Stickerlabel 75cl - Neck</t>
         </is>
       </c>
       <c r="C65" s="2183" t="n"/>
-      <c r="D65" s="2151" t="n"/>
-      <c r="E65" s="2150" t="n"/>
-      <c r="F65" s="2150" t="n"/>
-      <c r="G65" s="2150" t="n"/>
-      <c r="H65" s="2150" t="n"/>
-      <c r="I65" s="2150" t="n"/>
+      <c r="D65" s="2167" t="n"/>
+      <c r="E65" s="2184" t="n"/>
+      <c r="F65" s="2184" t="n"/>
+      <c r="G65" s="2184" t="n"/>
+      <c r="H65" s="2184" t="n"/>
+      <c r="I65" s="2184" t="n"/>
       <c r="J65" s="1521" t="n"/>
       <c r="K65" s="2152">
         <f>SUM(D65:I65)</f>
@@ -32860,46 +32864,46 @@
       <c r="Q65" s="1521" t="n"/>
     </row>
     <row r="66" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B66" s="2016" t="inlineStr">
-        <is>
-          <t>Stickerlabel 75cl - Neck</t>
-        </is>
-      </c>
-      <c r="C66" s="2183" t="n"/>
-      <c r="D66" s="2167" t="n"/>
-      <c r="E66" s="2184" t="n"/>
-      <c r="F66" s="2184" t="n"/>
-      <c r="G66" s="2184" t="n"/>
-      <c r="H66" s="2184" t="n"/>
-      <c r="I66" s="2184" t="n"/>
+      <c r="B66" s="2185" t="n"/>
+      <c r="C66" s="2186" t="n"/>
+      <c r="D66" s="2187" t="n"/>
+      <c r="E66" s="2187" t="n"/>
+      <c r="F66" s="2187" t="n"/>
+      <c r="G66" s="2187" t="n"/>
+      <c r="H66" s="2187" t="n"/>
+      <c r="I66" s="2187" t="n"/>
       <c r="J66" s="1521" t="n"/>
-      <c r="K66" s="2152">
-        <f>SUM(D66:I66)</f>
-        <v/>
-      </c>
+      <c r="K66" s="2152" t="n"/>
       <c r="L66" s="2112" t="n"/>
-      <c r="M66" s="2177">
-        <f>K66-K23*6</f>
-        <v/>
-      </c>
+      <c r="M66" s="2177" t="n"/>
       <c r="N66" s="1521" t="n"/>
       <c r="O66" s="1521" t="n"/>
       <c r="P66" s="1521" t="n"/>
       <c r="Q66" s="1521" t="n"/>
     </row>
     <row r="67" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B67" s="2185" t="n"/>
-      <c r="C67" s="2186" t="n"/>
-      <c r="D67" s="2187" t="n"/>
-      <c r="E67" s="2187" t="n"/>
-      <c r="F67" s="2187" t="n"/>
-      <c r="G67" s="2187" t="n"/>
-      <c r="H67" s="2187" t="n"/>
-      <c r="I67" s="2187" t="n"/>
+      <c r="B67" s="2016" t="inlineStr">
+        <is>
+          <t>Omdozen 6x75cl - Bedrukt:</t>
+        </is>
+      </c>
+      <c r="C67" s="2179" t="n"/>
+      <c r="D67" s="2165" t="n"/>
+      <c r="E67" s="2166" t="n"/>
+      <c r="F67" s="2166" t="n"/>
+      <c r="G67" s="2166" t="n"/>
+      <c r="H67" s="2166" t="n"/>
+      <c r="I67" s="2166" t="n"/>
       <c r="J67" s="1521" t="n"/>
-      <c r="K67" s="2152" t="n"/>
+      <c r="K67" s="2152">
+        <f>SUM(D67:I67)</f>
+        <v/>
+      </c>
       <c r="L67" s="2112" t="n"/>
-      <c r="M67" s="2177" t="n"/>
+      <c r="M67" s="2152">
+        <f>K67-K23</f>
+        <v/>
+      </c>
       <c r="N67" s="1521" t="n"/>
       <c r="O67" s="1521" t="n"/>
       <c r="P67" s="1521" t="n"/>
@@ -32908,16 +32912,16 @@
     <row r="68" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B68" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 6x75cl - Bedrukt:</t>
-        </is>
-      </c>
-      <c r="C68" s="2179" t="n"/>
-      <c r="D68" s="2165" t="n"/>
-      <c r="E68" s="2166" t="n"/>
-      <c r="F68" s="2166" t="n"/>
-      <c r="G68" s="2166" t="n"/>
-      <c r="H68" s="2166" t="n"/>
-      <c r="I68" s="2166" t="n"/>
+          <t>Omdozen 6x75cl - Blanco</t>
+        </is>
+      </c>
+      <c r="C68" s="2188" t="n"/>
+      <c r="D68" s="2160" t="n"/>
+      <c r="E68" s="2161" t="n"/>
+      <c r="F68" s="2161" t="n"/>
+      <c r="G68" s="2161" t="n"/>
+      <c r="H68" s="2161" t="n"/>
+      <c r="I68" s="2161" t="n"/>
       <c r="J68" s="1521" t="n"/>
       <c r="K68" s="2152">
         <f>SUM(D68:I68)</f>
@@ -32925,7 +32929,7 @@
       </c>
       <c r="L68" s="2112" t="n"/>
       <c r="M68" s="2152">
-        <f>K68-K23</f>
+        <f>K68-K24</f>
         <v/>
       </c>
       <c r="N68" s="1521" t="n"/>
@@ -32934,72 +32938,82 @@
       <c r="Q68" s="1521" t="n"/>
     </row>
     <row r="69" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B69" s="2016" t="inlineStr">
-        <is>
-          <t>Omdozen 6x75cl - Blanco</t>
-        </is>
-      </c>
-      <c r="C69" s="2188" t="n"/>
-      <c r="D69" s="2160" t="n"/>
-      <c r="E69" s="2161" t="n"/>
-      <c r="F69" s="2161" t="n"/>
-      <c r="G69" s="2161" t="n"/>
-      <c r="H69" s="2161" t="n"/>
-      <c r="I69" s="2161" t="n"/>
+      <c r="B69" s="1099" t="n"/>
+      <c r="C69" s="2170" t="n"/>
+      <c r="D69" s="1521" t="n"/>
+      <c r="E69" s="1521" t="n"/>
+      <c r="F69" s="1521" t="n"/>
+      <c r="G69" s="1521" t="n"/>
+      <c r="H69" s="1521" t="n"/>
+      <c r="I69" s="1521" t="n"/>
       <c r="J69" s="1521" t="n"/>
-      <c r="K69" s="2152">
-        <f>SUM(D69:I69)</f>
-        <v/>
-      </c>
+      <c r="K69" s="2152" t="n"/>
       <c r="L69" s="2112" t="n"/>
-      <c r="M69" s="2152">
-        <f>K69-K24</f>
-        <v/>
-      </c>
+      <c r="M69" s="2152" t="n"/>
       <c r="N69" s="1521" t="n"/>
       <c r="O69" s="1521" t="n"/>
       <c r="P69" s="1521" t="n"/>
       <c r="Q69" s="1521" t="n"/>
     </row>
     <row r="70" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B70" s="1099" t="n"/>
-      <c r="C70" s="2170" t="n"/>
-      <c r="D70" s="1521" t="n"/>
-      <c r="E70" s="1521" t="n"/>
-      <c r="F70" s="1521" t="n"/>
-      <c r="G70" s="1521" t="n"/>
-      <c r="H70" s="1521" t="n"/>
-      <c r="I70" s="1521" t="n"/>
+      <c r="B70" s="2016" t="inlineStr">
+        <is>
+          <t>Kurk:</t>
+        </is>
+      </c>
+      <c r="C70" s="2179" t="n"/>
+      <c r="D70" s="2165" t="n"/>
+      <c r="E70" s="2166" t="n"/>
+      <c r="F70" s="2166" t="n"/>
+      <c r="G70" s="2166" t="n"/>
+      <c r="H70" s="2166" t="n"/>
+      <c r="I70" s="2166" t="n"/>
       <c r="J70" s="1521" t="n"/>
-      <c r="K70" s="2152" t="n"/>
+      <c r="K70" s="2152">
+        <f>SUM(D70:I70)</f>
+        <v/>
+      </c>
       <c r="L70" s="2112" t="n"/>
-      <c r="M70" s="2152" t="n"/>
+      <c r="M70" s="2152">
+        <f>K70-SUM(K23:K24)*6-K25*12</f>
+        <v/>
+      </c>
       <c r="N70" s="1521" t="n"/>
-      <c r="O70" s="1521" t="n"/>
+      <c r="O70" s="1521" t="inlineStr">
+        <is>
+          <t>Doos á</t>
+        </is>
+      </c>
       <c r="P70" s="1521" t="n"/>
-      <c r="Q70" s="1521" t="n"/>
+      <c r="Q70" s="2189" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R70" s="2125">
+        <f>K70/Q70</f>
+        <v/>
+      </c>
     </row>
     <row r="71" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B71" s="2016" t="inlineStr">
         <is>
-          <t>Kurk:</t>
-        </is>
-      </c>
-      <c r="C71" s="2179" t="n"/>
-      <c r="D71" s="2165" t="n"/>
-      <c r="E71" s="2166" t="n"/>
-      <c r="F71" s="2166" t="n"/>
-      <c r="G71" s="2166" t="n"/>
-      <c r="H71" s="2166" t="n"/>
-      <c r="I71" s="2166" t="n"/>
-      <c r="J71" s="1521" t="n"/>
+          <t>Musseletten:</t>
+        </is>
+      </c>
+      <c r="C71" s="2188" t="n"/>
+      <c r="D71" s="2160" t="n"/>
+      <c r="E71" s="2161" t="n"/>
+      <c r="F71" s="2161" t="n"/>
+      <c r="G71" s="2161" t="n"/>
+      <c r="H71" s="2161" t="n"/>
+      <c r="I71" s="2161" t="n"/>
+      <c r="J71" s="2170" t="n"/>
       <c r="K71" s="2152">
         <f>SUM(D71:I71)</f>
         <v/>
       </c>
       <c r="L71" s="2112" t="n"/>
       <c r="M71" s="2152">
-        <f>K71-SUM(K23:K24)*6-K25*12</f>
+        <f>K71-SUM(K23:K24)*6--K25*12</f>
         <v/>
       </c>
       <c r="N71" s="1521" t="n"/>
@@ -33010,122 +33024,113 @@
       </c>
       <c r="P71" s="1521" t="n"/>
       <c r="Q71" s="2189" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="R71" s="2125">
         <f>K71/Q71</f>
         <v/>
       </c>
     </row>
-    <row r="72" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B72" s="2016" t="inlineStr">
-        <is>
-          <t>Musseletten:</t>
-        </is>
-      </c>
-      <c r="C72" s="2188" t="n"/>
-      <c r="D72" s="2160" t="n"/>
-      <c r="E72" s="2161" t="n"/>
-      <c r="F72" s="2161" t="n"/>
-      <c r="G72" s="2161" t="n"/>
-      <c r="H72" s="2161" t="n"/>
-      <c r="I72" s="2161" t="n"/>
-      <c r="J72" s="2170" t="n"/>
-      <c r="K72" s="2152">
-        <f>SUM(D72:I72)</f>
-        <v/>
-      </c>
+    <row r="72" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B72" s="1099" t="n"/>
+      <c r="C72" s="2170" t="n"/>
+      <c r="D72" s="1521" t="n"/>
+      <c r="E72" s="1521" t="n"/>
+      <c r="F72" s="1521" t="n"/>
+      <c r="G72" s="1521" t="n"/>
+      <c r="H72" s="1521" t="n"/>
+      <c r="I72" s="1521" t="n"/>
+      <c r="J72" s="1521" t="n"/>
+      <c r="K72" s="2190" t="n"/>
       <c r="L72" s="2112" t="n"/>
-      <c r="M72" s="2152">
-        <f>K72-SUM(K23:K24)*6--K25*12</f>
-        <v/>
-      </c>
+      <c r="M72" s="2177" t="n"/>
       <c r="N72" s="1521" t="n"/>
-      <c r="O72" s="1521" t="inlineStr">
-        <is>
-          <t>Doos á</t>
-        </is>
-      </c>
-      <c r="P72" s="1521" t="n"/>
-      <c r="Q72" s="2189" t="n">
-        <v>2700</v>
-      </c>
-      <c r="R72" s="2125">
-        <f>K72/Q72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B73" s="1099" t="n"/>
-      <c r="C73" s="2170" t="n"/>
-      <c r="D73" s="1521" t="n"/>
-      <c r="E73" s="1521" t="n"/>
-      <c r="F73" s="1521" t="n"/>
-      <c r="G73" s="1521" t="n"/>
-      <c r="H73" s="1521" t="n"/>
-      <c r="I73" s="1521" t="n"/>
-      <c r="J73" s="1521" t="n"/>
-      <c r="K73" s="2190" t="n"/>
-      <c r="L73" s="2112" t="n"/>
-      <c r="M73" s="2177" t="n"/>
+      <c r="O72" s="2182">
+        <f>O62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B73" s="2172" t="inlineStr">
+        <is>
+          <t>VERBRUIKEN BLIK-artikelen</t>
+        </is>
+      </c>
+      <c r="C73" s="2147" t="inlineStr">
+        <is>
+          <t>Opmerkingen</t>
+        </is>
+      </c>
+      <c r="D73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="E73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="F73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="G73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="H73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="I73" s="2010" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="J73" s="2112" t="n"/>
+      <c r="K73" s="2010" t="inlineStr">
+        <is>
+          <t>TOTALEN</t>
+        </is>
+      </c>
+      <c r="L73" s="2191" t="n"/>
+      <c r="M73" s="2010" t="inlineStr">
+        <is>
+          <t>VERLIES</t>
+        </is>
+      </c>
       <c r="N73" s="1521" t="n"/>
-      <c r="O73" s="2182">
-        <f>O63</f>
-        <v/>
-      </c>
+      <c r="O73" s="2182" t="n"/>
+      <c r="P73" s="2182" t="n"/>
+      <c r="Q73" s="2182" t="n"/>
+      <c r="R73" s="2182" t="n"/>
     </row>
     <row r="74" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B74" s="2172" t="inlineStr">
-        <is>
-          <t>VERBRUIKEN BLIK-artikelen</t>
-        </is>
-      </c>
-      <c r="C74" s="2147" t="inlineStr">
-        <is>
-          <t>Opmerkingen</t>
-        </is>
-      </c>
-      <c r="D74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="E74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="F74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="G74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="H74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="I74" s="2010" t="inlineStr">
-        <is>
-          <t>Aantal</t>
-        </is>
-      </c>
-      <c r="J74" s="2112" t="n"/>
-      <c r="K74" s="2010" t="inlineStr">
-        <is>
-          <t>TOTALEN</t>
-        </is>
-      </c>
-      <c r="L74" s="2191" t="n"/>
-      <c r="M74" s="2010" t="inlineStr">
-        <is>
-          <t>VERLIES</t>
-        </is>
+      <c r="B74" s="2192" t="inlineStr">
+        <is>
+          <t>Blik 33cl</t>
+        </is>
+      </c>
+      <c r="C74" s="2176" t="n"/>
+      <c r="D74" s="2193" t="n"/>
+      <c r="E74" s="2194" t="n"/>
+      <c r="F74" s="2194" t="n"/>
+      <c r="G74" s="2194" t="n"/>
+      <c r="H74" s="2194" t="n"/>
+      <c r="I74" s="2194" t="n"/>
+      <c r="J74" s="1521" t="n"/>
+      <c r="K74" s="2152">
+        <f>SUM(D74:I74)</f>
+        <v/>
+      </c>
+      <c r="L74" s="2112" t="n"/>
+      <c r="M74" s="2177">
+        <f>K74-(K28*12)</f>
+        <v/>
       </c>
       <c r="N74" s="1521" t="n"/>
       <c r="O74" s="2182" t="n"/>
@@ -33136,24 +33141,21 @@
     <row r="75" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B75" s="2192" t="inlineStr">
         <is>
-          <t>Blik 33cl</t>
-        </is>
-      </c>
-      <c r="C75" s="2176" t="n"/>
-      <c r="D75" s="2193" t="n"/>
-      <c r="E75" s="2194" t="n"/>
-      <c r="F75" s="2194" t="n"/>
-      <c r="G75" s="2194" t="n"/>
-      <c r="H75" s="2194" t="n"/>
-      <c r="I75" s="2194" t="n"/>
+          <t>Blik 44cl</t>
+        </is>
+      </c>
+      <c r="C75" s="2195" t="n"/>
+      <c r="D75" s="2196" t="n"/>
+      <c r="E75" s="2197" t="n"/>
+      <c r="F75" s="2197" t="n"/>
+      <c r="G75" s="2197" t="n"/>
+      <c r="H75" s="2197" t="n"/>
+      <c r="I75" s="2197" t="n"/>
       <c r="J75" s="1521" t="n"/>
-      <c r="K75" s="2152">
-        <f>SUM(D75:I75)</f>
-        <v/>
-      </c>
+      <c r="K75" s="2152" t="n"/>
       <c r="L75" s="2112" t="n"/>
       <c r="M75" s="2177">
-        <f>K75-(K28*12)</f>
+        <f>K75-(K29*12)</f>
         <v/>
       </c>
       <c r="N75" s="1521" t="n"/>
@@ -33165,21 +33167,24 @@
     <row r="76" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B76" s="2192" t="inlineStr">
         <is>
-          <t>Blik 44cl</t>
-        </is>
-      </c>
-      <c r="C76" s="2195" t="n"/>
-      <c r="D76" s="2196" t="n"/>
-      <c r="E76" s="2197" t="n"/>
-      <c r="F76" s="2197" t="n"/>
-      <c r="G76" s="2197" t="n"/>
-      <c r="H76" s="2197" t="n"/>
-      <c r="I76" s="2197" t="n"/>
+          <t>Blik Deksel</t>
+        </is>
+      </c>
+      <c r="C76" s="1615" t="n"/>
+      <c r="D76" s="2167" t="n"/>
+      <c r="E76" s="2184" t="n"/>
+      <c r="F76" s="2184" t="n"/>
+      <c r="G76" s="2184" t="n"/>
+      <c r="H76" s="2184" t="n"/>
+      <c r="I76" s="2184" t="n"/>
       <c r="J76" s="1521" t="n"/>
-      <c r="K76" s="2152" t="n"/>
+      <c r="K76" s="2152">
+        <f>SUM(D76:I76)</f>
+        <v/>
+      </c>
       <c r="L76" s="2112" t="n"/>
       <c r="M76" s="2177">
-        <f>K76-(K29*12)</f>
+        <f>K76-(K28*12)</f>
         <v/>
       </c>
       <c r="N76" s="1521" t="n"/>
@@ -33191,7 +33196,7 @@
     <row r="77" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B77" s="2192" t="inlineStr">
         <is>
-          <t>Blik Deksel</t>
+          <t>Stickerlabel 33cl blik</t>
         </is>
       </c>
       <c r="C77" s="1615" t="n"/>
@@ -33220,7 +33225,7 @@
     <row r="78" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B78" s="2192" t="inlineStr">
         <is>
-          <t>Stickerlabel 33cl blik</t>
+          <t>Stickerlabel 44cl blik</t>
         </is>
       </c>
       <c r="C78" s="1615" t="n"/>
@@ -33231,13 +33236,10 @@
       <c r="H78" s="2184" t="n"/>
       <c r="I78" s="2184" t="n"/>
       <c r="J78" s="1521" t="n"/>
-      <c r="K78" s="2152">
-        <f>SUM(D78:I78)</f>
-        <v/>
-      </c>
+      <c r="K78" s="2152" t="n"/>
       <c r="L78" s="2112" t="n"/>
       <c r="M78" s="2177">
-        <f>K78-(K28*12)</f>
+        <f>K78-(K29*12)</f>
         <v/>
       </c>
       <c r="N78" s="1521" t="n"/>
@@ -33249,7 +33251,7 @@
     <row r="79" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B79" s="2192" t="inlineStr">
         <is>
-          <t>Stickerlabel 44cl blik</t>
+          <t>Omdozen 12x33cl blik - Blanco</t>
         </is>
       </c>
       <c r="C79" s="1615" t="n"/>
@@ -33260,10 +33262,13 @@
       <c r="H79" s="2184" t="n"/>
       <c r="I79" s="2184" t="n"/>
       <c r="J79" s="1521" t="n"/>
-      <c r="K79" s="2152" t="n"/>
+      <c r="K79" s="2152">
+        <f>SUM(D79:I79)</f>
+        <v/>
+      </c>
       <c r="L79" s="2112" t="n"/>
-      <c r="M79" s="2177">
-        <f>K79-(K29*12)</f>
+      <c r="M79" s="2152">
+        <f>K79-K28</f>
         <v/>
       </c>
       <c r="N79" s="1521" t="n"/>
@@ -33275,7 +33280,7 @@
     <row r="80" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B80" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 12x33cl blik - Blanco</t>
+          <t>Omdozen 24x33cl blik - Blanco</t>
         </is>
       </c>
       <c r="C80" s="1615" t="n"/>
@@ -33286,25 +33291,17 @@
       <c r="H80" s="2184" t="n"/>
       <c r="I80" s="2184" t="n"/>
       <c r="J80" s="1521" t="n"/>
-      <c r="K80" s="2152">
-        <f>SUM(D80:I80)</f>
-        <v/>
-      </c>
+      <c r="K80" s="2152" t="n"/>
       <c r="L80" s="2112" t="n"/>
       <c r="M80" s="2152">
-        <f>K80-K28</f>
-        <v/>
-      </c>
-      <c r="N80" s="1521" t="n"/>
-      <c r="O80" s="2182" t="n"/>
-      <c r="P80" s="2182" t="n"/>
-      <c r="Q80" s="2182" t="n"/>
-      <c r="R80" s="2182" t="n"/>
+        <f>K80-K29</f>
+        <v/>
+      </c>
     </row>
     <row r="81" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B81" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 24x33cl blik - Blanco</t>
+          <t>Omdozen 12x44cl blik - Blanco</t>
         </is>
       </c>
       <c r="C81" s="1615" t="n"/>
@@ -33318,14 +33315,14 @@
       <c r="K81" s="2152" t="n"/>
       <c r="L81" s="2112" t="n"/>
       <c r="M81" s="2152">
-        <f>K81-K29</f>
+        <f>K81-K30</f>
         <v/>
       </c>
     </row>
     <row r="82" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B82" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 12x44cl blik - Blanco</t>
+          <t>Omdozen 24x44cl blik - Blanco</t>
         </is>
       </c>
       <c r="C82" s="1615" t="n"/>
@@ -33339,112 +33336,115 @@
       <c r="K82" s="2152" t="n"/>
       <c r="L82" s="2112" t="n"/>
       <c r="M82" s="2152">
-        <f>K82-K30</f>
+        <f>K82-K31</f>
         <v/>
       </c>
     </row>
     <row r="83" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B83" s="2192" t="inlineStr">
-        <is>
-          <t>Omdozen 24x44cl blik - Blanco</t>
-        </is>
-      </c>
-      <c r="C83" s="1615" t="n"/>
-      <c r="D83" s="2167" t="n"/>
-      <c r="E83" s="2184" t="n"/>
-      <c r="F83" s="2184" t="n"/>
-      <c r="G83" s="2184" t="n"/>
-      <c r="H83" s="2184" t="n"/>
-      <c r="I83" s="2184" t="n"/>
+      <c r="B83" s="1099" t="n"/>
+      <c r="C83" s="2170" t="n"/>
+      <c r="D83" s="1521" t="n"/>
+      <c r="E83" s="1521" t="n"/>
+      <c r="F83" s="1521" t="n"/>
+      <c r="G83" s="1521" t="n"/>
+      <c r="H83" s="1521" t="n"/>
+      <c r="I83" s="1521" t="n"/>
       <c r="J83" s="1521" t="n"/>
-      <c r="K83" s="2152" t="n"/>
+      <c r="K83" s="2190" t="n"/>
       <c r="L83" s="2112" t="n"/>
-      <c r="M83" s="2152">
-        <f>K83-K31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B84" s="1099" t="n"/>
-      <c r="C84" s="2170" t="n"/>
-      <c r="D84" s="1521" t="n"/>
-      <c r="E84" s="1521" t="n"/>
-      <c r="F84" s="1521" t="n"/>
-      <c r="G84" s="1521" t="n"/>
-      <c r="H84" s="1521" t="n"/>
-      <c r="I84" s="1521" t="n"/>
-      <c r="J84" s="1521" t="n"/>
-      <c r="K84" s="2190" t="n"/>
-      <c r="L84" s="2112" t="n"/>
-      <c r="M84" s="2177" t="n"/>
-    </row>
-    <row r="85" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B85" s="2172" t="inlineStr">
+      <c r="M83" s="2177" t="n"/>
+    </row>
+    <row r="84" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B84" s="2172" t="inlineStr">
         <is>
           <t>VERBRUIKEN FUST-artikelen</t>
         </is>
       </c>
-      <c r="C85" s="2147" t="inlineStr">
+      <c r="C84" s="2147" t="inlineStr">
         <is>
           <t>Opmerkingen</t>
         </is>
       </c>
-      <c r="D85" s="2010" t="inlineStr">
+      <c r="D84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="E85" s="2010" t="inlineStr">
+      <c r="E84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="F85" s="2010" t="inlineStr">
+      <c r="F84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="G85" s="2010" t="inlineStr">
+      <c r="G84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="H85" s="2010" t="inlineStr">
+      <c r="H84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="I85" s="2010" t="inlineStr">
+      <c r="I84" s="2010" t="inlineStr">
         <is>
           <t>Aantal</t>
         </is>
       </c>
-      <c r="J85" s="2112" t="n"/>
-      <c r="K85" s="2010" t="inlineStr">
+      <c r="J84" s="2112" t="n"/>
+      <c r="K84" s="2010" t="inlineStr">
         <is>
           <t>TOTALEN</t>
         </is>
       </c>
-      <c r="L85" s="2191" t="n"/>
-      <c r="M85" s="2010" t="inlineStr">
+      <c r="L84" s="2191" t="n"/>
+      <c r="M84" s="2010" t="inlineStr">
         <is>
           <t>VERLIES</t>
         </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B85" s="2016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global Keg 20L: </t>
+        </is>
+      </c>
+      <c r="C85" s="2176" t="n"/>
+      <c r="D85" s="2193" t="n"/>
+      <c r="E85" s="2194" t="n"/>
+      <c r="F85" s="2194" t="n"/>
+      <c r="G85" s="2194" t="n"/>
+      <c r="H85" s="2194" t="n"/>
+      <c r="I85" s="2194" t="n"/>
+      <c r="J85" s="1521" t="n"/>
+      <c r="K85" s="2152">
+        <f>SUM(D85:I85)</f>
+        <v/>
+      </c>
+      <c r="L85" s="2112" t="n"/>
+      <c r="M85" s="2152">
+        <f>K85-K34</f>
+        <v/>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B86" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global Keg 20L: </t>
-        </is>
-      </c>
-      <c r="C86" s="2176" t="n"/>
-      <c r="D86" s="2193" t="n"/>
-      <c r="E86" s="2194" t="n"/>
-      <c r="F86" s="2194" t="n"/>
-      <c r="G86" s="2194" t="n"/>
-      <c r="H86" s="2194" t="n"/>
-      <c r="I86" s="2194" t="n"/>
+          <t xml:space="preserve">Jopen Fust 20L: </t>
+        </is>
+      </c>
+      <c r="C86" s="1615" t="n"/>
+      <c r="D86" s="2167" t="n"/>
+      <c r="E86" s="2184" t="n"/>
+      <c r="F86" s="2184" t="n"/>
+      <c r="G86" s="2184" t="n"/>
+      <c r="H86" s="2184" t="n"/>
+      <c r="I86" s="2184" t="n"/>
       <c r="J86" s="1521" t="n"/>
       <c r="K86" s="2152">
         <f>SUM(D86:I86)</f>
@@ -33452,14 +33452,14 @@
       </c>
       <c r="L86" s="2112" t="n"/>
       <c r="M86" s="2152">
-        <f>K86-K34</f>
+        <f>K86-K35</f>
         <v/>
       </c>
     </row>
     <row r="87" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B87" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 20L: </t>
+          <t xml:space="preserve">Jopen Fust 30L: </t>
         </is>
       </c>
       <c r="C87" s="1615" t="n"/>
@@ -33469,21 +33469,21 @@
       <c r="G87" s="2184" t="n"/>
       <c r="H87" s="2184" t="n"/>
       <c r="I87" s="2184" t="n"/>
-      <c r="J87" s="1521" t="n"/>
+      <c r="J87" s="2170" t="n"/>
       <c r="K87" s="2152">
         <f>SUM(D87:I87)</f>
         <v/>
       </c>
       <c r="L87" s="2112" t="n"/>
       <c r="M87" s="2152">
-        <f>K87-K35</f>
+        <f>K87-K36</f>
         <v/>
       </c>
     </row>
     <row r="88" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B88" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 30L: </t>
+          <t xml:space="preserve">Jopen Fust 50L: </t>
         </is>
       </c>
       <c r="C88" s="1615" t="n"/>
@@ -33493,106 +33493,106 @@
       <c r="G88" s="2184" t="n"/>
       <c r="H88" s="2184" t="n"/>
       <c r="I88" s="2184" t="n"/>
-      <c r="J88" s="2170" t="n"/>
+      <c r="J88" s="1521" t="n"/>
       <c r="K88" s="2152">
         <f>SUM(D88:I88)</f>
         <v/>
       </c>
       <c r="L88" s="2112" t="n"/>
       <c r="M88" s="2152">
-        <f>K88-K36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B89" s="2016" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jopen Fust 50L: </t>
-        </is>
-      </c>
-      <c r="C89" s="1615" t="n"/>
-      <c r="D89" s="2167" t="n"/>
-      <c r="E89" s="2184" t="n"/>
-      <c r="F89" s="2184" t="n"/>
-      <c r="G89" s="2184" t="n"/>
-      <c r="H89" s="2184" t="n"/>
-      <c r="I89" s="2184" t="n"/>
+        <f>K88-K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B89" s="2185" t="n"/>
+      <c r="C89" s="2198" t="n"/>
+      <c r="D89" s="2156" t="n"/>
+      <c r="E89" s="2156" t="n"/>
+      <c r="F89" s="2156" t="n"/>
+      <c r="G89" s="2156" t="n"/>
+      <c r="H89" s="2156" t="n"/>
+      <c r="I89" s="2156" t="n"/>
       <c r="J89" s="1521" t="n"/>
-      <c r="K89" s="2152">
-        <f>SUM(D89:I89)</f>
-        <v/>
-      </c>
+      <c r="K89" s="2152" t="n"/>
       <c r="L89" s="2112" t="n"/>
-      <c r="M89" s="2152">
-        <f>K89-K37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B90" s="2185" t="n"/>
-      <c r="C90" s="2198" t="n"/>
-      <c r="D90" s="2156" t="n"/>
-      <c r="E90" s="2156" t="n"/>
-      <c r="F90" s="2156" t="n"/>
-      <c r="G90" s="2156" t="n"/>
-      <c r="H90" s="2156" t="n"/>
-      <c r="I90" s="2156" t="n"/>
+      <c r="M89" s="2152" t="n"/>
+    </row>
+    <row r="90" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B90" s="2016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fustdop: </t>
+        </is>
+      </c>
+      <c r="C90" s="1615" t="n"/>
+      <c r="D90" s="2167" t="n"/>
+      <c r="E90" s="2184" t="n"/>
+      <c r="F90" s="2184" t="n"/>
+      <c r="G90" s="2184" t="n"/>
+      <c r="H90" s="2184" t="n"/>
+      <c r="I90" s="2184" t="n"/>
       <c r="J90" s="1521" t="n"/>
-      <c r="K90" s="2152" t="n"/>
+      <c r="K90" s="2152">
+        <f>SUM(D90:I90)</f>
+        <v/>
+      </c>
       <c r="L90" s="2112" t="n"/>
-      <c r="M90" s="2152" t="n"/>
-    </row>
-    <row r="91" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B91" s="2016" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fustdop: </t>
-        </is>
-      </c>
-      <c r="C91" s="1615" t="n"/>
-      <c r="D91" s="2167" t="n"/>
-      <c r="E91" s="2184" t="n"/>
-      <c r="F91" s="2184" t="n"/>
-      <c r="G91" s="2184" t="n"/>
-      <c r="H91" s="2184" t="n"/>
-      <c r="I91" s="2184" t="n"/>
-      <c r="J91" s="1521" t="n"/>
-      <c r="K91" s="2152">
-        <f>SUM(D91:I91)</f>
-        <v/>
-      </c>
+      <c r="M90" s="2152">
+        <f>K90-SUM(K34:K37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B91" s="1099" t="n"/>
+      <c r="C91" s="2170" t="n"/>
+      <c r="D91" s="1521" t="n"/>
+      <c r="E91" s="1521" t="n"/>
+      <c r="F91" s="1521" t="n"/>
+      <c r="G91" s="1521" t="n"/>
+      <c r="H91" s="1521" t="n"/>
+      <c r="I91" s="1521" t="n"/>
+      <c r="J91" s="2170" t="n"/>
+      <c r="K91" s="2152" t="n"/>
       <c r="L91" s="2112" t="n"/>
-      <c r="M91" s="2152">
-        <f>K91-SUM(K34:K37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B92" s="1099" t="n"/>
-      <c r="C92" s="2170" t="n"/>
-      <c r="D92" s="1521" t="n"/>
-      <c r="E92" s="1521" t="n"/>
-      <c r="F92" s="1521" t="n"/>
-      <c r="G92" s="1521" t="n"/>
-      <c r="H92" s="1521" t="n"/>
-      <c r="I92" s="1521" t="n"/>
-      <c r="J92" s="2170" t="n"/>
-      <c r="K92" s="2152" t="n"/>
+      <c r="M91" s="2152" t="n"/>
+    </row>
+    <row r="92" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B92" s="2199" t="inlineStr">
+        <is>
+          <t>KeyKegFustdop:</t>
+        </is>
+      </c>
+      <c r="C92" s="2179" t="n"/>
+      <c r="D92" s="2193" t="n"/>
+      <c r="E92" s="2194" t="n"/>
+      <c r="F92" s="2194" t="n"/>
+      <c r="G92" s="2194" t="n"/>
+      <c r="H92" s="2194" t="n"/>
+      <c r="I92" s="2194" t="n"/>
+      <c r="J92" s="1521" t="n"/>
+      <c r="K92" s="2152">
+        <f>SUM(D92:I92)</f>
+        <v/>
+      </c>
       <c r="L92" s="2112" t="n"/>
-      <c r="M92" s="2152" t="n"/>
+      <c r="M92" s="2152">
+        <f>K92-K34-K41</f>
+        <v/>
+      </c>
     </row>
     <row r="93" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B93" s="2199" t="inlineStr">
-        <is>
-          <t>KeyKegFustdop:</t>
-        </is>
-      </c>
-      <c r="C93" s="2179" t="n"/>
-      <c r="D93" s="2193" t="n"/>
-      <c r="E93" s="2194" t="n"/>
-      <c r="F93" s="2194" t="n"/>
-      <c r="G93" s="2194" t="n"/>
-      <c r="H93" s="2194" t="n"/>
-      <c r="I93" s="2194" t="n"/>
+      <c r="B93" s="2200" t="inlineStr">
+        <is>
+          <t>KeyKeg 20L - Leeg</t>
+        </is>
+      </c>
+      <c r="C93" s="2201" t="n"/>
+      <c r="D93" s="2202" t="n"/>
+      <c r="E93" s="2203" t="n"/>
+      <c r="F93" s="2203" t="n"/>
+      <c r="G93" s="2203" t="n"/>
+      <c r="H93" s="2203" t="n"/>
+      <c r="I93" s="2203" t="n"/>
       <c r="J93" s="1521" t="n"/>
       <c r="K93" s="2152">
         <f>SUM(D93:I93)</f>
@@ -33600,23 +33600,23 @@
       </c>
       <c r="L93" s="2112" t="n"/>
       <c r="M93" s="2152">
-        <f>K93-K34-K42</f>
+        <f>K93-K34</f>
         <v/>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B94" s="2200" t="inlineStr">
-        <is>
-          <t>KeyKeg 20L - Leeg</t>
-        </is>
-      </c>
-      <c r="C94" s="2201" t="n"/>
-      <c r="D94" s="2202" t="n"/>
-      <c r="E94" s="2203" t="n"/>
-      <c r="F94" s="2203" t="n"/>
-      <c r="G94" s="2203" t="n"/>
-      <c r="H94" s="2203" t="n"/>
-      <c r="I94" s="2203" t="n"/>
+      <c r="B94" s="2016" t="inlineStr">
+        <is>
+          <t>KeyKeg 30L - Leeg</t>
+        </is>
+      </c>
+      <c r="C94" s="2204" t="n"/>
+      <c r="D94" s="2160" t="n"/>
+      <c r="E94" s="2161" t="n"/>
+      <c r="F94" s="2161" t="n"/>
+      <c r="G94" s="2161" t="n"/>
+      <c r="H94" s="2161" t="n"/>
+      <c r="I94" s="2161" t="n"/>
       <c r="J94" s="1521" t="n"/>
       <c r="K94" s="2152">
         <f>SUM(D94:I94)</f>
@@ -33624,64 +33624,48 @@
       </c>
       <c r="L94" s="2112" t="n"/>
       <c r="M94" s="2152">
-        <f>K94-K34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B95" s="2016" t="inlineStr">
-        <is>
-          <t>KeyKeg 30L - Leeg</t>
-        </is>
-      </c>
-      <c r="C95" s="2204" t="n"/>
-      <c r="D95" s="2160" t="n"/>
-      <c r="E95" s="2161" t="n"/>
-      <c r="F95" s="2161" t="n"/>
-      <c r="G95" s="2161" t="n"/>
-      <c r="H95" s="2161" t="n"/>
-      <c r="I95" s="2161" t="n"/>
-      <c r="J95" s="1521" t="n"/>
-      <c r="K95" s="2152">
-        <f>SUM(D95:I95)</f>
-        <v/>
-      </c>
-      <c r="L95" s="2112" t="n"/>
-      <c r="M95" s="2152">
-        <f>K95-K42</f>
-        <v/>
-      </c>
-    </row>
+        <f>K94-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="1339"/>
     <row r="96" ht="15" customHeight="1" s="1339"/>
-    <row r="97" ht="15" customHeight="1" s="1339"/>
+    <row r="97" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B97" s="2013" t="inlineStr">
+        <is>
+          <t>Ingevoerd in Mdrank</t>
+        </is>
+      </c>
+      <c r="C97" s="2026" t="inlineStr">
+        <is>
+          <t>door:</t>
+        </is>
+      </c>
+      <c r="D97" s="2205" t="n"/>
+      <c r="E97" s="1115" t="n"/>
+    </row>
     <row r="98" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B98" s="2013" t="inlineStr">
-        <is>
-          <t>Ingevoerd in Mdrank</t>
-        </is>
-      </c>
+      <c r="B98" s="2206" t="n"/>
       <c r="C98" s="2026" t="inlineStr">
         <is>
-          <t>door:</t>
-        </is>
-      </c>
-      <c r="D98" s="2205" t="n"/>
+          <t>datum:</t>
+        </is>
+      </c>
+      <c r="D98" s="2215" t="n"/>
       <c r="E98" s="1115" t="n"/>
     </row>
     <row r="99" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B99" s="2206" t="n"/>
-      <c r="C99" s="2026" t="inlineStr">
-        <is>
-          <t>datum:</t>
-        </is>
-      </c>
-      <c r="D99" s="2215" t="n"/>
-      <c r="E99" s="1115" t="n"/>
+      <c r="B99" s="2208" t="inlineStr">
+        <is>
+          <t>V2,1 : 09-10-17 KYT</t>
+        </is>
+      </c>
+      <c r="C99" s="1521" t="n"/>
     </row>
     <row r="100" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B100" s="2208" t="inlineStr">
         <is>
-          <t>V2,1 : 09-10-17 KYT</t>
+          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
         </is>
       </c>
       <c r="C100" s="1521" t="n"/>
@@ -33689,7 +33673,7 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B101" s="2208" t="inlineStr">
         <is>
-          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
+          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
         </is>
       </c>
       <c r="C101" s="1521" t="n"/>
@@ -33697,54 +33681,46 @@
     <row r="102" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B102" s="2208" t="inlineStr">
         <is>
-          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
+          <t>v3 6/2/24 TW</t>
         </is>
       </c>
       <c r="C102" s="1521" t="n"/>
-    </row>
-    <row r="103" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B103" s="2208" t="inlineStr">
-        <is>
-          <t>v3 6/2/24 TW</t>
-        </is>
-      </c>
-      <c r="C103" s="1521" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="M11:O11"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="M3:M5"/>
-    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="K43:M43"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B1:I2"/>
-    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="D98:E98"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="C3:E4"/>
-    <mergeCell ref="O73:R73"/>
+    <mergeCell ref="O72:R72"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="H3:I4"/>
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="B6:C11"/>
     <mergeCell ref="Q3:R4"/>
-    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="K48:M48"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B48:I48"/>
     <mergeCell ref="K15:M15"/>
-    <mergeCell ref="O63:R63"/>
+    <mergeCell ref="O62:R62"/>
     <mergeCell ref="F3:G4"/>
-    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="D97:E97"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="M1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M45:M46">
+  <conditionalFormatting sqref="M44:M45">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="29" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M62">
+  <conditionalFormatting sqref="M61">
     <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33765,37 +33741,37 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K80:K83">
+  <conditionalFormatting sqref="K79:K82">
     <cfRule type="cellIs" rank="0" priority="8" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="33" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K78:K79">
+  <conditionalFormatting sqref="K77:K78">
     <cfRule type="cellIs" rank="0" priority="9" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="33" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K77">
+  <conditionalFormatting sqref="K76">
     <cfRule type="cellIs" rank="0" priority="10" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="33" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K75:K76">
+  <conditionalFormatting sqref="K74:K75">
     <cfRule type="cellIs" rank="0" priority="11" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="33" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M74">
+  <conditionalFormatting sqref="M73">
     <cfRule type="cellIs" rank="0" priority="12" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K74">
+  <conditionalFormatting sqref="K73">
     <cfRule type="cellIs" rank="0" priority="13" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M75:M83">
+  <conditionalFormatting sqref="M74:M82">
     <cfRule type="cellIs" rank="0" priority="14" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33806,7 +33782,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M87">
+  <conditionalFormatting sqref="M86">
     <cfRule type="cellIs" rank="0" priority="17" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33817,12 +33793,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K87">
+  <conditionalFormatting sqref="K86">
     <cfRule type="cellIs" rank="0" priority="20" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M88">
+  <conditionalFormatting sqref="M87">
     <cfRule type="cellIs" rank="0" priority="21" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33833,12 +33809,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88">
+  <conditionalFormatting sqref="K87">
     <cfRule type="cellIs" rank="0" priority="24" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M89:M90">
+  <conditionalFormatting sqref="M88:M89">
     <cfRule type="cellIs" rank="0" priority="25" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33849,7 +33825,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K89:K90">
+  <conditionalFormatting sqref="K88:K89">
     <cfRule type="cellIs" rank="0" priority="28" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33859,7 +33835,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M86">
+  <conditionalFormatting sqref="M85">
     <cfRule type="cellIs" rank="0" priority="30" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33870,22 +33846,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K86">
+  <conditionalFormatting sqref="K85">
     <cfRule type="cellIs" rank="0" priority="33" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M85">
+  <conditionalFormatting sqref="M84">
     <cfRule type="cellIs" rank="0" priority="34" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34 M36:M42">
+  <conditionalFormatting sqref="M34 M36:M41">
     <cfRule type="cellIs" rank="0" priority="35" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="29" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M51:M61 M63:M73 M84 M91:M96">
+  <conditionalFormatting sqref="M50:M60 M62:M72 M83 M90:M95">
     <cfRule type="cellIs" rank="0" priority="36" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33901,17 +33877,17 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K85">
+  <conditionalFormatting sqref="K84">
     <cfRule type="cellIs" rank="0" priority="40" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K51:K54 K56:K57 K59:K60 K64:K66 K68:K70">
+  <conditionalFormatting sqref="K50:K53 K55:K56 K58:K59 K63:K65 K67:K69">
     <cfRule type="cellIs" rank="0" priority="41" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="33" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K42 K45:K47 K91:K96 R62 R71:R72">
+  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K41 K44:K46 K90:K95 R61 R70:R71">
     <cfRule type="cellIs" rank="0" priority="42" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -29784,7 +29784,7 @@
       </c>
       <c r="B61" s="2069" t="n"/>
       <c r="C61" s="2078">
-        <f>SUM(Afvulverslag!M85:M87)</f>
+        <f>SUM(Afvulverslag!M85:M86)</f>
         <v/>
       </c>
       <c r="D61" s="2070" t="n"/>
@@ -31093,7 +31093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.00390625" defaultRowHeight="15" zeroHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="2.5" customWidth="1" style="2094" min="1" max="1"/>
@@ -33411,16 +33411,16 @@
     <row r="85" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B85" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global Keg 20L: </t>
-        </is>
-      </c>
-      <c r="C85" s="2176" t="n"/>
-      <c r="D85" s="2193" t="n"/>
-      <c r="E85" s="2194" t="n"/>
-      <c r="F85" s="2194" t="n"/>
-      <c r="G85" s="2194" t="n"/>
-      <c r="H85" s="2194" t="n"/>
-      <c r="I85" s="2194" t="n"/>
+          <t xml:space="preserve">Jopen Fust 20L: </t>
+        </is>
+      </c>
+      <c r="C85" s="1615" t="n"/>
+      <c r="D85" s="2167" t="n"/>
+      <c r="E85" s="2184" t="n"/>
+      <c r="F85" s="2184" t="n"/>
+      <c r="G85" s="2184" t="n"/>
+      <c r="H85" s="2184" t="n"/>
+      <c r="I85" s="2184" t="n"/>
       <c r="J85" s="1521" t="n"/>
       <c r="K85" s="2152">
         <f>SUM(D85:I85)</f>
@@ -33428,14 +33428,14 @@
       </c>
       <c r="L85" s="2112" t="n"/>
       <c r="M85" s="2152">
-        <f>K85-K34</f>
+        <f>K85-K35</f>
         <v/>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B86" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 20L: </t>
+          <t xml:space="preserve">Jopen Fust 30L: </t>
         </is>
       </c>
       <c r="C86" s="1615" t="n"/>
@@ -33445,21 +33445,21 @@
       <c r="G86" s="2184" t="n"/>
       <c r="H86" s="2184" t="n"/>
       <c r="I86" s="2184" t="n"/>
-      <c r="J86" s="1521" t="n"/>
+      <c r="J86" s="2170" t="n"/>
       <c r="K86" s="2152">
         <f>SUM(D86:I86)</f>
         <v/>
       </c>
       <c r="L86" s="2112" t="n"/>
       <c r="M86" s="2152">
-        <f>K86-K35</f>
+        <f>K86-K36</f>
         <v/>
       </c>
     </row>
     <row r="87" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B87" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 30L: </t>
+          <t xml:space="preserve">Jopen Fust 50L: </t>
         </is>
       </c>
       <c r="C87" s="1615" t="n"/>
@@ -33469,106 +33469,106 @@
       <c r="G87" s="2184" t="n"/>
       <c r="H87" s="2184" t="n"/>
       <c r="I87" s="2184" t="n"/>
-      <c r="J87" s="2170" t="n"/>
+      <c r="J87" s="1521" t="n"/>
       <c r="K87" s="2152">
         <f>SUM(D87:I87)</f>
         <v/>
       </c>
       <c r="L87" s="2112" t="n"/>
       <c r="M87" s="2152">
-        <f>K87-K36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B88" s="2016" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jopen Fust 50L: </t>
-        </is>
-      </c>
-      <c r="C88" s="1615" t="n"/>
-      <c r="D88" s="2167" t="n"/>
-      <c r="E88" s="2184" t="n"/>
-      <c r="F88" s="2184" t="n"/>
-      <c r="G88" s="2184" t="n"/>
-      <c r="H88" s="2184" t="n"/>
-      <c r="I88" s="2184" t="n"/>
+        <f>K87-K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B88" s="2185" t="n"/>
+      <c r="C88" s="2198" t="n"/>
+      <c r="D88" s="2156" t="n"/>
+      <c r="E88" s="2156" t="n"/>
+      <c r="F88" s="2156" t="n"/>
+      <c r="G88" s="2156" t="n"/>
+      <c r="H88" s="2156" t="n"/>
+      <c r="I88" s="2156" t="n"/>
       <c r="J88" s="1521" t="n"/>
-      <c r="K88" s="2152">
-        <f>SUM(D88:I88)</f>
-        <v/>
-      </c>
+      <c r="K88" s="2152" t="n"/>
       <c r="L88" s="2112" t="n"/>
-      <c r="M88" s="2152">
-        <f>K88-K37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B89" s="2185" t="n"/>
-      <c r="C89" s="2198" t="n"/>
-      <c r="D89" s="2156" t="n"/>
-      <c r="E89" s="2156" t="n"/>
-      <c r="F89" s="2156" t="n"/>
-      <c r="G89" s="2156" t="n"/>
-      <c r="H89" s="2156" t="n"/>
-      <c r="I89" s="2156" t="n"/>
+      <c r="M88" s="2152" t="n"/>
+    </row>
+    <row r="89" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B89" s="2016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fustdop: </t>
+        </is>
+      </c>
+      <c r="C89" s="1615" t="n"/>
+      <c r="D89" s="2167" t="n"/>
+      <c r="E89" s="2184" t="n"/>
+      <c r="F89" s="2184" t="n"/>
+      <c r="G89" s="2184" t="n"/>
+      <c r="H89" s="2184" t="n"/>
+      <c r="I89" s="2184" t="n"/>
       <c r="J89" s="1521" t="n"/>
-      <c r="K89" s="2152" t="n"/>
+      <c r="K89" s="2152">
+        <f>SUM(D89:I89)</f>
+        <v/>
+      </c>
       <c r="L89" s="2112" t="n"/>
-      <c r="M89" s="2152" t="n"/>
-    </row>
-    <row r="90" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B90" s="2016" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fustdop: </t>
-        </is>
-      </c>
-      <c r="C90" s="1615" t="n"/>
-      <c r="D90" s="2167" t="n"/>
-      <c r="E90" s="2184" t="n"/>
-      <c r="F90" s="2184" t="n"/>
-      <c r="G90" s="2184" t="n"/>
-      <c r="H90" s="2184" t="n"/>
-      <c r="I90" s="2184" t="n"/>
-      <c r="J90" s="1521" t="n"/>
-      <c r="K90" s="2152">
-        <f>SUM(D90:I90)</f>
-        <v/>
-      </c>
+      <c r="M89" s="2152">
+        <f>K89-SUM(K34:K37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B90" s="1099" t="n"/>
+      <c r="C90" s="2170" t="n"/>
+      <c r="D90" s="1521" t="n"/>
+      <c r="E90" s="1521" t="n"/>
+      <c r="F90" s="1521" t="n"/>
+      <c r="G90" s="1521" t="n"/>
+      <c r="H90" s="1521" t="n"/>
+      <c r="I90" s="1521" t="n"/>
+      <c r="J90" s="2170" t="n"/>
+      <c r="K90" s="2152" t="n"/>
       <c r="L90" s="2112" t="n"/>
-      <c r="M90" s="2152">
-        <f>K90-SUM(K34:K37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B91" s="1099" t="n"/>
-      <c r="C91" s="2170" t="n"/>
-      <c r="D91" s="1521" t="n"/>
-      <c r="E91" s="1521" t="n"/>
-      <c r="F91" s="1521" t="n"/>
-      <c r="G91" s="1521" t="n"/>
-      <c r="H91" s="1521" t="n"/>
-      <c r="I91" s="1521" t="n"/>
-      <c r="J91" s="2170" t="n"/>
-      <c r="K91" s="2152" t="n"/>
+      <c r="M90" s="2152" t="n"/>
+    </row>
+    <row r="91" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B91" s="2199" t="inlineStr">
+        <is>
+          <t>KeyKegFustdop:</t>
+        </is>
+      </c>
+      <c r="C91" s="2179" t="n"/>
+      <c r="D91" s="2193" t="n"/>
+      <c r="E91" s="2194" t="n"/>
+      <c r="F91" s="2194" t="n"/>
+      <c r="G91" s="2194" t="n"/>
+      <c r="H91" s="2194" t="n"/>
+      <c r="I91" s="2194" t="n"/>
+      <c r="J91" s="1521" t="n"/>
+      <c r="K91" s="2152">
+        <f>SUM(D91:I91)</f>
+        <v/>
+      </c>
       <c r="L91" s="2112" t="n"/>
-      <c r="M91" s="2152" t="n"/>
+      <c r="M91" s="2152">
+        <f>K91-K34-K41</f>
+        <v/>
+      </c>
     </row>
     <row r="92" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B92" s="2199" t="inlineStr">
-        <is>
-          <t>KeyKegFustdop:</t>
-        </is>
-      </c>
-      <c r="C92" s="2179" t="n"/>
-      <c r="D92" s="2193" t="n"/>
-      <c r="E92" s="2194" t="n"/>
-      <c r="F92" s="2194" t="n"/>
-      <c r="G92" s="2194" t="n"/>
-      <c r="H92" s="2194" t="n"/>
-      <c r="I92" s="2194" t="n"/>
+      <c r="B92" s="2200" t="inlineStr">
+        <is>
+          <t>KeyKeg 20L - Leeg</t>
+        </is>
+      </c>
+      <c r="C92" s="2201" t="n"/>
+      <c r="D92" s="2202" t="n"/>
+      <c r="E92" s="2203" t="n"/>
+      <c r="F92" s="2203" t="n"/>
+      <c r="G92" s="2203" t="n"/>
+      <c r="H92" s="2203" t="n"/>
+      <c r="I92" s="2203" t="n"/>
       <c r="J92" s="1521" t="n"/>
       <c r="K92" s="2152">
         <f>SUM(D92:I92)</f>
@@ -33576,23 +33576,23 @@
       </c>
       <c r="L92" s="2112" t="n"/>
       <c r="M92" s="2152">
-        <f>K92-K34-K41</f>
+        <f>K92-K34</f>
         <v/>
       </c>
     </row>
     <row r="93" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B93" s="2200" t="inlineStr">
-        <is>
-          <t>KeyKeg 20L - Leeg</t>
-        </is>
-      </c>
-      <c r="C93" s="2201" t="n"/>
-      <c r="D93" s="2202" t="n"/>
-      <c r="E93" s="2203" t="n"/>
-      <c r="F93" s="2203" t="n"/>
-      <c r="G93" s="2203" t="n"/>
-      <c r="H93" s="2203" t="n"/>
-      <c r="I93" s="2203" t="n"/>
+      <c r="B93" s="2016" t="inlineStr">
+        <is>
+          <t>KeyKeg 30L - Leeg</t>
+        </is>
+      </c>
+      <c r="C93" s="2204" t="n"/>
+      <c r="D93" s="2160" t="n"/>
+      <c r="E93" s="2161" t="n"/>
+      <c r="F93" s="2161" t="n"/>
+      <c r="G93" s="2161" t="n"/>
+      <c r="H93" s="2161" t="n"/>
+      <c r="I93" s="2161" t="n"/>
       <c r="J93" s="1521" t="n"/>
       <c r="K93" s="2152">
         <f>SUM(D93:I93)</f>
@@ -33600,64 +33600,48 @@
       </c>
       <c r="L93" s="2112" t="n"/>
       <c r="M93" s="2152">
-        <f>K93-K34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B94" s="2016" t="inlineStr">
-        <is>
-          <t>KeyKeg 30L - Leeg</t>
-        </is>
-      </c>
-      <c r="C94" s="2204" t="n"/>
-      <c r="D94" s="2160" t="n"/>
-      <c r="E94" s="2161" t="n"/>
-      <c r="F94" s="2161" t="n"/>
-      <c r="G94" s="2161" t="n"/>
-      <c r="H94" s="2161" t="n"/>
-      <c r="I94" s="2161" t="n"/>
-      <c r="J94" s="1521" t="n"/>
-      <c r="K94" s="2152">
-        <f>SUM(D94:I94)</f>
-        <v/>
-      </c>
-      <c r="L94" s="2112" t="n"/>
-      <c r="M94" s="2152">
-        <f>K94-K41</f>
-        <v/>
-      </c>
-    </row>
+        <f>K93-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="1339"/>
     <row r="95" ht="15" customHeight="1" s="1339"/>
-    <row r="96" ht="15" customHeight="1" s="1339"/>
+    <row r="96" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B96" s="2013" t="inlineStr">
+        <is>
+          <t>Ingevoerd in Mdrank</t>
+        </is>
+      </c>
+      <c r="C96" s="2026" t="inlineStr">
+        <is>
+          <t>door:</t>
+        </is>
+      </c>
+      <c r="D96" s="2205" t="n"/>
+      <c r="E96" s="1115" t="n"/>
+    </row>
     <row r="97" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B97" s="2013" t="inlineStr">
-        <is>
-          <t>Ingevoerd in Mdrank</t>
-        </is>
-      </c>
+      <c r="B97" s="2206" t="n"/>
       <c r="C97" s="2026" t="inlineStr">
         <is>
-          <t>door:</t>
-        </is>
-      </c>
-      <c r="D97" s="2205" t="n"/>
+          <t>datum:</t>
+        </is>
+      </c>
+      <c r="D97" s="2215" t="n"/>
       <c r="E97" s="1115" t="n"/>
     </row>
     <row r="98" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B98" s="2206" t="n"/>
-      <c r="C98" s="2026" t="inlineStr">
-        <is>
-          <t>datum:</t>
-        </is>
-      </c>
-      <c r="D98" s="2215" t="n"/>
-      <c r="E98" s="1115" t="n"/>
+      <c r="B98" s="2208" t="inlineStr">
+        <is>
+          <t>V2,1 : 09-10-17 KYT</t>
+        </is>
+      </c>
+      <c r="C98" s="1521" t="n"/>
     </row>
     <row r="99" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B99" s="2208" t="inlineStr">
         <is>
-          <t>V2,1 : 09-10-17 KYT</t>
+          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
         </is>
       </c>
       <c r="C99" s="1521" t="n"/>
@@ -33665,7 +33649,7 @@
     <row r="100" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B100" s="2208" t="inlineStr">
         <is>
-          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
+          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
         </is>
       </c>
       <c r="C100" s="1521" t="n"/>
@@ -33673,18 +33657,10 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B101" s="2208" t="inlineStr">
         <is>
-          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
+          <t>v3 6/2/24 TW</t>
         </is>
       </c>
       <c r="C101" s="1521" t="n"/>
-    </row>
-    <row r="102" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B102" s="2208" t="inlineStr">
-        <is>
-          <t>v3 6/2/24 TW</t>
-        </is>
-      </c>
-      <c r="C102" s="1521" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -33694,7 +33670,7 @@
     <mergeCell ref="K43:M43"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B1:I2"/>
-    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="D97:E97"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="C3:E4"/>
     <mergeCell ref="O72:R72"/>
@@ -33710,7 +33686,7 @@
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="O62:R62"/>
     <mergeCell ref="F3:G4"/>
-    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="D96:E96"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="M1:R1"/>
@@ -33782,7 +33758,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M86">
+  <conditionalFormatting sqref="M85">
     <cfRule type="cellIs" rank="0" priority="17" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33793,12 +33769,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K86">
+  <conditionalFormatting sqref="K85">
     <cfRule type="cellIs" rank="0" priority="20" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M87">
+  <conditionalFormatting sqref="M86">
     <cfRule type="cellIs" rank="0" priority="21" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33809,12 +33785,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K87">
+  <conditionalFormatting sqref="K86">
     <cfRule type="cellIs" rank="0" priority="24" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M88:M89">
+  <conditionalFormatting sqref="M87:M88">
     <cfRule type="cellIs" rank="0" priority="25" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33825,29 +33801,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88:K89">
+  <conditionalFormatting sqref="K87:K88">
     <cfRule type="cellIs" rank="0" priority="28" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35">
     <cfRule type="cellIs" rank="0" priority="29" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="29" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M85">
-    <cfRule type="cellIs" rank="0" priority="30" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="31" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="31" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="32" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K85">
-    <cfRule type="cellIs" rank="0" priority="33" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33861,7 +33821,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50:M60 M62:M72 M83 M90:M95">
+  <conditionalFormatting sqref="M50:M60 M62:M72 M83 M89:M94">
     <cfRule type="cellIs" rank="0" priority="36" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33887,7 +33847,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K41 K44:K46 K90:K95 R61 R70:R71">
+  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K41 K44:K46 K89:K94 R61 R70:R71">
     <cfRule type="cellIs" rank="0" priority="42" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -29784,7 +29784,7 @@
       </c>
       <c r="B61" s="2069" t="n"/>
       <c r="C61" s="2078">
-        <f>SUM(Afvulverslag!M85:M86)</f>
+        <f>SUM(Afvulverslag!M85:M87,Afvulverslag!M89:M92)</f>
         <v/>
       </c>
       <c r="D61" s="2070" t="n"/>
@@ -31093,7 +31093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.00390625" defaultRowHeight="15" zeroHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="2.5" customWidth="1" style="2094" min="1" max="1"/>
@@ -32060,7 +32060,7 @@
     <row r="34" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B34" s="2013" t="inlineStr">
         <is>
-          <t>20L KeyKeg</t>
+          <t>20L KU Fust</t>
         </is>
       </c>
       <c r="C34" s="2149" t="n"/>
@@ -32084,7 +32084,7 @@
     <row r="35" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B35" s="2013" t="inlineStr">
         <is>
-          <t>20L KU Fust</t>
+          <t>30L Jopen Fust</t>
         </is>
       </c>
       <c r="C35" s="2149" t="n"/>
@@ -32101,23 +32101,23 @@
       </c>
       <c r="L35" s="2112" t="n"/>
       <c r="M35" s="2154">
-        <f>K35*20</f>
+        <f>K35*30</f>
         <v/>
       </c>
     </row>
     <row r="36" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B36" s="2013" t="inlineStr">
         <is>
-          <t>30L Jopen Fust</t>
-        </is>
-      </c>
-      <c r="C36" s="2158" t="n"/>
-      <c r="D36" s="2150" t="n"/>
-      <c r="E36" s="2151" t="n"/>
-      <c r="F36" s="2151" t="n"/>
-      <c r="G36" s="2151" t="n"/>
-      <c r="H36" s="2151" t="n"/>
-      <c r="I36" s="2150" t="n"/>
+          <t>50L Jopen Fust</t>
+        </is>
+      </c>
+      <c r="C36" s="2149" t="n"/>
+      <c r="D36" s="2160" t="n"/>
+      <c r="E36" s="2160" t="n"/>
+      <c r="F36" s="2160" t="n"/>
+      <c r="G36" s="2160" t="n"/>
+      <c r="H36" s="2160" t="n"/>
+      <c r="I36" s="2161" t="n"/>
       <c r="J36" s="1521" t="n"/>
       <c r="K36" s="2152">
         <f>SUM(D36:I36)</f>
@@ -32125,61 +32125,61 @@
       </c>
       <c r="L36" s="2112" t="n"/>
       <c r="M36" s="2154">
-        <f>K36*30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B37" s="2013" t="inlineStr">
-        <is>
-          <t>50L Jopen Fust</t>
-        </is>
-      </c>
-      <c r="C37" s="2149" t="n"/>
-      <c r="D37" s="2160" t="n"/>
-      <c r="E37" s="2160" t="n"/>
-      <c r="F37" s="2160" t="n"/>
-      <c r="G37" s="2160" t="n"/>
-      <c r="H37" s="2160" t="n"/>
-      <c r="I37" s="2161" t="n"/>
+        <f>K36*50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B37" s="2162" t="n"/>
+      <c r="C37" s="1521" t="n"/>
+      <c r="D37" s="2163" t="n"/>
+      <c r="E37" s="2163" t="n"/>
+      <c r="F37" s="2163" t="n"/>
+      <c r="G37" s="2163" t="n"/>
+      <c r="H37" s="2163" t="n"/>
+      <c r="I37" s="2164" t="n"/>
       <c r="J37" s="1521" t="n"/>
-      <c r="K37" s="2152">
-        <f>SUM(D37:I37)</f>
-        <v/>
-      </c>
+      <c r="K37" s="2152" t="n"/>
       <c r="L37" s="2112" t="n"/>
-      <c r="M37" s="2154">
-        <f>K37*50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B38" s="2162" t="n"/>
+      <c r="M37" s="2154" t="n"/>
+    </row>
+    <row r="38" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B38" s="2013" t="inlineStr">
+        <is>
+          <t>20L Gebr. Door Vrouwen Fust</t>
+        </is>
+      </c>
       <c r="C38" s="1521" t="n"/>
-      <c r="D38" s="2163" t="n"/>
-      <c r="E38" s="2163" t="n"/>
-      <c r="F38" s="2163" t="n"/>
-      <c r="G38" s="2163" t="n"/>
-      <c r="H38" s="2163" t="n"/>
-      <c r="I38" s="2164" t="n"/>
+      <c r="D38" s="2165" t="n"/>
+      <c r="E38" s="2165" t="n"/>
+      <c r="F38" s="2165" t="n"/>
+      <c r="G38" s="2165" t="n"/>
+      <c r="H38" s="2165" t="n"/>
+      <c r="I38" s="2166" t="n"/>
       <c r="J38" s="1521" t="n"/>
-      <c r="K38" s="2152" t="n"/>
+      <c r="K38" s="2152">
+        <f>SUM(D38:I38)</f>
+        <v/>
+      </c>
       <c r="L38" s="2112" t="n"/>
-      <c r="M38" s="2154" t="n"/>
+      <c r="M38" s="2154">
+        <f>K38*20</f>
+        <v/>
+      </c>
     </row>
     <row r="39" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B39" s="2013" t="inlineStr">
         <is>
-          <t>20L Gbr. Door Vrouwen fust</t>
+          <t>20L Other Fust</t>
         </is>
       </c>
       <c r="C39" s="1521" t="n"/>
-      <c r="D39" s="2165" t="n"/>
-      <c r="E39" s="2165" t="n"/>
-      <c r="F39" s="2165" t="n"/>
-      <c r="G39" s="2165" t="n"/>
-      <c r="H39" s="2165" t="n"/>
-      <c r="I39" s="2166" t="n"/>
+      <c r="D39" s="2151" t="n"/>
+      <c r="E39" s="2151" t="n"/>
+      <c r="F39" s="2151" t="n"/>
+      <c r="G39" s="2151" t="n"/>
+      <c r="H39" s="2151" t="n"/>
+      <c r="I39" s="2150" t="n"/>
       <c r="J39" s="1521" t="n"/>
       <c r="K39" s="2152">
         <f>SUM(D39:I39)</f>
@@ -32194,7 +32194,7 @@
     <row r="40" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B40" s="2013" t="inlineStr">
         <is>
-          <t>20L Other kegs</t>
+          <t>20L KeyKeg</t>
         </is>
       </c>
       <c r="C40" s="1521" t="n"/>
@@ -33411,7 +33411,7 @@
     <row r="85" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B85" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 20L: </t>
+          <t>20L KU Fust</t>
         </is>
       </c>
       <c r="C85" s="1615" t="n"/>
@@ -33428,14 +33428,14 @@
       </c>
       <c r="L85" s="2112" t="n"/>
       <c r="M85" s="2152">
-        <f>K85-K35</f>
+        <f>K85-K34</f>
         <v/>
       </c>
     </row>
     <row r="86" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B86" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 30L: </t>
+          <t>30L Jopen Fust</t>
         </is>
       </c>
       <c r="C86" s="1615" t="n"/>
@@ -33445,21 +33445,21 @@
       <c r="G86" s="2184" t="n"/>
       <c r="H86" s="2184" t="n"/>
       <c r="I86" s="2184" t="n"/>
-      <c r="J86" s="2170" t="n"/>
+      <c r="J86" s="1521" t="n"/>
       <c r="K86" s="2152">
         <f>SUM(D86:I86)</f>
         <v/>
       </c>
       <c r="L86" s="2112" t="n"/>
       <c r="M86" s="2152">
-        <f>K86-K36</f>
+        <f>K86-K35</f>
         <v/>
       </c>
     </row>
     <row r="87" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B87" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jopen Fust 50L: </t>
+          <t>50L Jopen Fust</t>
         </is>
       </c>
       <c r="C87" s="1615" t="n"/>
@@ -33476,7 +33476,7 @@
       </c>
       <c r="L87" s="2112" t="n"/>
       <c r="M87" s="2152">
-        <f>K87-K37</f>
+        <f>K87-K36</f>
         <v/>
       </c>
     </row>
@@ -33497,7 +33497,7 @@
     <row r="89" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B89" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fustdop: </t>
+          <t>20L Gebr. Door Vrouwen Fust</t>
         </is>
       </c>
       <c r="C89" s="1615" t="n"/>
@@ -33514,37 +33514,47 @@
       </c>
       <c r="L89" s="2112" t="n"/>
       <c r="M89" s="2152">
-        <f>K89-SUM(K34:K37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B90" s="1099" t="n"/>
-      <c r="C90" s="2170" t="n"/>
-      <c r="D90" s="1521" t="n"/>
-      <c r="E90" s="1521" t="n"/>
-      <c r="F90" s="1521" t="n"/>
-      <c r="G90" s="1521" t="n"/>
-      <c r="H90" s="1521" t="n"/>
-      <c r="I90" s="1521" t="n"/>
-      <c r="J90" s="2170" t="n"/>
-      <c r="K90" s="2152" t="n"/>
+        <f>K89-K38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B90" s="2016" t="inlineStr">
+        <is>
+          <t>20L Other Fust</t>
+        </is>
+      </c>
+      <c r="C90" s="1615" t="n"/>
+      <c r="D90" s="2167" t="n"/>
+      <c r="E90" s="2184" t="n"/>
+      <c r="F90" s="2184" t="n"/>
+      <c r="G90" s="2184" t="n"/>
+      <c r="H90" s="2184" t="n"/>
+      <c r="I90" s="2184" t="n"/>
+      <c r="J90" s="1521" t="n"/>
+      <c r="K90" s="2152">
+        <f>SUM(D90:I90)</f>
+        <v/>
+      </c>
       <c r="L90" s="2112" t="n"/>
-      <c r="M90" s="2152" t="n"/>
+      <c r="M90" s="2152">
+        <f>K90-K39</f>
+        <v/>
+      </c>
     </row>
     <row r="91" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B91" s="2199" t="inlineStr">
-        <is>
-          <t>KeyKegFustdop:</t>
-        </is>
-      </c>
-      <c r="C91" s="2179" t="n"/>
-      <c r="D91" s="2193" t="n"/>
-      <c r="E91" s="2194" t="n"/>
-      <c r="F91" s="2194" t="n"/>
-      <c r="G91" s="2194" t="n"/>
-      <c r="H91" s="2194" t="n"/>
-      <c r="I91" s="2194" t="n"/>
+      <c r="B91" s="2016" t="inlineStr">
+        <is>
+          <t>20L KeyKeg</t>
+        </is>
+      </c>
+      <c r="C91" s="1615" t="n"/>
+      <c r="D91" s="2167" t="n"/>
+      <c r="E91" s="2184" t="n"/>
+      <c r="F91" s="2184" t="n"/>
+      <c r="G91" s="2184" t="n"/>
+      <c r="H91" s="2184" t="n"/>
+      <c r="I91" s="2184" t="n"/>
       <c r="J91" s="1521" t="n"/>
       <c r="K91" s="2152">
         <f>SUM(D91:I91)</f>
@@ -33552,23 +33562,23 @@
       </c>
       <c r="L91" s="2112" t="n"/>
       <c r="M91" s="2152">
-        <f>K91-K34-K41</f>
+        <f>K91-K40</f>
         <v/>
       </c>
     </row>
     <row r="92" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B92" s="2200" t="inlineStr">
-        <is>
-          <t>KeyKeg 20L - Leeg</t>
-        </is>
-      </c>
-      <c r="C92" s="2201" t="n"/>
-      <c r="D92" s="2202" t="n"/>
-      <c r="E92" s="2203" t="n"/>
-      <c r="F92" s="2203" t="n"/>
-      <c r="G92" s="2203" t="n"/>
-      <c r="H92" s="2203" t="n"/>
-      <c r="I92" s="2203" t="n"/>
+      <c r="B92" s="2016" t="inlineStr">
+        <is>
+          <t>30L KeyKeg</t>
+        </is>
+      </c>
+      <c r="C92" s="1615" t="n"/>
+      <c r="D92" s="2167" t="n"/>
+      <c r="E92" s="2184" t="n"/>
+      <c r="F92" s="2184" t="n"/>
+      <c r="G92" s="2184" t="n"/>
+      <c r="H92" s="2184" t="n"/>
+      <c r="I92" s="2184" t="n"/>
       <c r="J92" s="1521" t="n"/>
       <c r="K92" s="2152">
         <f>SUM(D92:I92)</f>
@@ -33576,80 +33586,102 @@
       </c>
       <c r="L92" s="2112" t="n"/>
       <c r="M92" s="2152">
-        <f>K92-K34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B93" s="2016" t="inlineStr">
-        <is>
-          <t>KeyKeg 30L - Leeg</t>
-        </is>
-      </c>
-      <c r="C93" s="2204" t="n"/>
-      <c r="D93" s="2160" t="n"/>
-      <c r="E93" s="2161" t="n"/>
-      <c r="F93" s="2161" t="n"/>
-      <c r="G93" s="2161" t="n"/>
-      <c r="H93" s="2161" t="n"/>
-      <c r="I93" s="2161" t="n"/>
+        <f>K92-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B93" s="2185" t="n"/>
+      <c r="C93" s="2198" t="n"/>
+      <c r="D93" s="2156" t="n"/>
+      <c r="E93" s="2156" t="n"/>
+      <c r="F93" s="2156" t="n"/>
+      <c r="G93" s="2156" t="n"/>
+      <c r="H93" s="2156" t="n"/>
+      <c r="I93" s="2156" t="n"/>
       <c r="J93" s="1521" t="n"/>
-      <c r="K93" s="2152">
-        <f>SUM(D93:I93)</f>
-        <v/>
-      </c>
+      <c r="K93" s="2152" t="n"/>
       <c r="L93" s="2112" t="n"/>
-      <c r="M93" s="2152">
-        <f>K93-K41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="1339"/>
-    <row r="95" ht="15" customHeight="1" s="1339"/>
-    <row r="96" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B96" s="2013" t="inlineStr">
+      <c r="M93" s="2152" t="n"/>
+    </row>
+    <row r="94" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B94" s="2016" t="inlineStr">
+        <is>
+          <t>Fustdop:</t>
+        </is>
+      </c>
+      <c r="C94" s="1615" t="n"/>
+      <c r="D94" s="2167" t="n"/>
+      <c r="E94" s="2184" t="n"/>
+      <c r="F94" s="2184" t="n"/>
+      <c r="G94" s="2184" t="n"/>
+      <c r="H94" s="2184" t="n"/>
+      <c r="I94" s="2184" t="n"/>
+      <c r="J94" s="1521" t="n"/>
+      <c r="K94" s="2152">
+        <f>SUM(D94:I94)</f>
+        <v/>
+      </c>
+      <c r="L94" s="2112" t="n"/>
+      <c r="M94" s="2152">
+        <f>K94-K34-K35-K36-K38-K39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B95" s="2016" t="inlineStr">
+        <is>
+          <t>KeyKegFustdop:</t>
+        </is>
+      </c>
+      <c r="C95" s="2204" t="n"/>
+      <c r="D95" s="2160" t="n"/>
+      <c r="E95" s="2161" t="n"/>
+      <c r="F95" s="2161" t="n"/>
+      <c r="G95" s="2161" t="n"/>
+      <c r="H95" s="2161" t="n"/>
+      <c r="I95" s="2161" t="n"/>
+      <c r="J95" s="1521" t="n"/>
+      <c r="K95" s="2152">
+        <f>SUM(D95:I95)</f>
+        <v/>
+      </c>
+      <c r="L95" s="2112" t="n"/>
+      <c r="M95" s="2152">
+        <f>K95-K40-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="1339"/>
+    <row r="97" ht="15" customHeight="1" s="1339"/>
+    <row r="98" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B98" s="2013" t="inlineStr">
         <is>
           <t>Ingevoerd in Mdrank</t>
         </is>
       </c>
-      <c r="C96" s="2026" t="inlineStr">
+      <c r="C98" s="2026" t="inlineStr">
         <is>
           <t>door:</t>
         </is>
       </c>
-      <c r="D96" s="2205" t="n"/>
-      <c r="E96" s="1115" t="n"/>
-    </row>
-    <row r="97" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B97" s="2206" t="n"/>
-      <c r="C97" s="2026" t="inlineStr">
+      <c r="D98" s="2205" t="n"/>
+      <c r="E98" s="1115" t="n"/>
+    </row>
+    <row r="99" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B99" s="2206" t="n"/>
+      <c r="C99" s="2026" t="inlineStr">
         <is>
           <t>datum:</t>
         </is>
       </c>
-      <c r="D97" s="2215" t="n"/>
-      <c r="E97" s="1115" t="n"/>
-    </row>
-    <row r="98" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B98" s="2208" t="inlineStr">
-        <is>
-          <t>V2,1 : 09-10-17 KYT</t>
-        </is>
-      </c>
-      <c r="C98" s="1521" t="n"/>
-    </row>
-    <row r="99" ht="15" customFormat="1" customHeight="1" s="1425">
-      <c r="B99" s="2208" t="inlineStr">
-        <is>
-          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
-        </is>
-      </c>
-      <c r="C99" s="1521" t="n"/>
+      <c r="D99" s="2215" t="n"/>
+      <c r="E99" s="1115" t="n"/>
     </row>
     <row r="100" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B100" s="2208" t="inlineStr">
         <is>
-          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
+          <t>V2,1 : 09-10-17 KYT</t>
         </is>
       </c>
       <c r="C100" s="1521" t="n"/>
@@ -33657,10 +33689,26 @@
     <row r="101" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B101" s="2208" t="inlineStr">
         <is>
+          <t>V2,001 : 02/10/2017 KYT, invoeg MR-Opdracht</t>
+        </is>
+      </c>
+      <c r="C101" s="1521" t="n"/>
+    </row>
+    <row r="102" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B102" s="2208" t="inlineStr">
+        <is>
+          <t>V2,002 : 22/11/2018 KYT: nav MvdG&amp;JL</t>
+        </is>
+      </c>
+      <c r="C102" s="1521" t="n"/>
+    </row>
+    <row r="103" ht="15" customFormat="1" customHeight="1" s="1425">
+      <c r="B103" s="2208" t="inlineStr">
+        <is>
           <t>v3 6/2/24 TW</t>
         </is>
       </c>
-      <c r="C101" s="1521" t="n"/>
+      <c r="C103" s="1521" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -33670,7 +33718,7 @@
     <mergeCell ref="K43:M43"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B1:I2"/>
-    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="D99:E99"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="C3:E4"/>
     <mergeCell ref="O72:R72"/>
@@ -33686,7 +33734,7 @@
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="O62:R62"/>
     <mergeCell ref="F3:G4"/>
-    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="D98:E98"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="M1:R1"/>
@@ -33821,7 +33869,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50:M60 M62:M72 M83 M89:M94">
+  <conditionalFormatting sqref="M50:M60 M62:M72 M83 M89:M96">
     <cfRule type="cellIs" rank="0" priority="36" equalAverage="0" operator="equal" aboveAverage="0" dxfId="30" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>
@@ -33847,7 +33895,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K41 K44:K46 K89:K94 R61 R70:R71">
+  <conditionalFormatting sqref="K17:K18 K20:K21 K23:K25 K34:K41 K44:K46 K89:K96 R61 R70:R71">
     <cfRule type="cellIs" rank="0" priority="42" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>0</formula>
     </cfRule>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -7,18 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recept-voorblad" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brouwen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gistkaart Invoer" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verwerking" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Afvullen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Afvulverslag" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recipe Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brew Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fermentation Chart" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filling" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filling Report" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xleta.ROUND" hidden="1" function="0" vbProcedure="0">#NAME?</definedName>
     <definedName name="_xleta.ROUNDUP" hidden="1" function="0" vbProcedure="0">#NAME?</definedName>
     <definedName name="_xleta.TYPE" hidden="1" function="0" vbProcedure="0">#NAME?</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Recept-voorblad'!$A$1:$P$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Recipe Sheet'!$A$1:$P$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -10115,7 +10115,7 @@
     <row r="1" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A1" s="1074" t="inlineStr">
         <is>
-          <t>Receptuur</t>
+          <t xml:space="preserve">Recipe Sheet</t>
         </is>
       </c>
       <c r="B1" s="1075" t="n"/>
@@ -10169,7 +10169,7 @@
     <row r="3" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A3" s="1082" t="inlineStr">
         <is>
-          <t>Naam bier</t>
+          <t xml:space="preserve">Beer name</t>
         </is>
       </c>
       <c r="B3" s="1083" t="n"/>
@@ -10180,7 +10180,7 @@
       <c r="G3" s="1075" t="n"/>
       <c r="H3" s="1085" t="inlineStr">
         <is>
-          <t>Batch nr.:</t>
+          <t xml:space="preserve">Batch No.:</t>
         </is>
       </c>
       <c r="I3" s="1075" t="n"/>
@@ -10224,7 +10224,7 @@
     <row r="5" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A5" s="1096" t="inlineStr">
         <is>
-          <t>Naam Brouwerij</t>
+          <t xml:space="preserve">Brewery name</t>
         </is>
       </c>
       <c r="B5" s="1075" t="n"/>
@@ -10270,7 +10270,7 @@
     <row r="7" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A7" s="1085" t="inlineStr">
         <is>
-          <t>Bier stijl</t>
+          <t xml:space="preserve">Beer style</t>
         </is>
       </c>
       <c r="B7" s="1076" t="n"/>
@@ -10278,7 +10278,7 @@
       <c r="D7" s="1076" t="n"/>
       <c r="E7" s="1102" t="inlineStr">
         <is>
-          <t>Aantal brouwsels</t>
+          <t xml:space="preserve">Number of brews</t>
         </is>
       </c>
       <c r="F7" s="1076" t="n"/>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="H7" s="1104" t="inlineStr">
         <is>
-          <t>Datum orderpicken:</t>
+          <t xml:space="preserve">Date order picked:</t>
         </is>
       </c>
       <c r="I7" s="1075" t="n"/>
@@ -10334,14 +10334,14 @@
     <row r="9" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A9" s="1109" t="inlineStr">
         <is>
-          <t>Brouwsel (hl)</t>
+          <t xml:space="preserve">Brew size (hl)</t>
         </is>
       </c>
       <c r="B9" s="1076" t="n"/>
       <c r="C9" s="1110" t="n"/>
       <c r="D9" s="1076" t="n"/>
       <c r="E9" s="1111">
-        <f>IF(LEFT(Q1,2)="WP", "Kamers mashfilter","walsenmolen")</f>
+        <f>IF(LEFT(Q1,2)="WP", "Mash Filter Chambers","Roller Mill Setting")</f>
         <v/>
       </c>
       <c r="F9" s="1075" t="n"/>
@@ -10364,7 +10364,7 @@
     <row r="10" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A10" s="1113" t="inlineStr">
         <is>
-          <t>Eindproduct specificaties</t>
+          <t xml:space="preserve">End Product Specifications</t>
         </is>
       </c>
       <c r="B10" s="1114" t="n"/>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="F11" s="1118" t="inlineStr">
         <is>
-          <t>Spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="G11" s="1116" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="M11" s="1117" t="inlineStr">
         <is>
-          <t>Spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="N11" s="1098" t="n"/>
@@ -10446,7 +10446,7 @@
     <row r="12" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A12" s="1119" t="inlineStr">
         <is>
-          <t>Origineel extract</t>
+          <t xml:space="preserve">Original Extract</t>
         </is>
       </c>
       <c r="B12" s="1075" t="n"/>
@@ -10460,7 +10460,7 @@
       <c r="F12" s="1122" t="n"/>
       <c r="G12" s="1123" t="inlineStr">
         <is>
-          <t>Troebeling (Lab)</t>
+          <t xml:space="preserve">Turbidity (Lab)</t>
         </is>
       </c>
       <c r="H12" s="1075" t="n"/>
@@ -10485,7 +10485,7 @@
     <row r="13" ht="15" customFormat="1" customHeight="1" s="1073">
       <c r="A13" s="1125" t="inlineStr">
         <is>
-          <t>Rest extract</t>
+          <t xml:space="preserve">Final Extract</t>
         </is>
       </c>
       <c r="C13" s="1083" t="n"/>
@@ -10498,7 +10498,7 @@
       <c r="F13" s="1127" t="n"/>
       <c r="G13" s="1128" t="inlineStr">
         <is>
-          <t>CO2 fles</t>
+          <t xml:space="preserve">CO2 bottle</t>
         </is>
       </c>
       <c r="J13" s="1083" t="n"/>
@@ -10534,7 +10534,7 @@
       <c r="F14" s="1127" t="n"/>
       <c r="G14" s="1128" t="inlineStr">
         <is>
-          <t>CO2 Can</t>
+          <t xml:space="preserve">CO2 can</t>
         </is>
       </c>
       <c r="J14" s="1083" t="n"/>
@@ -10557,7 +10557,7 @@
     <row r="15" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A15" s="1125" t="inlineStr">
         <is>
-          <t>Bitterheid</t>
+          <t xml:space="preserve">Bitterness</t>
         </is>
       </c>
       <c r="C15" s="1083" t="n"/>
@@ -10570,7 +10570,7 @@
       <c r="F15" s="1131" t="n"/>
       <c r="G15" s="1128" t="inlineStr">
         <is>
-          <t>CO2 fust</t>
+          <t xml:space="preserve">CO2 keg</t>
         </is>
       </c>
       <c r="J15" s="1083" t="n"/>
@@ -10593,7 +10593,7 @@
     <row r="16" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A16" s="1125" t="inlineStr">
         <is>
-          <t>Kleur</t>
+          <t xml:space="preserve">Colour</t>
         </is>
       </c>
       <c r="C16" s="1083" t="n"/>
@@ -10621,7 +10621,7 @@
       <c r="M16" s="1129" t="n"/>
       <c r="N16" s="1137" t="inlineStr">
         <is>
-          <t>Bier risico</t>
+          <t xml:space="preserve">Beer Risk Category</t>
         </is>
       </c>
       <c r="O16" s="1114" t="n"/>
@@ -10695,7 +10695,7 @@
     <row r="19" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A19" s="1148" t="inlineStr">
         <is>
-          <t>Process paramaters</t>
+          <t xml:space="preserve">Process Parameters</t>
         </is>
       </c>
       <c r="B19" s="1114" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F20" s="1117" t="inlineStr">
         <is>
-          <t>Spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="G20" s="1149" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="M20" s="1118" t="inlineStr">
         <is>
-          <t>Spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="N20" s="1108" t="n"/>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A21" s="1119">
-        <f>IF(LEFT(Q1,2)="WP", "Pitching Temp,","Wort koeling temp,")</f>
+        <f>IF(LEFT(Q1,2)="WP", "Pitching Temp","Wort Cooling Temp")</f>
         <v/>
       </c>
       <c r="B21" s="1075" t="n"/>
@@ -10790,7 +10790,7 @@
       <c r="F21" s="1122" t="n"/>
       <c r="G21" s="1123" t="inlineStr">
         <is>
-          <t>Vergistingstijd</t>
+          <t xml:space="preserve">Fermentation Time</t>
         </is>
       </c>
       <c r="H21" s="1075" t="n"/>
@@ -10798,14 +10798,14 @@
       <c r="J21" s="1076" t="n"/>
       <c r="K21" s="1120" t="inlineStr">
         <is>
-          <t>dagen</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="L21" s="1151" t="n"/>
       <c r="M21" s="1124" t="n"/>
       <c r="N21" s="1137" t="inlineStr">
         <is>
-          <t>Bier status</t>
+          <t xml:space="preserve">Beer Status</t>
         </is>
       </c>
       <c r="O21" s="1114" t="n"/>
@@ -10819,7 +10819,7 @@
     <row r="22" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A22" s="1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main Fermentation </t>
+          <t xml:space="preserve">Main Fermentation</t>
         </is>
       </c>
       <c r="D22" s="1126" t="inlineStr">
@@ -10831,7 +10831,7 @@
       <c r="F22" s="1127" t="n"/>
       <c r="G22" s="1136" t="inlineStr">
         <is>
-          <t>Lagertijd</t>
+          <t xml:space="preserve">Lagering Time</t>
         </is>
       </c>
       <c r="H22" s="1136" t="n"/>
@@ -10839,7 +10839,7 @@
       <c r="J22" s="1128" t="n"/>
       <c r="K22" s="1126" t="inlineStr">
         <is>
-          <t>dagen</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="L22" s="1151" t="n"/>
@@ -10856,7 +10856,7 @@
     <row r="23" ht="15" customFormat="1" customHeight="1" s="1130">
       <c r="A23" s="1125" t="inlineStr">
         <is>
-          <t>T release,</t>
+          <t xml:space="preserve">Temp Release</t>
         </is>
       </c>
       <c r="C23" s="1083" t="n"/>
@@ -10869,7 +10869,7 @@
       <c r="F23" s="1127" t="n"/>
       <c r="G23" s="1136" t="inlineStr">
         <is>
-          <t>Lager temp,</t>
+          <t xml:space="preserve">Lagering Temp</t>
         </is>
       </c>
       <c r="H23" s="1136" t="n"/>
@@ -10894,7 +10894,7 @@
     <row r="24" ht="15.75" customFormat="1" customHeight="1" s="1159">
       <c r="A24" s="1125" t="inlineStr">
         <is>
-          <t>Temp, Dry, Warm,</t>
+          <t xml:space="preserve">Temp Warm Dry Hop</t>
         </is>
       </c>
       <c r="C24" s="1083" t="n"/>
@@ -10907,7 +10907,7 @@
       <c r="F24" s="1127" t="n"/>
       <c r="G24" s="1136" t="inlineStr">
         <is>
-          <t>Pasteurisatie</t>
+          <t xml:space="preserve">Pasteurisation</t>
         </is>
       </c>
       <c r="H24" s="1136" t="n"/>
@@ -10931,7 +10931,7 @@
     <row r="25" ht="15" customFormat="1" customHeight="1" s="1159">
       <c r="A25" s="1125" t="inlineStr">
         <is>
-          <t>Extract dry, Warm 1</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 1</t>
         </is>
       </c>
       <c r="C25" s="1083" t="n"/>
@@ -10944,7 +10944,7 @@
       <c r="F25" s="1127" t="n"/>
       <c r="G25" s="1128" t="inlineStr">
         <is>
-          <t>Troebeling na Sep</t>
+          <t xml:space="preserve">Turbidity After Centrifuge</t>
         </is>
       </c>
       <c r="J25" s="1083" t="n"/>
@@ -10966,7 +10966,7 @@
     <row r="26" ht="15" customFormat="1" customHeight="1" s="1159">
       <c r="A26" s="1125" t="inlineStr">
         <is>
-          <t>Extract dry, Warm 2</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 2</t>
         </is>
       </c>
       <c r="C26" s="1083" t="n"/>
@@ -10979,7 +10979,7 @@
       <c r="F26" s="1127" t="n"/>
       <c r="G26" s="1128" t="inlineStr">
         <is>
-          <t>Bitterheid BH</t>
+          <t xml:space="preserve">Bitterness Brewhouse</t>
         </is>
       </c>
       <c r="J26" s="1083" t="n"/>
@@ -11002,7 +11002,7 @@
     <row r="27" ht="15" customFormat="1" customHeight="1" s="1159">
       <c r="A27" s="1163" t="inlineStr">
         <is>
-          <t>Extract dry, Warm 3</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 3</t>
         </is>
       </c>
       <c r="B27" s="1080" t="n"/>
@@ -11060,7 +11060,7 @@
     <row r="29" ht="15.75" customFormat="1" customHeight="1" s="1159">
       <c r="A29" s="1171" t="inlineStr">
         <is>
-          <t>Soort</t>
+          <t xml:space="preserve">Type of malt</t>
         </is>
       </c>
       <c r="B29" s="1114" t="n"/>
@@ -11088,7 +11088,7 @@
       <c r="H29" s="1115" t="n"/>
       <c r="I29" s="1171" t="inlineStr">
         <is>
-          <t>Lotnummer</t>
+          <t xml:space="preserve">Lot Number</t>
         </is>
       </c>
       <c r="J29" s="1114" t="n"/>
@@ -11099,7 +11099,7 @@
       <c r="O29" s="1115" t="n"/>
       <c r="P29" s="1082" t="inlineStr">
         <is>
-          <t>Totaal kg:</t>
+          <t xml:space="preserve">Total kg:</t>
         </is>
       </c>
       <c r="Q29" s="1138" t="n"/>
@@ -11471,7 +11471,7 @@
     <row r="40" ht="15" customFormat="1" customHeight="1" s="1204">
       <c r="A40" s="1205" t="inlineStr">
         <is>
-          <t>Totaal:</t>
+          <t xml:space="preserve">Total kg:</t>
         </is>
       </c>
       <c r="B40" s="1075" t="n"/>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="I40" s="1211" t="inlineStr">
         <is>
-          <t>Berekende kleur:</t>
+          <t xml:space="preserve">Calculated Colour:</t>
         </is>
       </c>
       <c r="J40" s="1114" t="n"/>
@@ -11549,7 +11549,7 @@
     <row r="42" ht="15" customFormat="1" customHeight="1" s="1204">
       <c r="A42" s="1216" t="inlineStr">
         <is>
-          <t>Soort</t>
+          <t xml:space="preserve">Hop Variety</t>
         </is>
       </c>
       <c r="B42" s="1075" t="n"/>
@@ -11567,13 +11567,13 @@
       <c r="F42" s="1115" t="n"/>
       <c r="G42" s="1217" t="inlineStr">
         <is>
-          <t>Kooktijd</t>
+          <t xml:space="preserve">Boiling Time</t>
         </is>
       </c>
       <c r="H42" s="1083" t="n"/>
       <c r="I42" s="1218" t="inlineStr">
         <is>
-          <t>Rendement</t>
+          <t xml:space="preserve">Utilisation</t>
         </is>
       </c>
       <c r="J42" s="1115" t="n"/>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="L42" s="1082" t="inlineStr">
         <is>
-          <t>Lotnummer</t>
+          <t xml:space="preserve">Lot Number</t>
         </is>
       </c>
       <c r="M42" s="1080" t="n"/>
@@ -11592,7 +11592,7 @@
       <c r="O42" s="1081" t="n"/>
       <c r="P42" s="1220" t="inlineStr">
         <is>
-          <t>Totaal gram:</t>
+          <t xml:space="preserve">Total Grams:</t>
         </is>
       </c>
       <c r="Q42" s="1138" t="n"/>
@@ -11613,7 +11613,7 @@
       <c r="I43" s="1229" t="n"/>
       <c r="J43" s="1178" t="n"/>
       <c r="K43" s="1230">
-        <f>IFERROR(IF(E43="-","",(E43*1000)*(D43/100)*(I43/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E43="-","",(E43*1000)*(D43/100)*(I43/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L43" s="1231" t="n"/>
@@ -11642,7 +11642,7 @@
       <c r="I44" s="1229" t="n"/>
       <c r="J44" s="1178" t="n"/>
       <c r="K44" s="1181">
-        <f>IFERROR(IF(E44="-","",(E44*1000)*(D44/100)*(I44/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E44="-","",(E44*1000)*(D44/100)*(I44/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L44" s="1231" t="n"/>
@@ -11671,7 +11671,7 @@
       <c r="I45" s="1240" t="n"/>
       <c r="J45" s="1199" t="n"/>
       <c r="K45" s="1241">
-        <f>IFERROR(IF(E45="-","",(E45*1000)*(D45/100)*(I45/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E45="-","",(E45*1000)*(D45/100)*(I45/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L45" s="1242" t="n"/>
@@ -11700,7 +11700,7 @@
       <c r="I46" s="1247" t="n"/>
       <c r="J46" s="1227" t="n"/>
       <c r="K46" s="1248">
-        <f>IFERROR(IF(E46="-","",(E46*1000)*(D46/100)*(I46/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E46="-","",(E46*1000)*(D46/100)*(I46/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L46" s="1249" t="n"/>
@@ -11729,7 +11729,7 @@
       <c r="I47" s="1229" t="n"/>
       <c r="J47" s="1178" t="n"/>
       <c r="K47" s="1181">
-        <f>IFERROR(IF(E47="-","",(E47*1000)*(D47/100)*(I47/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E47="-","",(E47*1000)*(D47/100)*(I47/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L47" s="1231" t="n"/>
@@ -11758,7 +11758,7 @@
       <c r="I48" s="1240" t="n"/>
       <c r="J48" s="1199" t="n"/>
       <c r="K48" s="1241">
-        <f>IFERROR(IF(E48="-","",(E48*1000)*(D48/100)*(I48/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E48="-","",(E48*1000)*(D48/100)*(I48/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L48" s="1242" t="n"/>
@@ -11787,7 +11787,7 @@
       <c r="I49" s="1247" t="n"/>
       <c r="J49" s="1227" t="n"/>
       <c r="K49" s="1248">
-        <f>IFERROR(IF(E49="-","",(E49*1000)*(D49/100)*(I49/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E49="-","",(E49*1000)*(D49/100)*(I49/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L49" s="1249" t="n"/>
@@ -11816,7 +11816,7 @@
       <c r="I50" s="1229" t="n"/>
       <c r="J50" s="1178" t="n"/>
       <c r="K50" s="1181">
-        <f>IFERROR(IF(E50="-","",(E50*1000)*(D50/100)*(I50/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E50="-","",(E50*1000)*(D50/100)*(I50/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L50" s="1231" t="n"/>
@@ -11845,7 +11845,7 @@
       <c r="I51" s="1240" t="n"/>
       <c r="J51" s="1199" t="n"/>
       <c r="K51" s="1241">
-        <f>IFERROR(IF(E51="-","",(E51*1000)*(D51/100)*(I51/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E51="-","",(E51*1000)*(D51/100)*(I51/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L51" s="1242" t="n"/>
@@ -11874,7 +11874,7 @@
       <c r="I52" s="1247" t="n"/>
       <c r="J52" s="1227" t="n"/>
       <c r="K52" s="1248">
-        <f>IFERROR(IF(E52="-","",(E52*1000)*(D52/100)*(I52/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E52="-","",(E52*1000)*(D52/100)*(I52/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L52" s="1249" t="n"/>
@@ -11903,7 +11903,7 @@
       <c r="I53" s="1229" t="n"/>
       <c r="J53" s="1178" t="n"/>
       <c r="K53" s="1181">
-        <f>IFERROR(IF(E53="-","",(E53*1000)*(D53/100)*(I53/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E53="-","",(E53*1000)*(D53/100)*(I53/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L53" s="1231" t="n"/>
@@ -11932,7 +11932,7 @@
       <c r="I54" s="1229" t="n"/>
       <c r="J54" s="1178" t="n"/>
       <c r="K54" s="1181">
-        <f>IFERROR(IF(E54="-","",(E54*1000)*(D54/100)*(I54/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E54="-","",(E54*1000)*(D54/100)*(I54/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L54" s="1231" t="n"/>
@@ -11961,7 +11961,7 @@
       <c r="I55" s="1247" t="n"/>
       <c r="J55" s="1227" t="n"/>
       <c r="K55" s="1248">
-        <f>IFERROR(IF(E55="-","",(E55*1000)*(D55/100)*(I55/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E55="-","",(E55*1000)*(D55/100)*(I55/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L55" s="1249" t="n"/>
@@ -11990,7 +11990,7 @@
       <c r="I56" s="1229" t="n"/>
       <c r="J56" s="1178" t="n"/>
       <c r="K56" s="1181">
-        <f>IFERROR(IF(E56="-","",(E56*1000)*(D56/100)*(I56/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E56="-","",(E56*1000)*(D56/100)*(I56/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L56" s="1231" t="n"/>
@@ -12019,7 +12019,7 @@
       <c r="I57" s="1240" t="n"/>
       <c r="J57" s="1199" t="n"/>
       <c r="K57" s="1241">
-        <f>IFERROR(IF(E57="-","",(E57*1000)*(D57/100)*(I57/100)/(IF(Brouwen!$F$16*100="-",$C$9*100,Brouwen!$F$16*100))),"")</f>
+        <f>IFERROR(IF(E57="-","",(E57*1000)*(D57/100)*(I57/100)/(IF('Brew Sheet'!$F$16*100="-",$C$9*100,'Brew Sheet'!$F$16*100))),"")</f>
         <v/>
       </c>
       <c r="L57" s="1242" t="n"/>
@@ -12207,7 +12207,7 @@
       <c r="F64" s="1076" t="n"/>
       <c r="G64" s="1268" t="inlineStr">
         <is>
-          <t>Totale bitterheid:</t>
+          <t xml:space="preserve">Total Bitterness:</t>
         </is>
       </c>
       <c r="H64" s="1075" t="n"/>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M64" s="1271" t="inlineStr">
         <is>
-          <t>Totaal kg hop:</t>
+          <t xml:space="preserve">Total kg Hops:</t>
         </is>
       </c>
       <c r="N64" s="1075" t="n"/>
@@ -12242,7 +12242,7 @@
     <row r="65" ht="15.75" customFormat="1" customHeight="1" s="1221">
       <c r="A65" s="1275" t="inlineStr">
         <is>
-          <t>Hop totaal gewicht</t>
+          <t xml:space="preserve">Total Hop Weight</t>
         </is>
       </c>
       <c r="B65" s="1075" t="n"/>
@@ -12269,7 +12269,7 @@
     <row r="66" ht="15" customFormat="1" customHeight="1" s="1221">
       <c r="A66" s="1276" t="inlineStr">
         <is>
-          <t>Hop soort</t>
+          <t xml:space="preserve">Hop Variety</t>
         </is>
       </c>
       <c r="B66" s="1075" t="n"/>
@@ -12277,7 +12277,7 @@
       <c r="D66" s="1076" t="n"/>
       <c r="E66" s="1276" t="inlineStr">
         <is>
-          <t>Totaal gram</t>
+          <t xml:space="preserve">Total Grams</t>
         </is>
       </c>
       <c r="F66" s="1075" t="n"/>
@@ -12285,7 +12285,7 @@
       <c r="H66" s="1076" t="n"/>
       <c r="I66" s="1276" t="inlineStr">
         <is>
-          <t>Hop soort</t>
+          <t xml:space="preserve">Hop Variety</t>
         </is>
       </c>
       <c r="J66" s="1075" t="n"/>
@@ -12293,7 +12293,7 @@
       <c r="L66" s="1076" t="n"/>
       <c r="M66" s="1276" t="inlineStr">
         <is>
-          <t>Totaal gram</t>
+          <t xml:space="preserve">Total Grams</t>
         </is>
       </c>
       <c r="N66" s="1075" t="n"/>
@@ -12521,7 +12521,7 @@
     <row r="74" ht="15" customFormat="1" customHeight="1" s="1221">
       <c r="A74" s="1285" t="inlineStr">
         <is>
-          <t>Soort</t>
+          <t xml:space="preserve">Type Of Addition</t>
         </is>
       </c>
       <c r="B74" s="1114" t="n"/>
@@ -12541,14 +12541,14 @@
       <c r="H74" s="1114" t="n"/>
       <c r="I74" s="1287" t="inlineStr">
         <is>
-          <t>Wanneer</t>
+          <t xml:space="preserve">Addition Moment</t>
         </is>
       </c>
       <c r="J74" s="1114" t="n"/>
       <c r="K74" s="1115" t="n"/>
       <c r="L74" s="1288" t="inlineStr">
         <is>
-          <t>Lotnummer</t>
+          <t xml:space="preserve">Lot Number</t>
         </is>
       </c>
       <c r="M74" s="1080" t="n"/>
@@ -12821,7 +12821,7 @@
     <row r="86" ht="15" customFormat="1" customHeight="1" s="1221">
       <c r="A86" s="1296" t="inlineStr">
         <is>
-          <t>Soort</t>
+          <t xml:space="preserve">Yeast Strain</t>
         </is>
       </c>
       <c r="B86" s="1114" t="n"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="G86" s="1298" t="inlineStr">
         <is>
-          <t>Hoeveelheid per batch</t>
+          <t xml:space="preserve">Amount Per Batch</t>
         </is>
       </c>
       <c r="H86" s="1114" t="n"/>
@@ -12844,7 +12844,7 @@
       <c r="K86" s="1115" t="n"/>
       <c r="L86" s="1299" t="inlineStr">
         <is>
-          <t>Lotnummer</t>
+          <t xml:space="preserve">Lot Number</t>
         </is>
       </c>
       <c r="M86" s="1080" t="n"/>
@@ -12943,7 +12943,7 @@
     <row r="90" ht="15" customFormat="1" customHeight="1" s="1221">
       <c r="A90" s="1285" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t xml:space="preserve">Type Of Addition</t>
         </is>
       </c>
       <c r="B90" s="1114" t="n"/>
@@ -12963,14 +12963,14 @@
       <c r="H90" s="1114" t="n"/>
       <c r="I90" s="1287" t="inlineStr">
         <is>
-          <t>When</t>
+          <t xml:space="preserve">Addition Moment</t>
         </is>
       </c>
       <c r="J90" s="1114" t="n"/>
       <c r="K90" s="1115" t="n"/>
       <c r="L90" s="1288" t="inlineStr">
         <is>
-          <t>Lotnummer</t>
+          <t xml:space="preserve">Lot Number</t>
         </is>
       </c>
       <c r="M90" s="1080" t="n"/>
@@ -13248,7 +13248,7 @@
     <row r="101" ht="18.75" customFormat="1" customHeight="1" s="1310">
       <c r="A101" s="1330" t="inlineStr">
         <is>
-          <t>Revisie nummer</t>
+          <t xml:space="preserve">Revision Number</t>
         </is>
       </c>
       <c r="B101" s="1114" t="n"/>
@@ -13275,14 +13275,14 @@
     <row r="102" ht="15" customFormat="1" customHeight="1" s="1331">
       <c r="A102" s="1298" t="inlineStr">
         <is>
-          <t>Revisie nummer</t>
+          <t xml:space="preserve">Revision Number</t>
         </is>
       </c>
       <c r="B102" s="1114" t="n"/>
       <c r="C102" s="1115" t="n"/>
       <c r="D102" s="1332" t="inlineStr">
         <is>
-          <t>Wijziging</t>
+          <t xml:space="preserve">Change</t>
         </is>
       </c>
       <c r="E102" s="1333" t="n"/>
@@ -13296,13 +13296,13 @@
       <c r="M102" s="1333" t="n"/>
       <c r="N102" s="1296" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="O102" s="1114" t="n"/>
       <c r="P102" s="1334" t="inlineStr">
         <is>
-          <t>Door</t>
+          <t xml:space="preserve">Initials</t>
         </is>
       </c>
       <c r="Q102" s="1138" t="n"/>
@@ -14072,13 +14072,13 @@
   <sheetData>
     <row r="1" ht="11.25" customHeight="1" s="1339">
       <c r="A1" s="1349">
-        <f>'Recept-voorblad'!Q1</f>
+        <f>'Recipe Sheet'!Q1</f>
         <v/>
       </c>
       <c r="B1" s="1083" t="n"/>
       <c r="C1" s="1350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brouw specificaties </t>
+          <t xml:space="preserve">Brewing Specifications</t>
         </is>
       </c>
       <c r="D1" s="1075" t="n"/>
@@ -14095,14 +14095,14 @@
       <c r="O1" s="1075" t="n"/>
       <c r="P1" s="1351" t="inlineStr">
         <is>
-          <t>Bier status</t>
+          <t xml:space="preserve">Beer Status</t>
         </is>
       </c>
       <c r="Q1" s="1315" t="n"/>
       <c r="R1" s="1316" t="n"/>
       <c r="S1" s="1352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invullen op de brouwdag </t>
+          <t xml:space="preserve">Brewing data</t>
         </is>
       </c>
       <c r="T1" s="1106" t="n"/>
@@ -14140,7 +14140,7 @@
       <c r="N2" s="1080" t="n"/>
       <c r="O2" s="1080" t="n"/>
       <c r="P2" s="1353">
-        <f>'Recept-voorblad'!N23</f>
+        <f>'Recipe Sheet'!N23</f>
         <v/>
       </c>
       <c r="Q2" s="1315" t="n"/>
@@ -14169,11 +14169,11 @@
       <c r="B3" s="1083" t="n"/>
       <c r="C3" s="1354" t="inlineStr">
         <is>
-          <t>Naam bier</t>
+          <t xml:space="preserve">Beer Name</t>
         </is>
       </c>
       <c r="E3" s="1355">
-        <f>'Recept-voorblad'!C3</f>
+        <f>'Recipe Sheet'!C3</f>
         <v/>
       </c>
       <c r="F3" s="1075" t="n"/>
@@ -14183,18 +14183,18 @@
       <c r="J3" s="1076" t="n"/>
       <c r="K3" s="1356" t="inlineStr">
         <is>
-          <t>Batchnummer</t>
+          <t xml:space="preserve">Batch No.</t>
         </is>
       </c>
       <c r="M3" s="1083" t="n"/>
       <c r="N3" s="1357">
-        <f>'Recept-voorblad'!K3</f>
+        <f>'Recipe Sheet'!K3</f>
         <v/>
       </c>
       <c r="O3" s="1083" t="n"/>
       <c r="P3" s="1358" t="inlineStr">
         <is>
-          <t>Brouwsel nr,</t>
+          <t xml:space="preserve">Brew Number</t>
         </is>
       </c>
       <c r="Q3" s="1093" t="n"/>
@@ -14254,7 +14254,7 @@
       <c r="O4" s="1081" t="n"/>
       <c r="P4" s="1360" t="inlineStr">
         <is>
-          <t>Order nr, Software</t>
+          <t xml:space="preserve">Order No. Software</t>
         </is>
       </c>
       <c r="Q4" s="1106" t="n"/>
@@ -14283,11 +14283,11 @@
       <c r="B5" s="1083" t="n"/>
       <c r="C5" s="1354" t="inlineStr">
         <is>
-          <t>Bier stijl</t>
+          <t xml:space="preserve">Beer Style</t>
         </is>
       </c>
       <c r="E5" s="1364">
-        <f>'Recept-voorblad'!C7</f>
+        <f>'Recipe Sheet'!C7</f>
         <v/>
       </c>
       <c r="F5" s="1083" t="n"/>
@@ -14301,7 +14301,7 @@
       <c r="J5" s="1087" t="n"/>
       <c r="K5" s="1367" t="inlineStr">
         <is>
-          <t>Datum 1e brouwsel</t>
+          <t xml:space="preserve">Date Of 1st Brew</t>
         </is>
       </c>
       <c r="L5" s="1075" t="n"/>
@@ -14310,7 +14310,7 @@
       <c r="O5" s="1107" t="n"/>
       <c r="P5" s="1369" t="inlineStr">
         <is>
-          <t>Naam brouwer</t>
+          <t xml:space="preserve">Brewer</t>
         </is>
       </c>
       <c r="Q5" s="1078" t="n"/>
@@ -14352,7 +14352,7 @@
       <c r="O6" s="1094" t="n"/>
       <c r="P6" s="1374" t="inlineStr">
         <is>
-          <t>Start inmaischen (dd-mm uu:mm)</t>
+          <t xml:space="preserve">Start Mash-in (dd-mm hh:mm)</t>
         </is>
       </c>
       <c r="Q6" s="1078" t="n"/>
@@ -14379,7 +14379,7 @@
     <row r="7" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A7" s="1377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brouw specificaties </t>
+          <t xml:space="preserve">Brewing Specifications</t>
         </is>
       </c>
       <c r="B7" s="1080" t="n"/>
@@ -14391,7 +14391,7 @@
       <c r="H7" s="1081" t="n"/>
       <c r="I7" s="1378" t="inlineStr">
         <is>
-          <t>Recept specificaties</t>
+          <t xml:space="preserve">Recipe Specifications</t>
         </is>
       </c>
       <c r="J7" s="1114" t="n"/>
@@ -14402,7 +14402,7 @@
       <c r="O7" s="1115" t="n"/>
       <c r="P7" s="1379" t="inlineStr">
         <is>
-          <t>Maischen</t>
+          <t xml:space="preserve">Mashing</t>
         </is>
       </c>
       <c r="Q7" s="1315" t="n"/>
@@ -14429,7 +14429,7 @@
     </row>
     <row r="8" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A8" s="1383">
-        <f>IF(LEFT(A1,2)="WP", "Totaal volume batch","Recept nummer braukon")</f>
+        <f>IF(LEFT(A1,2)="WP", "Total Volume Of Batch","Recipe Number Braukon")</f>
         <v/>
       </c>
       <c r="B8" s="1075" t="n"/>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="I8" s="1386" t="inlineStr">
         <is>
-          <t>Gewenste stamwort</t>
+          <t xml:space="preserve">Target Original Extract</t>
         </is>
       </c>
       <c r="J8" s="1075" t="n"/>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="P8" s="1389" t="inlineStr">
         <is>
-          <t>Maisch water</t>
+          <t xml:space="preserve">Mash Water</t>
         </is>
       </c>
       <c r="Q8" s="1106" t="n"/>
@@ -14523,7 +14523,7 @@
     <row r="9" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A9" s="1393" t="inlineStr">
         <is>
-          <t>Receptnaam Software</t>
+          <t xml:space="preserve">Recipe Name Software</t>
         </is>
       </c>
       <c r="E9" s="1083" t="n"/>
@@ -14532,12 +14532,12 @@
       <c r="H9" s="1178" t="n"/>
       <c r="I9" s="1395" t="inlineStr">
         <is>
-          <t>Gewenste eind plato</t>
+          <t xml:space="preserve">Target Final Extract</t>
         </is>
       </c>
       <c r="M9" s="1083" t="n"/>
       <c r="N9" s="1396">
-        <f>'Recept-voorblad'!F13</f>
+        <f>'Recipe Sheet'!F13</f>
         <v/>
       </c>
       <c r="O9" s="1397" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="P9" s="1398" t="inlineStr">
         <is>
-          <t>pH na inmaischen</t>
+          <t xml:space="preserve">pH After Mash-in</t>
         </is>
       </c>
       <c r="Q9" s="1078" t="n"/>
@@ -14574,7 +14574,7 @@
     </row>
     <row r="10" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A10" s="1401">
-        <f>IF(LEFT(A1,2)="WP", "Stort special bin kg","Maischwater")</f>
+        <f>IF(LEFT(A1,2)="WP", "Special Bin Total kg","Mash Water")</f>
         <v/>
       </c>
       <c r="E10" s="1083" t="n"/>
@@ -14585,7 +14585,7 @@
         <v/>
       </c>
       <c r="I10" s="1395">
-        <f>IF(LEFT(A1,2)="WP", "Maischwater"," ")</f>
+        <f>IF(LEFT(A1,2)="WP", "Mash Water"," ")</f>
         <v/>
       </c>
       <c r="M10" s="1083" t="n"/>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="P10" s="1405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correctie zuur </t>
+          <t xml:space="preserve">Acid For Correction</t>
         </is>
       </c>
       <c r="Q10" s="1078" t="n"/>
@@ -14650,7 +14650,7 @@
     </row>
     <row r="11" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A11" s="1401">
-        <f>IF(LEFT(A1,2)="WP", "Naam special bin storting"," ")</f>
+        <f>IF(LEFT(A1,2)="WP", "Special Bin Recipe Name"," ")</f>
         <v/>
       </c>
       <c r="E11" s="1083" t="n"/>
@@ -14659,7 +14659,7 @@
       <c r="H11" s="1178" t="n"/>
       <c r="I11" s="1395" t="inlineStr">
         <is>
-          <t>pH Maische</t>
+          <t xml:space="preserve">Mash pH</t>
         </is>
       </c>
       <c r="M11" s="1083" t="n"/>
@@ -14667,7 +14667,7 @@
       <c r="O11" s="1178" t="n"/>
       <c r="P11" s="1398" t="inlineStr">
         <is>
-          <t>pH na correctie</t>
+          <t xml:space="preserve">pH After Correction</t>
         </is>
       </c>
       <c r="Q11" s="1078" t="n"/>
@@ -14695,19 +14695,19 @@
     <row r="12" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A12" s="1393" t="inlineStr">
         <is>
-          <t>Beslag dikte</t>
+          <t xml:space="preserve">Grist:Water Ratio (kg:L)</t>
         </is>
       </c>
       <c r="E12" s="1083" t="n"/>
       <c r="F12" s="1414">
-        <f>"1 :"&amp;ROUNDUP(IF(LEFT(A1,2)="WP",(N10*100)/'Recept-voorblad'!D40,(F10*100)/'Recept-voorblad'!D40),2)</f>
+        <f>"1 :"&amp;ROUNDUP(IF(LEFT(A1,2)="WP",(N10*100)/'Recipe Sheet'!D40,(F10*100)/'Recipe Sheet'!D40),2)</f>
         <v/>
       </c>
       <c r="G12" s="1177" t="n"/>
       <c r="H12" s="1178" t="n"/>
       <c r="I12" s="1395" t="inlineStr">
         <is>
-          <t>pH Start koken</t>
+          <t xml:space="preserve">pH Start Boil</t>
         </is>
       </c>
       <c r="M12" s="1083" t="n"/>
@@ -14715,7 +14715,7 @@
       <c r="O12" s="1178" t="n"/>
       <c r="P12" s="1398" t="inlineStr">
         <is>
-          <t>Joodnormaal test OK?</t>
+          <t xml:space="preserve">Iodine Test OK?</t>
         </is>
       </c>
       <c r="Q12" s="1078" t="n"/>
@@ -14742,7 +14742,7 @@
     </row>
     <row r="13" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A13" s="1393">
-        <f>IF(LEFT(A1,2)="WP", "Cumm. Corp./sparging vol."," ")</f>
+        <f>IF(LEFT(A1,2)="WP", "Cum. Sparge Vol."," ")</f>
         <v/>
       </c>
       <c r="E13" s="1083" t="n"/>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="I13" s="1395" t="inlineStr">
         <is>
-          <t>pH Eind Koken</t>
+          <t xml:space="preserve">pH End Boil</t>
         </is>
       </c>
       <c r="M13" s="1083" t="n"/>
@@ -14762,7 +14762,7 @@
       <c r="O13" s="1178" t="n"/>
       <c r="P13" s="1417" t="inlineStr">
         <is>
-          <t>Afwijking maische schema?</t>
+          <t xml:space="preserve">Mash Schedule Deviation?</t>
         </is>
       </c>
       <c r="Q13" s="1078" t="n"/>
@@ -14790,12 +14790,12 @@
     <row r="14" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A14" s="1393" t="inlineStr">
         <is>
-          <t>Brouwsel (hl)</t>
+          <t xml:space="preserve">Brew Size (hl)</t>
         </is>
       </c>
       <c r="E14" s="1083" t="n"/>
       <c r="F14" s="1419">
-        <f>'Recept-voorblad'!C9</f>
+        <f>'Recipe Sheet'!C9</f>
         <v/>
       </c>
       <c r="G14" s="1177" t="n"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="I14" s="1395" t="inlineStr">
         <is>
-          <t>Beluchting</t>
+          <t xml:space="preserve">Aeration</t>
         </is>
       </c>
       <c r="M14" s="1083" t="n"/>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="P14" s="1421" t="inlineStr">
         <is>
-          <t>Spoelwater</t>
+          <t xml:space="preserve">Rinse Water Mash Tun</t>
         </is>
       </c>
       <c r="Q14" s="1093" t="n"/>
@@ -14881,7 +14881,7 @@
     <row r="15" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A15" s="1424" t="inlineStr">
         <is>
-          <t>Verwacht extract begin kook</t>
+          <t xml:space="preserve">Target Pre-Boil Extract</t>
         </is>
       </c>
       <c r="B15" s="1425" t="n"/>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="I15" s="1427" t="inlineStr">
         <is>
-          <t>Wort naar gisttank Temp</t>
+          <t xml:space="preserve">Target Temp Cooled Wort To GLT</t>
         </is>
       </c>
       <c r="J15" s="1080" t="n"/>
@@ -14905,7 +14905,7 @@
       <c r="L15" s="1080" t="n"/>
       <c r="M15" s="1081" t="n"/>
       <c r="N15" s="1428">
-        <f>'Recept-voorblad'!F21</f>
+        <f>'Recipe Sheet'!F21</f>
         <v/>
       </c>
       <c r="O15" s="1429" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="P15" s="1379" t="inlineStr">
         <is>
-          <t>Filtratie &amp; voorloopvat</t>
+          <t xml:space="preserve">Filtration &amp; VLT</t>
         </is>
       </c>
       <c r="Q15" s="1315" t="n"/>
@@ -14943,7 +14943,7 @@
     <row r="16" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A16" s="1433" t="inlineStr">
         <is>
-          <t>Volume kook</t>
+          <t xml:space="preserve">Pre-Boil Volume</t>
         </is>
       </c>
       <c r="B16" s="1434" t="n"/>
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="I16" s="1367">
-        <f>IF(LEFT(A1,2)="WP", "Sparging instellingen","Filtratie volumes")</f>
+        <f>IF(LEFT(A1,2)="WP", "Sparge Flow Settings Brewmaxx","Filtration Volumes")</f>
         <v/>
       </c>
       <c r="J16" s="1114" t="n"/>
@@ -14969,7 +14969,7 @@
       <c r="O16" s="1115" t="n"/>
       <c r="P16" s="1360" t="inlineStr">
         <is>
-          <t>Plato 1e wortvolume</t>
+          <t xml:space="preserve">Plato First Runnings</t>
         </is>
       </c>
       <c r="Q16" s="1106" t="n"/>
@@ -15033,7 +15033,7 @@
     <row r="17" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A17" s="1433" t="inlineStr">
         <is>
-          <t>Wortvoorkoeler temp</t>
+          <t xml:space="preserve">Wort Pre-Cooler Setpoint</t>
         </is>
       </c>
       <c r="B17" s="1434" t="n"/>
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="I17" s="1383">
-        <f>IF(LEFT(A1,2)="WP", "sparging 1e","1e afloop")</f>
+        <f>IF(LEFT(A1,2)="WP", "Sparge 1st","First Runnings")</f>
         <v/>
       </c>
       <c r="J17" s="1075" t="n"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="P17" s="1369" t="inlineStr">
         <is>
-          <t>Extract laatste afloop</t>
+          <t xml:space="preserve">Extract Last Runnings</t>
         </is>
       </c>
       <c r="Q17" s="1078" t="n"/>
@@ -15125,7 +15125,7 @@
     </row>
     <row r="18" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A18" s="1424">
-        <f>IF(LEFT(A1,2)="WP", "Volume water aditie terug koeling","Totaal volume brouwsel ")</f>
+        <f>IF(LEFT(A1,2)="WP", "Water Addition To GLT","Total Brew Volume")</f>
         <v/>
       </c>
       <c r="B18" s="1425" t="n"/>
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="I18" s="1401">
-        <f>IF(LEFT(A1,2)="WP", "sparging 2e","Spoelwater")</f>
+        <f>IF(LEFT(A1,2)="WP", "Sparge 2nd","Sparge Water")</f>
         <v/>
       </c>
       <c r="M18" s="1083" t="n"/>
@@ -15151,7 +15151,7 @@
       </c>
       <c r="P18" s="1369" t="inlineStr">
         <is>
-          <t>Eerste afloop</t>
+          <t xml:space="preserve">First Runnings Volume</t>
         </is>
       </c>
       <c r="Q18" s="1078" t="n"/>
@@ -15214,7 +15214,7 @@
     </row>
     <row r="19" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A19" s="1433">
-        <f>IF(LEFT(A1,2)="WP", "Eindvolume brouwsel","Eindvolume in CKT")</f>
+        <f>IF(LEFT(A1,2)="WP", "Cooled Volume To GLT","Final Volume In CKT")</f>
         <v/>
       </c>
       <c r="B19" s="1434" t="n"/>
@@ -15222,7 +15222,7 @@
       <c r="D19" s="1434" t="n"/>
       <c r="E19" s="1435" t="n"/>
       <c r="F19" s="1419">
-        <f>IF(LEFT(A1,2)="WP", 'Recept-voorblad'!C9,'Recept-voorblad'!C9*'Recept-voorblad'!G7)</f>
+        <f>IF(LEFT(A1,2)="WP", 'Recipe Sheet'!C9,'Recipe Sheet'!C9*'Recipe Sheet'!G7)</f>
         <v/>
       </c>
       <c r="G19" s="1177" t="n"/>
@@ -15232,7 +15232,7 @@
         </is>
       </c>
       <c r="I19" s="1401">
-        <f>IF(LEFT(A1,2)="WP", "sparging 3e","Spoel afloop")</f>
+        <f>IF(LEFT(A1,2)="WP", "Sparge 3rd","Sparge Runnings")</f>
         <v/>
       </c>
       <c r="M19" s="1083" t="n"/>
@@ -15242,7 +15242,7 @@
         <v/>
       </c>
       <c r="P19" s="1369">
-        <f>IF(LEFT(A1,2)="WP", "Cumm, Sparging vol,","spoelwater")</f>
+        <f>IF(LEFT(A1,2)="WP", "Cum. Sparge Vol.","Sparge Water")</f>
         <v/>
       </c>
       <c r="Q19" s="1078" t="n"/>
@@ -15306,7 +15306,7 @@
     <row r="20" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A20" s="1424" t="inlineStr">
         <is>
-          <t>Gewenste verdamping</t>
+          <t xml:space="preserve">Target Evaporation</t>
         </is>
       </c>
       <c r="B20" s="1425" t="n"/>
@@ -15321,7 +15321,7 @@
         </is>
       </c>
       <c r="I20" s="1401">
-        <f>IF(LEFT(A1,2)="WP", "sparging 4e","Totaal gefiltreerd volume")</f>
+        <f>IF(LEFT(A1,2)="WP", "Sparge 4th","Total Lautered Volume")</f>
         <v/>
       </c>
       <c r="M20" s="1083" t="n"/>
@@ -15331,7 +15331,7 @@
         <v/>
       </c>
       <c r="P20" s="1369">
-        <f>IF(LEFT(A1,2)="WP", "Last run pH","Spoelafloop")</f>
+        <f>IF(LEFT(A1,2)="WP", "Last Runnings pH","Sparge Runnings")</f>
         <v/>
       </c>
       <c r="Q20" s="1446" t="n"/>
@@ -15359,7 +15359,7 @@
     <row r="21" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A21" s="1424" t="inlineStr">
         <is>
-          <t>Intensiteit koken</t>
+          <t xml:space="preserve">Boil Intensity</t>
         </is>
       </c>
       <c r="B21" s="1425" t="n"/>
@@ -15374,7 +15374,7 @@
         </is>
       </c>
       <c r="I21" s="1450">
-        <f>IF(LEFT(A1,2)="WP", "Aantal kamers Mash Filter","Lauterfactor")</f>
+        <f>IF(LEFT(A1,2)="WP", "Number Of Mashfilter Chambers","Lauter Factor")</f>
         <v/>
       </c>
       <c r="J21" s="1114" t="n"/>
@@ -15385,7 +15385,7 @@
       <c r="O21" s="1115" t="n"/>
       <c r="P21" s="1451" t="inlineStr">
         <is>
-          <t>Filtratie tijd</t>
+          <t xml:space="preserve">Filtration Time</t>
         </is>
       </c>
       <c r="Q21" s="1093" t="n"/>
@@ -15449,7 +15449,7 @@
     <row r="22" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A22" s="1455" t="inlineStr">
         <is>
-          <t>Whirlpool rust</t>
+          <t xml:space="preserve">Whirlpool Rest</t>
         </is>
       </c>
       <c r="B22" s="1455" t="n"/>
@@ -15471,7 +15471,7 @@
       <c r="O22" s="1115" t="n"/>
       <c r="P22" s="1460" t="inlineStr">
         <is>
-          <t>Koken</t>
+          <t xml:space="preserve">Boiling</t>
         </is>
       </c>
       <c r="Q22" s="1315" t="n"/>
@@ -15499,7 +15499,7 @@
     <row r="23" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A23" s="1450" t="inlineStr">
         <is>
-          <t>Maisch schema</t>
+          <t xml:space="preserve">Mash Schedule</t>
         </is>
       </c>
       <c r="B23" s="1114" t="n"/>
@@ -15510,7 +15510,7 @@
       <c r="G23" s="1114" t="n"/>
       <c r="H23" s="1115" t="n"/>
       <c r="I23" s="1450">
-        <f>IF(LEFT(A1,2)="WP", "Toevoegingen:","Extra toevoegingen")</f>
+        <f>IF(LEFT(A1,2)="WP", "Brewing Additions:","Extra Additions")</f>
         <v/>
       </c>
       <c r="J23" s="1114" t="n"/>
@@ -15521,7 +15521,7 @@
       <c r="O23" s="1115" t="n"/>
       <c r="P23" s="1360" t="inlineStr">
         <is>
-          <t>pH begin kook</t>
+          <t xml:space="preserve">pH Start Boil</t>
         </is>
       </c>
       <c r="Q23" s="1106" t="n"/>
@@ -15549,7 +15549,7 @@
     <row r="24" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A24" s="1466" t="inlineStr">
         <is>
-          <t>Inmaischen</t>
+          <t xml:space="preserve">Mash-in</t>
         </is>
       </c>
       <c r="C24" s="1467" t="n"/>
@@ -15562,32 +15562,32 @@
       <c r="F24" s="1469" t="n"/>
       <c r="G24" s="1341" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="H24" s="1470" t="n"/>
       <c r="I24" s="1459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toevoegingen </t>
+          <t xml:space="preserve">Addition Type </t>
         </is>
       </c>
       <c r="J24" s="1114" t="n"/>
       <c r="K24" s="1115" t="n"/>
       <c r="L24" s="1471" t="inlineStr">
         <is>
-          <t>Hoeveelheid</t>
+          <t xml:space="preserve">Amount</t>
         </is>
       </c>
       <c r="M24" s="1115" t="n"/>
       <c r="N24" s="1471" t="inlineStr">
         <is>
-          <t>Moment</t>
+          <t xml:space="preserve">Timing</t>
         </is>
       </c>
       <c r="O24" s="1115" t="n"/>
       <c r="P24" s="1446" t="inlineStr">
         <is>
-          <t>Extract begin kook</t>
+          <t xml:space="preserve">Extract Start Boil</t>
         </is>
       </c>
       <c r="Q24" s="1078" t="n"/>
@@ -15654,7 +15654,7 @@
     <row r="25" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A25" s="1475" t="inlineStr">
         <is>
-          <t>Verhogen naar</t>
+          <t xml:space="preserve">Raise To</t>
         </is>
       </c>
       <c r="C25" s="1476" t="n"/>
@@ -15667,28 +15667,28 @@
       <c r="F25" s="1478" t="n"/>
       <c r="G25" s="1341" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="I25" s="1479">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A75="","",'Recept-voorblad'!A75),IF('Recept-voorblad'!A91="-","-",IF('Recept-voorblad'!A91="Revisie nummer","",'Recept-voorblad'!A91)))</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A75="","",'Recipe Sheet'!A75),IF('Recipe Sheet'!A91="-","-",IF('Recipe Sheet'!A91="Revision Number","",'Recipe Sheet'!A91)))</f>
         <v/>
       </c>
       <c r="J25" s="1223" t="n"/>
       <c r="K25" s="1224" t="n"/>
       <c r="L25" s="1480">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E75="","",'Recept-voorblad'!E75),IF('Recept-voorblad'!E91="","",'Recept-voorblad'!E91))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E75="","",'Recipe Sheet'!E75),IF('Recipe Sheet'!E91="","",'Recipe Sheet'!E91))</f>
         <v/>
       </c>
       <c r="M25" s="1481" t="n"/>
       <c r="N25" s="1482">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I75="","",'Recept-voorblad'!I75),IF('Recept-voorblad'!I91="","",'Recept-voorblad'!I91))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I75="","",'Recipe Sheet'!I75),IF('Recipe Sheet'!I91="","",'Recipe Sheet'!I91))</f>
         <v/>
       </c>
       <c r="O25" s="1481" t="n"/>
       <c r="P25" s="1446" t="inlineStr">
         <is>
-          <t>V begin kook (80°C)</t>
+          <t xml:space="preserve">Volume Start Boil (80°C)</t>
         </is>
       </c>
       <c r="Q25" s="1078" t="n"/>
@@ -15755,7 +15755,7 @@
     <row r="26" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A26" s="1475" t="inlineStr">
         <is>
-          <t>Verhogen naar</t>
+          <t xml:space="preserve">Raise To</t>
         </is>
       </c>
       <c r="B26" s="1341" t="n"/>
@@ -15769,75 +15769,75 @@
       <c r="F26" s="1478" t="n"/>
       <c r="G26" s="1341" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="I26" s="1486">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A76="","",'Recept-voorblad'!A76),IF('Recept-voorblad'!A92="-","-",IF('Recept-voorblad'!A92="Revisie nummer","",'Recept-voorblad'!A92)))</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A76="","",'Recipe Sheet'!A76),IF('Recipe Sheet'!A92="-","-",IF('Recipe Sheet'!A92="Revision Number","",'Recipe Sheet'!A92)))</f>
         <v/>
       </c>
       <c r="J26" s="1177" t="n"/>
       <c r="K26" s="1178" t="n"/>
       <c r="L26" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E76="","",'Recept-voorblad'!E76),IF('Recept-voorblad'!E92="","",'Recept-voorblad'!E92))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E76="","",'Recipe Sheet'!E76),IF('Recipe Sheet'!E92="","",'Recipe Sheet'!E92))</f>
         <v/>
       </c>
       <c r="M26" s="1488" t="n"/>
       <c r="N26" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I76="","",'Recept-voorblad'!I76),IF('Recept-voorblad'!I92="","",'Recept-voorblad'!I92))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I76="","",'Recipe Sheet'!I76),IF('Recipe Sheet'!I92="","",'Recipe Sheet'!I92))</f>
         <v/>
       </c>
       <c r="O26" s="1488" t="n"/>
       <c r="P26" s="1446" t="inlineStr">
         <is>
-          <t>Zuurcorrectie</t>
+          <t xml:space="preserve">Acid Correction</t>
         </is>
       </c>
       <c r="Q26" s="1078" t="n"/>
       <c r="R26" s="1078" t="n"/>
       <c r="S26" s="1443" t="n"/>
       <c r="T26" s="1490">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="U26" s="1443" t="n"/>
       <c r="V26" s="1491">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="W26" s="1443" t="n"/>
       <c r="X26" s="1492">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="Y26" s="1443" t="n"/>
       <c r="Z26" s="1493">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AA26" s="1443" t="n"/>
       <c r="AB26" s="1494">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AC26" s="1443" t="n"/>
       <c r="AD26" s="1494">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AE26" s="1443" t="n"/>
       <c r="AF26" s="1494">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AG26" s="1443" t="n"/>
       <c r="AH26" s="1494">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AI26" s="1443" t="n"/>
       <c r="AJ26" s="1494">
-        <f>IF(LEFT(A1,2)="WP", "liter","milliliter")</f>
+        <f>IF(LEFT(A1,2)="WP", "liter","ml")</f>
         <v/>
       </c>
       <c r="AK26" s="1340" t="n"/>
@@ -15845,7 +15845,7 @@
     <row r="27" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A27" s="1475" t="inlineStr">
         <is>
-          <t>Verhogen naar</t>
+          <t xml:space="preserve">Raise To</t>
         </is>
       </c>
       <c r="B27" s="1341" t="n"/>
@@ -15859,28 +15859,28 @@
       <c r="F27" s="1478" t="n"/>
       <c r="G27" s="1341" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="I27" s="1486">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A77="","",'Recept-voorblad'!A77),IF('Recept-voorblad'!A93="-","-",IF('Recept-voorblad'!A93="Revisie nummer","",'Recept-voorblad'!A93)))</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A77="","",'Recipe Sheet'!A77),IF('Recipe Sheet'!A93="-","-",IF('Recipe Sheet'!A93="Revision Number","",'Recipe Sheet'!A93)))</f>
         <v/>
       </c>
       <c r="J27" s="1177" t="n"/>
       <c r="K27" s="1178" t="n"/>
       <c r="L27" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E77="","",'Recept-voorblad'!E77),IF('Recept-voorblad'!E93="","",'Recept-voorblad'!E93))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E77="","",'Recipe Sheet'!E77),IF('Recipe Sheet'!E93="","",'Recipe Sheet'!E93))</f>
         <v/>
       </c>
       <c r="M27" s="1488" t="n"/>
       <c r="N27" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I77="","",'Recept-voorblad'!I77),IF('Recept-voorblad'!I93="","",'Recept-voorblad'!I93))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I77="","",'Recipe Sheet'!I77),IF('Recipe Sheet'!I93="","",'Recipe Sheet'!I93))</f>
         <v/>
       </c>
       <c r="O27" s="1488" t="n"/>
       <c r="P27" s="1495" t="inlineStr">
         <is>
-          <t>pH na zuurcorrectie / tijd</t>
+          <t xml:space="preserve">pH After Acid Correction / Time</t>
         </is>
       </c>
       <c r="Q27" s="1078" t="n"/>
@@ -15908,7 +15908,7 @@
     <row r="28" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A28" s="1475" t="inlineStr">
         <is>
-          <t>Verhogen naar</t>
+          <t xml:space="preserve">Raise To</t>
         </is>
       </c>
       <c r="C28" s="1476" t="n"/>
@@ -15921,28 +15921,28 @@
       <c r="F28" s="1478" t="n"/>
       <c r="G28" s="1341" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="I28" s="1486">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A78="","",'Recept-voorblad'!A78),IF('Recept-voorblad'!A94="-","-",IF('Recept-voorblad'!A94="Revisie nummer","",'Recept-voorblad'!A94)))</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A78="","",'Recipe Sheet'!A78),IF('Recipe Sheet'!A94="-","-",IF('Recipe Sheet'!A94="Revision Number","",'Recipe Sheet'!A94)))</f>
         <v/>
       </c>
       <c r="J28" s="1177" t="n"/>
       <c r="K28" s="1178" t="n"/>
       <c r="L28" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E78="","",'Recept-voorblad'!E78),IF('Recept-voorblad'!E94="","",'Recept-voorblad'!E94))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E78="","",'Recipe Sheet'!E78),IF('Recipe Sheet'!E94="","",'Recipe Sheet'!E94))</f>
         <v/>
       </c>
       <c r="M28" s="1488" t="n"/>
       <c r="N28" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I78="","",'Recept-voorblad'!I78),IF('Recept-voorblad'!I94="","",'Recept-voorblad'!I94))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I78="","",'Recipe Sheet'!I78),IF('Recipe Sheet'!I94="","",'Recipe Sheet'!I94))</f>
         <v/>
       </c>
       <c r="O28" s="1488" t="n"/>
       <c r="P28" s="1446" t="inlineStr">
         <is>
-          <t>Totale kooktijd</t>
+          <t xml:space="preserve">Total Boil Time</t>
         </is>
       </c>
       <c r="Q28" s="1078" t="n"/>
@@ -16006,7 +16006,7 @@
     <row r="29" ht="13.5" customFormat="1" customHeight="1" s="1099">
       <c r="A29" s="1098" t="inlineStr">
         <is>
-          <t>Uitmaischen op</t>
+          <t xml:space="preserve">Mash-out At</t>
         </is>
       </c>
       <c r="C29" s="1506" t="n"/>
@@ -16019,28 +16019,28 @@
       <c r="F29" s="1509" t="n"/>
       <c r="G29" s="1099" t="inlineStr">
         <is>
-          <t>Minuten rust</t>
+          <t xml:space="preserve">Rest (min)</t>
         </is>
       </c>
       <c r="I29" s="1486">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A79="","",'Recept-voorblad'!A79),IF('Recept-voorblad'!A95="-","-",IF('Recept-voorblad'!A95="Revisie nummer","",'Recept-voorblad'!A95)))</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A79="","",'Recipe Sheet'!A79),IF('Recipe Sheet'!A95="-","-",IF('Recipe Sheet'!A95="Revision Number","",'Recipe Sheet'!A95)))</f>
         <v/>
       </c>
       <c r="J29" s="1177" t="n"/>
       <c r="K29" s="1178" t="n"/>
       <c r="L29" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E79="","",'Recept-voorblad'!E79),IF('Recept-voorblad'!E95="","",'Recept-voorblad'!E95))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E79="","",'Recipe Sheet'!E79),IF('Recipe Sheet'!E95="","",'Recipe Sheet'!E95))</f>
         <v/>
       </c>
       <c r="M29" s="1488" t="n"/>
       <c r="N29" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I79="","",'Recept-voorblad'!I79),IF('Recept-voorblad'!I95="","",'Recept-voorblad'!I95))</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I79="","",'Recipe Sheet'!I79),IF('Recipe Sheet'!I95="","",'Recipe Sheet'!I95))</f>
         <v/>
       </c>
       <c r="O29" s="1488" t="n"/>
       <c r="P29" s="1369" t="inlineStr">
         <is>
-          <t>Verdamping</t>
+          <t xml:space="preserve">Evaporation Rate</t>
         </is>
       </c>
       <c r="Q29" s="1078" t="n"/>
@@ -16138,24 +16138,24 @@
       <c r="G30" s="1089" t="n"/>
       <c r="H30" s="1090" t="n"/>
       <c r="I30" s="1513">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A80="","",'Recept-voorblad'!A80),"-")</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A80="","",'Recipe Sheet'!A80),"-")</f>
         <v/>
       </c>
       <c r="J30" s="1177" t="n"/>
       <c r="K30" s="1178" t="n"/>
       <c r="L30" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E80="","",'Recept-voorblad'!E80),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E80="","",'Recipe Sheet'!E80),"-")</f>
         <v/>
       </c>
       <c r="M30" s="1488" t="n"/>
       <c r="N30" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I80="","",'Recept-voorblad'!I80),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I80="","",'Recipe Sheet'!I80),"-")</f>
         <v/>
       </c>
       <c r="O30" s="1488" t="n"/>
       <c r="P30" s="1446" t="inlineStr">
         <is>
-          <t>Extra toevoeging</t>
+          <t xml:space="preserve">Extra Additions</t>
         </is>
       </c>
       <c r="Q30" s="1078" t="n"/>
@@ -16187,24 +16187,24 @@
       <c r="F31" s="1521" t="n"/>
       <c r="H31" s="1100" t="n"/>
       <c r="I31" s="1513">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A81="","",'Recept-voorblad'!A81),"-")</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A81="","",'Recipe Sheet'!A81),"-")</f>
         <v/>
       </c>
       <c r="J31" s="1177" t="n"/>
       <c r="K31" s="1178" t="n"/>
       <c r="L31" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E81="","",'Recept-voorblad'!E81),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E81="","",'Recipe Sheet'!E81),"-")</f>
         <v/>
       </c>
       <c r="M31" s="1488" t="n"/>
       <c r="N31" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I81="","",'Recept-voorblad'!I81),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I81="","",'Recipe Sheet'!I81),"-")</f>
         <v/>
       </c>
       <c r="O31" s="1488" t="n"/>
       <c r="P31" s="1358" t="inlineStr">
         <is>
-          <t>Extract einde kook</t>
+          <t xml:space="preserve">Extract End Of Boil</t>
         </is>
       </c>
       <c r="Q31" s="1093" t="n"/>
@@ -16272,24 +16272,24 @@
       <c r="F32" s="1521" t="n"/>
       <c r="H32" s="1100" t="n"/>
       <c r="I32" s="1513">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A82="","",'Recept-voorblad'!A82),"-")</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A82="","",'Recipe Sheet'!A82),"-")</f>
         <v/>
       </c>
       <c r="J32" s="1177" t="n"/>
       <c r="K32" s="1178" t="n"/>
       <c r="L32" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E82="","",'Recept-voorblad'!E82),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E82="","",'Recipe Sheet'!E82),"-")</f>
         <v/>
       </c>
       <c r="M32" s="1488" t="n"/>
       <c r="N32" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I82="","",'Recept-voorblad'!I82),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I82="","",'Recipe Sheet'!I82),"-")</f>
         <v/>
       </c>
       <c r="O32" s="1488" t="n"/>
       <c r="P32" s="1525" t="inlineStr">
         <is>
-          <t>Whirlpool/ Einde kook</t>
+          <t xml:space="preserve">Whirlpool / End Of Boil</t>
         </is>
       </c>
       <c r="Q32" s="1315" t="n"/>
@@ -16321,24 +16321,24 @@
       <c r="F33" s="1521" t="n"/>
       <c r="H33" s="1100" t="n"/>
       <c r="I33" s="1513">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A83="","",'Recept-voorblad'!A83),"-")</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A83="","",'Recipe Sheet'!A83),"-")</f>
         <v/>
       </c>
       <c r="J33" s="1177" t="n"/>
       <c r="K33" s="1178" t="n"/>
       <c r="L33" s="1487">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E83="","",'Recept-voorblad'!E83),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E83="","",'Recipe Sheet'!E83),"-")</f>
         <v/>
       </c>
       <c r="M33" s="1488" t="n"/>
       <c r="N33" s="1489">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I83="","",'Recept-voorblad'!I83),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I83="","",'Recipe Sheet'!I83),"-")</f>
         <v/>
       </c>
       <c r="O33" s="1488" t="n"/>
       <c r="P33" s="1526" t="inlineStr">
         <is>
-          <t>Volume whirlpool</t>
+          <t xml:space="preserve">Volume Whirlpool</t>
         </is>
       </c>
       <c r="Q33" s="1106" t="n"/>
@@ -16412,24 +16412,24 @@
       <c r="G34" s="1168" t="n"/>
       <c r="H34" s="1169" t="n"/>
       <c r="I34" s="1532">
-        <f>IF(LEFT(A1,2)="WP",IF('Recept-voorblad'!A84="","",'Recept-voorblad'!A84),"-")</f>
+        <f>IF(LEFT(A1,2)="WP",IF('Recipe Sheet'!A84="","",'Recipe Sheet'!A84),"-")</f>
         <v/>
       </c>
       <c r="J34" s="1507" t="n"/>
       <c r="K34" s="1533" t="n"/>
       <c r="L34" s="1534">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!E84="","",'Recept-voorblad'!E84),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!E84="","",'Recipe Sheet'!E84),"-")</f>
         <v/>
       </c>
       <c r="M34" s="1535" t="n"/>
       <c r="N34" s="1536">
-        <f>IF(LEFT($A$1,2)="WP",IF('Recept-voorblad'!I84="","",'Recept-voorblad'!I84),"-")</f>
+        <f>IF(LEFT($A$1,2)="WP",IF('Recipe Sheet'!I84="","",'Recipe Sheet'!I84),"-")</f>
         <v/>
       </c>
       <c r="O34" s="1535" t="n"/>
       <c r="P34" s="1446" t="inlineStr">
         <is>
-          <t>Extract</t>
+          <t xml:space="preserve">Extract Cooled Wort</t>
         </is>
       </c>
       <c r="Q34" s="1078" t="n"/>
@@ -16496,7 +16496,7 @@
     <row r="35" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A35" s="1539" t="inlineStr">
         <is>
-          <t>Hop dosering</t>
+          <t xml:space="preserve">Hop dosing</t>
         </is>
       </c>
       <c r="B35" s="1080" t="n"/>
@@ -16511,18 +16511,18 @@
         </is>
       </c>
       <c r="I35" s="1541">
-        <f>IF(LEFT(A1,2)="WP", "Automatische dosering:","receptuur additieven")</f>
+        <f>IF(LEFT(A1,2)="WP", "Automatic Dosing:","Recipe Additives")</f>
         <v/>
       </c>
       <c r="J35" s="1114" t="n"/>
       <c r="K35" s="1114" t="n"/>
       <c r="L35" s="1115" t="n"/>
       <c r="M35" s="1541">
-        <f>IF(LEFT(A1,2)="WP", "Zuur [L]","hoeveel&amp;wanneer")</f>
+        <f>IF(LEFT(A1,2)="WP", "Acid [L]","Amount &amp; Timing")</f>
         <v/>
       </c>
       <c r="N35" s="1541">
-        <f>IF(LEFT(A1,2)="WP", "Tannines [L]","paraaf")</f>
+        <f>IF(LEFT(A1,2)="WP", "Tannins [L]","Initials")</f>
         <v/>
       </c>
       <c r="O35" s="1115" t="n"/>
@@ -16556,12 +16556,12 @@
     <row r="36" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A36" s="1545" t="inlineStr">
         <is>
-          <t>Hopgift</t>
+          <t xml:space="preserve">Hop Addition</t>
         </is>
       </c>
       <c r="B36" s="1224" t="n"/>
       <c r="C36" s="1384">
-        <f>'Recept-voorblad'!G43</f>
+        <f>'Recipe Sheet'!G43</f>
         <v/>
       </c>
       <c r="D36" s="1469" t="inlineStr">
@@ -16570,17 +16570,17 @@
         </is>
       </c>
       <c r="E36" s="1546">
-        <f>IF(A36=" "," ", "doseerpunt")</f>
+        <f>IF(A36=" "," ", "Hop Doser / Method")</f>
         <v/>
       </c>
       <c r="F36" s="1223" t="n"/>
       <c r="G36" s="1224" t="n"/>
       <c r="H36" s="1478">
-        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recept-voorblad'!G42:Q56,MATCH(Brouwen!C36,'Recept-voorblad'!G42:G56,0),11),""),IF(IFERROR(1/INDEX('Recept-voorblad'!G42:Q56,MATCH(Brouwen!C36,'Recept-voorblad'!G42:G56,0),3),"nee")="nee",IF(Brouwen!C36="","","nee"),"ja"))</f>
+        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recipe Sheet'!G42:Q56,MATCH('Brew Sheet'!C36,'Recipe Sheet'!G42:G56,0),11),""),IF(IFERROR(1/INDEX('Recipe Sheet'!G42:Q56,MATCH('Brew Sheet'!C36,'Recipe Sheet'!G42:G56,0),3),"no")="no",IF('Brew Sheet'!C36="","","no"),"yes"))</f>
         <v/>
       </c>
       <c r="I36" s="1547">
-        <f>IF(LEFT(A1,2)="WP","Inmaischen",'Recept-voorblad'!A75)</f>
+        <f>IF(LEFT(A1,2)="WP","Mash-in",'Recipe Sheet'!A75)</f>
         <v/>
       </c>
       <c r="J36" s="1075" t="n"/>
@@ -16594,7 +16594,7 @@
       <c r="O36" s="1224" t="n"/>
       <c r="P36" s="1369" t="inlineStr">
         <is>
-          <t>Werkelijke rust tijd</t>
+          <t xml:space="preserve">Actual Rest Time</t>
         </is>
       </c>
       <c r="Q36" s="1078" t="n"/>
@@ -16657,12 +16657,12 @@
     </row>
     <row r="37" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A37" s="1557">
-        <f>IF(C37="-"," ","Hopgift")</f>
+        <f>IF(C37="-"," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B37" s="1178" t="n"/>
       <c r="C37" s="1402">
-        <f t="array" ref="C37:C37">IFERROR(INDEX('Recept-voorblad'!G43:G57,MATCH(FALSE(),'Recept-voorblad'!G43:G57= C36,0)),"")</f>
+        <f t="array" ref="C37:C37">IFERROR(INDEX('Recipe Sheet'!G43:G57,MATCH(FALSE(),'Recipe Sheet'!G43:G57= C36,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="1478">
@@ -16670,17 +16670,17 @@
         <v/>
       </c>
       <c r="E37" s="1558">
-        <f>IF(A37=" "," ", "doseerpunt")</f>
+        <f>IF(A37=" "," ", "Hop Doser / Method")</f>
         <v/>
       </c>
       <c r="F37" s="1177" t="n"/>
       <c r="G37" s="1178" t="n"/>
       <c r="H37" s="1478">
-        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recept-voorblad'!G43:Q57,MATCH(Brouwen!C37,'Recept-voorblad'!G43:G57,0),11),""),IF(IFERROR(1/INDEX('Recept-voorblad'!G43:Q57,MATCH(Brouwen!C37,'Recept-voorblad'!G43:G57,0),3),"nee")="nee",IF(Brouwen!C37="","","nee"),"ja"))</f>
+        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recipe Sheet'!G43:Q57,MATCH('Brew Sheet'!C37,'Recipe Sheet'!G43:G57,0),11),""),IF(IFERROR(1/INDEX('Recipe Sheet'!G43:Q57,MATCH('Brew Sheet'!C37,'Recipe Sheet'!G43:G57,0),3),"no")="no",IF('Brew Sheet'!C37="","","no"),"yes"))</f>
         <v/>
       </c>
       <c r="I37" s="1559">
-        <f>IF(LEFT(A1,2)="WP", "Koken",'Recept-voorblad'!A76)</f>
+        <f>IF(LEFT(A1,2)="WP", "Boil",'Recipe Sheet'!A76)</f>
         <v/>
       </c>
       <c r="L37" s="1560">
@@ -16692,7 +16692,7 @@
       <c r="O37" s="1178" t="n"/>
       <c r="P37" s="1369" t="inlineStr">
         <is>
-          <t>Beluchting</t>
+          <t xml:space="preserve">Aeration Rate</t>
         </is>
       </c>
       <c r="Q37" s="1078" t="n"/>
@@ -16746,12 +16746,12 @@
     </row>
     <row r="38" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A38" s="1557">
-        <f>IF(C38="-"," ","Hopgift")</f>
+        <f>IF(C38="-"," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B38" s="1178" t="n"/>
       <c r="C38" s="1567">
-        <f t="array" ref="C38:C38">IFERROR(INDEX('Recept-voorblad'!G43:G57,MATCH(1,('Recept-voorblad'!G43:G57&lt;C37)*('Recept-voorblad'!G43:G57&lt;C36),0)),"")</f>
+        <f t="array" ref="C38:C38">IFERROR(INDEX('Recipe Sheet'!G43:G57,MATCH(1,('Recipe Sheet'!G43:G57&lt;C37)*('Recipe Sheet'!G43:G57&lt;C36),0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="1478">
@@ -16759,17 +16759,17 @@
         <v/>
       </c>
       <c r="E38" s="1558">
-        <f>IF(A38=" "," ", "doseerpunt")</f>
+        <f>IF(A38=" "," ", "Hop Doser / Method")</f>
         <v/>
       </c>
       <c r="F38" s="1177" t="n"/>
       <c r="G38" s="1178" t="n"/>
       <c r="H38" s="1478">
-        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recept-voorblad'!G44:Q58,MATCH(Brouwen!C38,'Recept-voorblad'!G44:G58,0),11),""),IF(IFERROR(1/INDEX('Recept-voorblad'!G44:Q58,MATCH(Brouwen!C38,'Recept-voorblad'!G44:G58,0),3),"nee")="nee",IF(Brouwen!C38="","","nee"),"ja"))</f>
+        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recipe Sheet'!G44:Q58,MATCH('Brew Sheet'!C38,'Recipe Sheet'!G44:G58,0),11),""),IF(IFERROR(1/INDEX('Recipe Sheet'!G44:Q58,MATCH('Brew Sheet'!C38,'Recipe Sheet'!G44:G58,0),3),"no")="no",IF('Brew Sheet'!C38="","","no"),"yes"))</f>
         <v/>
       </c>
       <c r="I38" s="1568">
-        <f>IF(LEFT(A1,2)="WP", "Inline sparge",'Recept-voorblad'!A77)</f>
+        <f>IF(LEFT(A1,2)="WP", "Inline Sparge",'Recipe Sheet'!A77)</f>
         <v/>
       </c>
       <c r="L38" s="1083" t="n"/>
@@ -16778,7 +16778,7 @@
       <c r="O38" s="1178" t="n"/>
       <c r="P38" s="1369" t="inlineStr">
         <is>
-          <t>Water additie</t>
+          <t xml:space="preserve">Water Addition After Whirlpool</t>
         </is>
       </c>
       <c r="Q38" s="1446" t="n"/>
@@ -16841,12 +16841,12 @@
     </row>
     <row r="39" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A39" s="1557">
-        <f>IF(C39="-"," ","Hopgift")</f>
+        <f>IF(C39="-"," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B39" s="1178" t="n"/>
       <c r="C39" s="1567">
-        <f t="array" ref="C39:C39">IFERROR(INDEX('Recept-voorblad'!G44:G58,MATCH(1,('Recept-voorblad'!G44:G58&lt;C38)*('Recept-voorblad'!G44:G58&lt;C37),0)),"")</f>
+        <f t="array" ref="C39:C39">IFERROR(INDEX('Recipe Sheet'!G44:G58,MATCH(1,('Recipe Sheet'!G44:G58&lt;C38)*('Recipe Sheet'!G44:G58&lt;C37),0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="1478">
@@ -16854,29 +16854,29 @@
         <v/>
       </c>
       <c r="E39" s="1558">
-        <f>IF(A39=" "," ", "doseerpunt")</f>
+        <f>IF(A39=" "," ", "Hop Doser / Method")</f>
         <v/>
       </c>
       <c r="F39" s="1177" t="n"/>
       <c r="G39" s="1178" t="n"/>
       <c r="H39" s="1478">
-        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recept-voorblad'!G45:Q59,MATCH(Brouwen!C39,'Recept-voorblad'!G45:G59,0),11),""),IF(IFERROR(1/INDEX('Recept-voorblad'!G45:Q59,MATCH(Brouwen!C39,'Recept-voorblad'!G45:G59,0),3),"nee")="nee",IF(Brouwen!C39="","","nee"),"ja"))</f>
+        <f>IF(LEFT($A$1,2)="WP",IFERROR(INDEX('Recipe Sheet'!G45:Q59,MATCH('Brew Sheet'!C39,'Recipe Sheet'!G45:G59,0),11),""),IF(IFERROR(1/INDEX('Recipe Sheet'!G45:Q59,MATCH('Brew Sheet'!C39,'Recipe Sheet'!G45:G59,0),3),"no")="no",IF('Brew Sheet'!C39="","","no"),"yes"))</f>
         <v/>
       </c>
       <c r="I39" s="1568">
-        <f>IF(LEFT(A1,2)="WP", " ",'Recept-voorblad'!A78)</f>
+        <f>IF(LEFT(A1,2)="WP", " ",'Recipe Sheet'!A78)</f>
         <v/>
       </c>
       <c r="L39" s="1083" t="n"/>
       <c r="M39" s="1561">
-        <f>IF(LEFT(A1,2)="WP"," ",'Recept-voorblad'!E78&amp;" "&amp;'Recept-voorblad'!I78)</f>
+        <f>IF(LEFT(A1,2)="WP"," ",'Recipe Sheet'!E78&amp;" "&amp;'Recipe Sheet'!I78)</f>
         <v/>
       </c>
       <c r="N39" s="1561" t="n"/>
       <c r="O39" s="1178" t="n"/>
       <c r="P39" s="1369" t="inlineStr">
         <is>
-          <t>Volume brouwsel</t>
+          <t xml:space="preserve">Brew Volume</t>
         </is>
       </c>
       <c r="Q39" s="1446" t="n"/>
@@ -16966,12 +16966,12 @@
     </row>
     <row r="40" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A40" s="1557">
-        <f>IF(C40=""," ","Hopgift")</f>
+        <f>IF(C40=""," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B40" s="1178" t="n"/>
       <c r="C40" s="1567">
-        <f t="array" ref="C40:C40">IFERROR(INDEX('Recept-voorblad'!G45:G59,MATCH(1,('Recept-voorblad'!G45:G59&lt;C39)*('Recept-voorblad'!G45:G59&lt;C38),0)),"")</f>
+        <f t="array" ref="C40:C40">IFERROR(INDEX('Recipe Sheet'!G45:G59,MATCH(1,('Recipe Sheet'!G45:G59&lt;C39)*('Recipe Sheet'!G45:G59&lt;C38),0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="1478">
@@ -16979,29 +16979,29 @@
         <v/>
       </c>
       <c r="E40" s="1558">
-        <f>IF(A40=" "," ", "doseerpunt")</f>
+        <f>IF(A40=" "," ", "Hop Doser / Method")</f>
         <v/>
       </c>
       <c r="F40" s="1177" t="n"/>
       <c r="G40" s="1178" t="n"/>
       <c r="H40" s="1478">
-        <f>IFERROR(INDEX('Recept-voorblad'!G46:Q60,MATCH(Brouwen!C40,'Recept-voorblad'!G46:G60,0),11),"")</f>
+        <f>IFERROR(INDEX('Recipe Sheet'!G46:Q60,MATCH('Brew Sheet'!C40,'Recipe Sheet'!G46:G60,0),11),"")</f>
         <v/>
       </c>
       <c r="I40" s="1568">
-        <f>IF(LEFT(A1,2)="WP", " ",'Recept-voorblad'!A79)</f>
+        <f>IF(LEFT(A1,2)="WP", " ",'Recipe Sheet'!A79)</f>
         <v/>
       </c>
       <c r="L40" s="1083" t="n"/>
       <c r="M40" s="1561">
-        <f>IF(LEFT(A1,2)="WP"," ",'Recept-voorblad'!E79&amp;" "&amp;'Recept-voorblad'!I79)</f>
+        <f>IF(LEFT(A1,2)="WP"," ",'Recipe Sheet'!E79&amp;" "&amp;'Recipe Sheet'!I79)</f>
         <v/>
       </c>
       <c r="N40" s="1561" t="n"/>
       <c r="O40" s="1178" t="n"/>
       <c r="P40" s="1580" t="inlineStr">
         <is>
-          <t>Volume GLT</t>
+          <t xml:space="preserve">Total Volume In GLT</t>
         </is>
       </c>
       <c r="Q40" s="1495" t="n"/>
@@ -17094,12 +17094,12 @@
     </row>
     <row r="41" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A41" s="1557">
-        <f>IF(C41=""," ","Hopgift")</f>
+        <f>IF(C41=""," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B41" s="1178" t="n"/>
       <c r="C41" s="1567">
-        <f t="array" ref="C41:C41">IFERROR(INDEX('Recept-voorblad'!G46:G60,MATCH(1,('Recept-voorblad'!G46:G60&lt;C40)*('Recept-voorblad'!G46:G60&lt;C39),0)),"")</f>
+        <f t="array" ref="C41:C41">IFERROR(INDEX('Recipe Sheet'!G46:G60,MATCH(1,('Recipe Sheet'!G46:G60&lt;C40)*('Recipe Sheet'!G46:G60&lt;C39),0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="1478">
@@ -17107,29 +17107,29 @@
         <v/>
       </c>
       <c r="E41" s="1558">
-        <f>IF(A41=" "," ", "doseerpunt")</f>
+        <f>IF(A41=" "," ", "Dosing Point")</f>
         <v/>
       </c>
       <c r="F41" s="1177" t="n"/>
       <c r="G41" s="1178" t="n"/>
       <c r="H41" s="1478">
-        <f>IFERROR(INDEX('Recept-voorblad'!G47:Q61,MATCH(Brouwen!C41,'Recept-voorblad'!G47:G61,0),11),"")</f>
+        <f>IFERROR(INDEX('Recipe Sheet'!G47:Q61,MATCH('Brew Sheet'!C41,'Recipe Sheet'!G47:G61,0),11),"")</f>
         <v/>
       </c>
       <c r="I41" s="1568">
-        <f>IF(LEFT(A1,2)="WP", " ",'Recept-voorblad'!A80)</f>
+        <f>IF(LEFT(A1,2)="WP", " ",'Recipe Sheet'!A80)</f>
         <v/>
       </c>
       <c r="L41" s="1083" t="n"/>
       <c r="M41" s="1561">
-        <f>IF(LEFT(A1,2)="WP"," ",'Recept-voorblad'!E80&amp;" "&amp;'Recept-voorblad'!I80)</f>
+        <f>IF(LEFT(A1,2)="WP"," ",'Recipe Sheet'!E80&amp;" "&amp;'Recipe Sheet'!I80)</f>
         <v/>
       </c>
       <c r="N41" s="1561" t="n"/>
       <c r="O41" s="1178" t="n"/>
       <c r="P41" s="1580" t="inlineStr">
         <is>
-          <t>Extract Tank</t>
+          <t xml:space="preserve">Extract In GLT</t>
         </is>
       </c>
       <c r="Q41" s="1495" t="n"/>
@@ -17222,12 +17222,12 @@
     </row>
     <row r="42" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A42" s="1557">
-        <f>IF(C42=""," ","Hopgift")</f>
+        <f>IF(C42=""," ","Hop Addition")</f>
         <v/>
       </c>
       <c r="B42" s="1178" t="n"/>
       <c r="C42" s="1567">
-        <f t="array" ref="C42:C42">IFERROR(INDEX('Recept-voorblad'!G47:G61,MATCH(1,('Recept-voorblad'!G47:G61&lt;C41)*('Recept-voorblad'!G47:G61&lt;C40)*('Recept-voorblad'!G47:G61&lt;C39),0)),"")</f>
+        <f t="array" ref="C42:C42">IFERROR(INDEX('Recipe Sheet'!G47:G61,MATCH(1,('Recipe Sheet'!G47:G61&lt;C41)*('Recipe Sheet'!G47:G61&lt;C40)*('Recipe Sheet'!G47:G61&lt;C39),0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="1585">
@@ -17235,13 +17235,13 @@
         <v/>
       </c>
       <c r="E42" s="1558">
-        <f>IF(A42=" "," ", "doseerpunt")</f>
+        <f>IF(A42=" "," ", "Dosing Point")</f>
         <v/>
       </c>
       <c r="F42" s="1177" t="n"/>
       <c r="G42" s="1178" t="n"/>
       <c r="H42" s="1478">
-        <f>IFERROR(INDEX('Recept-voorblad'!G48:Q62,MATCH(Brouwen!C42,'Recept-voorblad'!G48:G62,0),11),"")</f>
+        <f>IFERROR(INDEX('Recipe Sheet'!G48:Q62,MATCH('Brew Sheet'!C42,'Recipe Sheet'!G48:G62,0),11),"")</f>
         <v/>
       </c>
       <c r="I42" s="1586" t="n"/>
@@ -17344,7 +17344,7 @@
     <row r="43" ht="14.25" customFormat="1" customHeight="1" s="1099">
       <c r="A43" s="1590" t="inlineStr">
         <is>
-          <t>Opmerkingen :</t>
+          <t xml:space="preserve">Comments:</t>
         </is>
       </c>
       <c r="B43" s="1591" t="n"/>
@@ -17358,7 +17358,7 @@
       <c r="J43" s="1224" t="n"/>
       <c r="K43" s="1587" t="inlineStr">
         <is>
-          <t>Droge Gist enting:</t>
+          <t xml:space="preserve">Yeast Pitching:</t>
         </is>
       </c>
       <c r="L43" s="1114" t="n"/>
@@ -17367,7 +17367,7 @@
       <c r="O43" s="1115" t="n"/>
       <c r="P43" s="1580" t="inlineStr">
         <is>
-          <t>Einde brouwen (dd-mm uu:mm)</t>
+          <t xml:space="preserve">End Time Brew (dd-mm uu:mm)</t>
         </is>
       </c>
       <c r="Q43" s="1495" t="n"/>
@@ -17405,19 +17405,19 @@
       <c r="J44" s="1227" t="n"/>
       <c r="K44" s="1383" t="inlineStr">
         <is>
-          <t>Temp start</t>
+          <t xml:space="preserve">Temp Start</t>
         </is>
       </c>
       <c r="L44" s="1075" t="n"/>
       <c r="M44" s="1076" t="n"/>
       <c r="N44" s="1595">
-        <f>'Recept-voorblad'!F21</f>
+        <f>'Recipe Sheet'!F21</f>
         <v/>
       </c>
       <c r="O44" s="1224" t="n"/>
       <c r="P44" s="1596" t="inlineStr">
         <is>
-          <t>Totale tijd brouwen</t>
+          <t xml:space="preserve">Total Brewing Time</t>
         </is>
       </c>
       <c r="Q44" s="1597" t="n"/>
@@ -17428,7 +17428,7 @@
       </c>
       <c r="T44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="U44" s="1598">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="V44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="W44" s="1598">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="X44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="Y44" s="1598">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="Z44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="AA44" s="1598">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="AB44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="AC44" s="1598">
@@ -17473,7 +17473,7 @@
       </c>
       <c r="AD44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="AE44" s="1598">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="AF44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="AG44" s="1598">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AH44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
       <c r="AI44" s="1598">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="AJ44" s="1599" t="inlineStr">
         <is>
-          <t>uur</t>
+          <t xml:space="preserve">hrs</t>
         </is>
       </c>
     </row>
@@ -17517,17 +17517,17 @@
       <c r="J45" s="1178" t="n"/>
       <c r="K45" s="1401" t="inlineStr">
         <is>
-          <t>Temp max</t>
+          <t xml:space="preserve">Temp Max</t>
         </is>
       </c>
       <c r="M45" s="1083" t="n"/>
       <c r="N45" s="1601">
-        <f>'Recept-voorblad'!F22</f>
+        <f>'Recipe Sheet'!F22</f>
         <v/>
       </c>
       <c r="O45" s="1178" t="n"/>
       <c r="P45" s="1602">
-        <f>IF(LEFT(A1,2)="WP", " ","Beluchtingsfilter gestoomd?")</f>
+        <f>IF(LEFT(A1,2)="WP", " ","Aeration Filter Steamed?")</f>
         <v/>
       </c>
       <c r="Q45" s="1602" t="n"/>
@@ -17564,17 +17564,17 @@
       <c r="J46" s="1178" t="n"/>
       <c r="K46" s="1401" t="inlineStr">
         <is>
-          <t>Giststam</t>
+          <t xml:space="preserve">Yeast Strain</t>
         </is>
       </c>
       <c r="M46" s="1083" t="n"/>
       <c r="N46" s="1609">
-        <f>SUBSTITUTE('Recept-voorblad'!A87&amp;IF('Recept-voorblad'!A88=0,"",'Recept-voorblad'!A88),"(g/brew)"," ")</f>
+        <f>SUBSTITUTE('Recipe Sheet'!A87&amp;IF('Recipe Sheet'!A88=0,"",'Recipe Sheet'!A88),"(g/brew)"," ")</f>
         <v/>
       </c>
       <c r="O46" s="1178" t="n"/>
       <c r="P46" s="1602">
-        <f>IF(LEFT(A1,2)="WP", " ","Wortline gesteriliseerd?")</f>
+        <f>IF(LEFT(A1,2)="WP", " ","Wort Line Sterilised?")</f>
         <v/>
       </c>
       <c r="Q46" s="1602" t="n"/>
@@ -17611,7 +17611,7 @@
       <c r="J47" s="1178" t="n"/>
       <c r="K47" s="1401" t="inlineStr">
         <is>
-          <t>Gerehydrateerd?</t>
+          <t xml:space="preserve">Rehydrated?</t>
         </is>
       </c>
       <c r="M47" s="1083" t="n"/>
@@ -17655,17 +17655,17 @@
       <c r="J48" s="1178" t="n"/>
       <c r="K48" s="1401" t="inlineStr">
         <is>
-          <t>Gewicht [gram]</t>
+          <t xml:space="preserve">Weight [g]</t>
         </is>
       </c>
       <c r="M48" s="1083" t="n"/>
       <c r="N48" s="1617">
-        <f>'Recept-voorblad'!G87+IF('Recept-voorblad'!G88="",0,'Recept-voorblad'!G88)</f>
+        <f>'Recipe Sheet'!G87+IF('Recipe Sheet'!G88="",0,'Recipe Sheet'!G88)</f>
         <v/>
       </c>
       <c r="O48" s="1178" t="n"/>
       <c r="P48" s="1602">
-        <f>IF(LEFT(A1,2)="WP", " ","Bostelbak nummer")</f>
+        <f>IF(LEFT(A1,2)="WP", " ","Spent Grain Bin No.")</f>
         <v/>
       </c>
       <c r="Q48" s="1602" t="n"/>
@@ -17702,14 +17702,14 @@
       <c r="J49" s="1178" t="n"/>
       <c r="K49" s="1401" t="inlineStr">
         <is>
-          <t>Bij 1e brouwsel</t>
+          <t xml:space="preserve">Pitched in 1st brew?</t>
         </is>
       </c>
       <c r="M49" s="1083" t="n"/>
       <c r="N49" s="1615" t="n"/>
       <c r="O49" s="1178" t="n"/>
       <c r="P49" s="1602">
-        <f>IF(LEFT(A1,2)="WP", " ","Pauze  in process (uu:mm)")</f>
+        <f>IF(LEFT(A1,2)="WP", " ","Process Pause (hh:mm)")</f>
         <v/>
       </c>
       <c r="Q49" s="1602" t="n"/>
@@ -17746,7 +17746,7 @@
       <c r="J50" s="1178" t="n"/>
       <c r="K50" s="1401" t="inlineStr">
         <is>
-          <t>Geënt op (datum):</t>
+          <t xml:space="preserve">Date Of Pitching:</t>
         </is>
       </c>
       <c r="M50" s="1083" t="n"/>
@@ -17792,7 +17792,7 @@
       <c r="J51" s="1178" t="n"/>
       <c r="K51" s="1401" t="inlineStr">
         <is>
-          <t>Door:</t>
+          <t xml:space="preserve">Pitched By:</t>
         </is>
       </c>
       <c r="M51" s="1083" t="n"/>
@@ -17832,7 +17832,7 @@
       <c r="J52" s="1199" t="n"/>
       <c r="K52" s="1629" t="inlineStr">
         <is>
-          <t>Programma aan?</t>
+          <t xml:space="preserve">Fermentation Program Started?</t>
         </is>
       </c>
       <c r="L52" s="1080" t="n"/>
@@ -18022,7 +18022,7 @@
         </is>
       </c>
       <c r="L55" s="1638">
-        <f>'Recept-voorblad'!$T$15</f>
+        <f>'Recipe Sheet'!$T$15</f>
         <v/>
       </c>
       <c r="M55" s="1632" t="inlineStr">
@@ -20288,7 +20288,7 @@
     <row r="1" ht="15.75" customHeight="1" s="1339">
       <c r="K1" s="1648" t="inlineStr">
         <is>
-          <t>Specificaties</t>
+          <t xml:space="preserve">Specifications</t>
         </is>
       </c>
       <c r="L1" s="1078" t="n"/>
@@ -20322,7 +20322,7 @@
         </is>
       </c>
       <c r="H2" s="1654">
-        <f>CHOOSE(WEEKDAY(H4),"Zondag","Maandag","Dinsdag","Woensdag","Donderdag","Vrijdag","Zaterdag")</f>
+        <f>CHOOSE(WEEKDAY(H4),"Sunday","Monday","Tuesday","Wednesday","Thursday","Friday","Saturday")</f>
         <v/>
       </c>
       <c r="K2" s="1655" t="inlineStr">
@@ -20397,16 +20397,16 @@
         </is>
       </c>
       <c r="O3" s="1669">
-        <f>'Recept-voorblad'!F12</f>
+        <f>'Recipe Sheet'!F12</f>
         <v/>
       </c>
       <c r="P3" s="1670">
-        <f>'Recept-voorblad'!E12</f>
+        <f>'Recipe Sheet'!E12</f>
         <v/>
       </c>
       <c r="Q3" s="1671" t="inlineStr">
         <is>
-          <t>Lager temp,</t>
+          <t xml:space="preserve">Lagering Temp</t>
         </is>
       </c>
       <c r="R3" s="1672" t="n"/>
@@ -20416,13 +20416,13 @@
         </is>
       </c>
       <c r="T3" s="1669">
-        <f>'Recept-voorblad'!M23</f>
+        <f>'Recipe Sheet'!M23</f>
         <v/>
       </c>
       <c r="U3" s="1673" t="n"/>
       <c r="V3" s="1670" t="n"/>
       <c r="X3" s="1674">
-        <f>IF(COUNTIF('Recept-voorblad'!G58:I63,"warm")&gt;0,IF(SUMIF('Recept-voorblad'!G58:P63,"warm",'Recept-voorblad'!P58:P63)= "&gt;65000","Dry hop methode= "&amp;"warm hopsteiner","Dry hop methode= "&amp;"warm hopgun"),"")</f>
+        <f>IF(COUNTIF('Recipe Sheet'!G58:I63,"warm")&gt;0,IF(SUMIF('Recipe Sheet'!G58:P63,"warm",'Recipe Sheet'!P58:P63)= "&gt;65000","Dry hop method: "&amp;"warm Hopsteiner","Dry hop method: "&amp;"warm HopGun"),"")</f>
         <v/>
       </c>
       <c r="Y3" s="1078" t="n"/>
@@ -20434,13 +20434,13 @@
     </row>
     <row r="4" ht="14.25" customHeight="1" s="1339">
       <c r="A4" s="1675">
-        <f>'Recept-voorblad'!C3</f>
+        <f>'Recipe Sheet'!C3</f>
         <v/>
       </c>
       <c r="B4" s="1676" t="n"/>
       <c r="C4" s="1677" t="n"/>
       <c r="D4" s="1678">
-        <f>Brouwen!I5</f>
+        <f>'Brew Sheet'!I5</f>
         <v/>
       </c>
       <c r="E4" s="1679" t="n"/>
@@ -20449,7 +20449,7 @@
         <v/>
       </c>
       <c r="K4" s="1681">
-        <f>'Recept-voorblad'!A23</f>
+        <f>'Recipe Sheet'!A23</f>
         <v/>
       </c>
       <c r="L4" s="1078" t="n"/>
@@ -20460,16 +20460,16 @@
         </is>
       </c>
       <c r="O4" s="1683">
-        <f>'Recept-voorblad'!F23</f>
+        <f>'Recipe Sheet'!F23</f>
         <v/>
       </c>
       <c r="P4" s="1684">
-        <f>'Recept-voorblad'!E23</f>
+        <f>'Recipe Sheet'!E23</f>
         <v/>
       </c>
       <c r="Q4" s="1685" t="inlineStr">
         <is>
-          <t>Lagering time</t>
+          <t xml:space="preserve">Lagering Time</t>
         </is>
       </c>
       <c r="R4" s="1686" t="n"/>
@@ -20479,13 +20479,13 @@
         </is>
       </c>
       <c r="T4" s="1688">
-        <f>'Recept-voorblad'!M22</f>
+        <f>'Recipe Sheet'!M22</f>
         <v/>
       </c>
       <c r="U4" s="1689" t="n"/>
       <c r="V4" s="1690" t="n"/>
       <c r="X4" s="1691">
-        <f>ROUND(SUMIF('Recept-voorblad'!G55:P60,"warm",'Recept-voorblad'!P55:P60)/1000,1)&amp;"  kilogram dry hop"</f>
+        <f>ROUND(SUMIF('Recipe Sheet'!G55:P60,"warm",'Recipe Sheet'!P55:P60)/1000,1)&amp;"  kg dry hop"</f>
         <v/>
       </c>
       <c r="Y4" s="1078" t="n"/>
@@ -20504,7 +20504,7 @@
       <c r="H5" s="1696" t="n"/>
       <c r="K5" s="1681" t="inlineStr">
         <is>
-          <t>Temp, Warm dryhop 1</t>
+          <t xml:space="preserve">Temp Warm Dry Hop 1</t>
         </is>
       </c>
       <c r="L5" s="1078" t="n"/>
@@ -20515,16 +20515,16 @@
         </is>
       </c>
       <c r="O5" s="1683">
-        <f>'Recept-voorblad'!F24</f>
+        <f>'Recipe Sheet'!F24</f>
         <v/>
       </c>
       <c r="P5" s="1684">
-        <f>'Recept-voorblad'!E24</f>
+        <f>'Recipe Sheet'!E24</f>
         <v/>
       </c>
       <c r="Q5" s="1685" t="inlineStr">
         <is>
-          <t>Rest extract</t>
+          <t xml:space="preserve">Final Extract</t>
         </is>
       </c>
       <c r="R5" s="1686" t="n"/>
@@ -20534,11 +20534,11 @@
         </is>
       </c>
       <c r="T5" s="1683">
-        <f>'Recept-voorblad'!F13</f>
+        <f>'Recipe Sheet'!F13</f>
         <v/>
       </c>
       <c r="U5" s="1697">
-        <f>'Recept-voorblad'!E13</f>
+        <f>'Recipe Sheet'!E13</f>
         <v/>
       </c>
       <c r="V5" s="1690" t="n"/>
@@ -20558,7 +20558,7 @@
       <c r="E6" s="1078" t="n"/>
       <c r="K6" s="1681" t="inlineStr">
         <is>
-          <t>Extract warm dryhop 1</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 1</t>
         </is>
       </c>
       <c r="L6" s="1078" t="n"/>
@@ -20569,11 +20569,11 @@
         </is>
       </c>
       <c r="O6" s="1683">
-        <f>'Recept-voorblad'!F25</f>
+        <f>'Recipe Sheet'!F25</f>
         <v/>
       </c>
       <c r="P6" s="1684">
-        <f>'Recept-voorblad'!E25</f>
+        <f>'Recipe Sheet'!E25</f>
         <v/>
       </c>
       <c r="Q6" s="1685" t="inlineStr">
@@ -20584,16 +20584,16 @@
       <c r="R6" s="1686" t="n"/>
       <c r="S6" s="1687" t="n"/>
       <c r="T6" s="1683">
-        <f>'Recept-voorblad'!F17</f>
+        <f>'Recipe Sheet'!F17</f>
         <v/>
       </c>
       <c r="U6" s="1697">
-        <f>'Recept-voorblad'!E17</f>
+        <f>'Recipe Sheet'!E17</f>
         <v/>
       </c>
       <c r="V6" s="1690" t="n"/>
       <c r="X6" s="1674">
-        <f>IF(COUNTIF('Recept-voorblad'!G58:I63," @16C")&gt;0,IF(SUMIF('Recept-voorblad'!G58:P63," @16C",'Recept-voorblad'!P58:P63)= "&gt;65000","Dry hop methode= "&amp;"@16C hopsteiner","Dry hop methode= "&amp;" @16C hopgun"),"")</f>
+        <f>IF(COUNTIF('Recipe Sheet'!G58:I63," @16C")&gt;0,IF(SUMIF('Recipe Sheet'!G58:P63," @16C",'Recipe Sheet'!P58:P63)= "&gt;65000","Dry hop method: "&amp;"@16C Hopsteiner","Dry hop method: "&amp;" @16C HopGun"),"")</f>
         <v/>
       </c>
       <c r="Y6" s="1078" t="n"/>
@@ -20611,7 +20611,7 @@
       <c r="E7" s="1699" t="n"/>
       <c r="K7" s="1681" t="inlineStr">
         <is>
-          <t>Extract warm dryhop 2</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 2</t>
         </is>
       </c>
       <c r="L7" s="1078" t="n"/>
@@ -20622,11 +20622,11 @@
         </is>
       </c>
       <c r="O7" s="1683">
-        <f>'Recept-voorblad'!F26</f>
+        <f>'Recipe Sheet'!F26</f>
         <v/>
       </c>
       <c r="P7" s="1690">
-        <f>'Recept-voorblad'!E26</f>
+        <f>'Recipe Sheet'!E26</f>
         <v/>
       </c>
       <c r="Q7" s="1700" t="inlineStr">
@@ -20641,16 +20641,16 @@
         </is>
       </c>
       <c r="T7" s="1703">
-        <f>'Recept-voorblad'!F14</f>
+        <f>'Recipe Sheet'!F14</f>
         <v/>
       </c>
       <c r="U7" s="1704">
-        <f>'Recept-voorblad'!E14</f>
+        <f>'Recipe Sheet'!E14</f>
         <v/>
       </c>
       <c r="V7" s="1705" t="n"/>
       <c r="X7" s="1691">
-        <f>ROUND(SUMIF('Recept-voorblad'!G58:P63," @16C",'Recept-voorblad'!P58:P63)/1000,1)&amp;"  kilogram dry hop"</f>
+        <f>ROUND(SUMIF('Recipe Sheet'!G58:P63," @16C",'Recipe Sheet'!P58:P63)/1000,1)&amp;"  kg dry hop"</f>
         <v/>
       </c>
       <c r="Y7" s="1078" t="n"/>
@@ -20664,19 +20664,19 @@
       <c r="A8" s="1706" t="n"/>
       <c r="B8" s="1351" t="inlineStr">
         <is>
-          <t>Bier risico</t>
+          <t xml:space="preserve">Beer Risk Category</t>
         </is>
       </c>
       <c r="C8" s="1316" t="n"/>
       <c r="D8" s="1351" t="inlineStr">
         <is>
-          <t>Bier status</t>
+          <t xml:space="preserve">Beer Status</t>
         </is>
       </c>
       <c r="E8" s="1316" t="n"/>
       <c r="K8" s="1681" t="inlineStr">
         <is>
-          <t>Extract warm dryhop 3</t>
+          <t xml:space="preserve">Extract Warm Dry Hop 3</t>
         </is>
       </c>
       <c r="L8" s="1078" t="n"/>
@@ -20687,16 +20687,16 @@
         </is>
       </c>
       <c r="O8" s="1683">
-        <f>'Recept-voorblad'!F27</f>
+        <f>'Recipe Sheet'!F27</f>
         <v/>
       </c>
       <c r="P8" s="1690">
-        <f>'Recept-voorblad'!E27</f>
+        <f>'Recipe Sheet'!E27</f>
         <v/>
       </c>
       <c r="Q8" s="1707" t="inlineStr">
         <is>
-          <t>Berekeningen</t>
+          <t xml:space="preserve">Automatic Calculations</t>
         </is>
       </c>
       <c r="R8" s="1663" t="n"/>
@@ -20715,12 +20715,12 @@
     <row r="9" ht="14.25" customHeight="1" s="1339">
       <c r="A9" s="1706" t="n"/>
       <c r="B9" s="1142">
-        <f>'Recept-voorblad'!N17</f>
+        <f>'Recipe Sheet'!N17</f>
         <v/>
       </c>
       <c r="C9" s="1107" t="n"/>
       <c r="D9" s="1142">
-        <f>'Recept-voorblad'!N23</f>
+        <f>'Recipe Sheet'!N23</f>
         <v/>
       </c>
       <c r="E9" s="1107" t="n"/>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="O9" s="1688">
-        <f>'Recept-voorblad'!M21</f>
+        <f>'Recipe Sheet'!M21</f>
         <v/>
       </c>
       <c r="P9" s="1690" t="n"/>
@@ -20819,7 +20819,7 @@
     <row r="12" ht="19.5" customHeight="1" s="1339">
       <c r="A12" s="1717" t="inlineStr">
         <is>
-          <t>Dagen</t>
+          <t xml:space="preserve">Days</t>
         </is>
       </c>
       <c r="B12" s="1718" t="inlineStr">
@@ -20829,12 +20829,12 @@
       </c>
       <c r="C12" s="1719" t="inlineStr">
         <is>
-          <t>Temp Hoog</t>
+          <t xml:space="preserve">Temp Top</t>
         </is>
       </c>
       <c r="D12" s="1719" t="inlineStr">
         <is>
-          <t>Temp Laag</t>
+          <t xml:space="preserve">Temp Bottom</t>
         </is>
       </c>
       <c r="E12" s="1720" t="inlineStr">
@@ -20844,7 +20844,7 @@
       </c>
       <c r="F12" s="1721" t="inlineStr">
         <is>
-          <t>div,</t>
+          <t xml:space="preserve">Div.</t>
         </is>
       </c>
       <c r="G12" s="1722" t="inlineStr">
@@ -20854,34 +20854,34 @@
       </c>
       <c r="H12" s="1723" t="inlineStr">
         <is>
-          <t>Plato afname</t>
+          <t xml:space="preserve">Plato Decrease</t>
         </is>
       </c>
       <c r="I12" s="1724" t="inlineStr">
         <is>
-          <t>Tijd tussen meting</t>
+          <t xml:space="preserve">Hours Since Last Reading</t>
         </is>
       </c>
       <c r="J12" s="1718" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="K12" s="1719" t="inlineStr">
         <is>
-          <t>Tijd</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="L12" s="1719" t="inlineStr">
         <is>
-          <t>Actie</t>
+          <t xml:space="preserve">Action Taken</t>
         </is>
       </c>
       <c r="M12" s="1725" t="n"/>
       <c r="N12" s="1726" t="n"/>
       <c r="O12" s="1719" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="P12" s="1725" t="n"/>
@@ -20909,13 +20909,13 @@
         <v/>
       </c>
       <c r="B13" s="1728">
-        <f>IF(Brouwen!AG41="",IF(Brouwen!AE41="",IF(Brouwen!AC41="",IF(Brouwen!AA41="",IF(Brouwen!Y41="",IF(Brouwen!W41="",IF(Brouwen!U41="",Brouwen!S41,Brouwen!U41),Brouwen!W41),Brouwen!Y41),Brouwen!AA41),Brouwen!AC41),Brouwen!AE41),Brouwen!AG41)</f>
+        <f>IF('Brew Sheet'!AG41="",IF('Brew Sheet'!AE41="",IF('Brew Sheet'!AC41="",IF('Brew Sheet'!AA41="",IF('Brew Sheet'!Y41="",IF('Brew Sheet'!W41="",IF('Brew Sheet'!U41="",'Brew Sheet'!S41,'Brew Sheet'!U41),'Brew Sheet'!W41),'Brew Sheet'!Y41),'Brew Sheet'!AA41),'Brew Sheet'!AC41),'Brew Sheet'!AE41),'Brew Sheet'!AG41)</f>
         <v/>
       </c>
       <c r="C13" s="1729" t="n"/>
       <c r="D13" s="1729" t="n"/>
       <c r="E13" s="1730">
-        <f>IF(Brouwen!S35="","",AVERAGE(Brouwen!S35,Brouwen!U35,Brouwen!W35,Brouwen!Y35,Brouwen!AA35,Brouwen!AC35,Brouwen!AE35,Brouwen!AG35,Brouwen!AI35))</f>
+        <f>IF('Brew Sheet'!S35="","",AVERAGE('Brew Sheet'!S35,'Brew Sheet'!U35,'Brew Sheet'!W35,'Brew Sheet'!Y35,'Brew Sheet'!AA35,'Brew Sheet'!AC35,'Brew Sheet'!AE35,'Brew Sheet'!AG35,'Brew Sheet'!AI35))</f>
         <v/>
       </c>
       <c r="F13" s="1661" t="n"/>
@@ -20923,7 +20923,7 @@
       <c r="H13" s="1732" t="n"/>
       <c r="I13" s="1663" t="n"/>
       <c r="J13" s="1733">
-        <f>TRUNC(IF(Brouwen!AG6="",IF(Brouwen!AE6="",IF(Brouwen!AC6="",IF(Brouwen!AA6="",IF(Brouwen!Y6="",IF(Brouwen!W6="",IF(Brouwen!U6="",Brouwen!S6,Brouwen!U6),Brouwen!W6),Brouwen!Y6),Brouwen!AA6),Brouwen!AC6),Brouwen!AE6),Brouwen!AG6))</f>
+        <f>TRUNC(IF('Brew Sheet'!AG6="",IF('Brew Sheet'!AE6="",IF('Brew Sheet'!AC6="",IF('Brew Sheet'!AA6="",IF('Brew Sheet'!Y6="",IF('Brew Sheet'!W6="",IF('Brew Sheet'!U6="",'Brew Sheet'!S6,'Brew Sheet'!U6),'Brew Sheet'!W6),'Brew Sheet'!Y6),'Brew Sheet'!AA6),'Brew Sheet'!AC6),'Brew Sheet'!AE6),'Brew Sheet'!AG6))</f>
         <v/>
       </c>
       <c r="K13" s="1734" t="n"/>
@@ -20932,7 +20932,7 @@
       <c r="N13" s="1736" t="n"/>
       <c r="O13" s="1729" t="inlineStr">
         <is>
-          <t>laatste brouwsel</t>
+          <t xml:space="preserve">last brew</t>
         </is>
       </c>
       <c r="P13" s="1735" t="n"/>
@@ -21314,7 +21314,7 @@
       <c r="M23" s="1747" t="n"/>
       <c r="N23" s="1748" t="n"/>
       <c r="O23" s="1739">
-        <f>IF('Recept-voorblad'!I91="-","-",'Recept-voorblad'!E91&amp;" "&amp;'Recept-voorblad'!A91&amp;" @"&amp;'Recept-voorblad'!I91)</f>
+        <f>IF('Recipe Sheet'!I91="-","-",'Recipe Sheet'!E91&amp;" "&amp;'Recipe Sheet'!A91&amp;" @"&amp;'Recipe Sheet'!I91)</f>
         <v/>
       </c>
       <c r="P23" s="1747" t="n"/>
@@ -21356,7 +21356,7 @@
       <c r="M24" s="1747" t="n"/>
       <c r="N24" s="1748" t="n"/>
       <c r="O24" s="1739">
-        <f>IF('Recept-voorblad'!I92="-","-",'Recept-voorblad'!E92&amp;" "&amp;'Recept-voorblad'!A92&amp;" @"&amp;'Recept-voorblad'!I92)</f>
+        <f>IF('Recipe Sheet'!I92="-","-",'Recipe Sheet'!E92&amp;" "&amp;'Recipe Sheet'!A92&amp;" @"&amp;'Recipe Sheet'!I92)</f>
         <v/>
       </c>
       <c r="P24" s="1747" t="n"/>
@@ -21398,7 +21398,7 @@
       <c r="M25" s="1747" t="n"/>
       <c r="N25" s="1748" t="n"/>
       <c r="O25" s="1739">
-        <f>IF('Recept-voorblad'!I93="-","-",'Recept-voorblad'!E93&amp;" "&amp;'Recept-voorblad'!A93&amp;" @"&amp;'Recept-voorblad'!I93)</f>
+        <f>IF('Recipe Sheet'!I93="-","-",'Recipe Sheet'!E93&amp;" "&amp;'Recipe Sheet'!A93&amp;" @"&amp;'Recipe Sheet'!I93)</f>
         <v/>
       </c>
       <c r="P25" s="1747" t="n"/>
@@ -21440,7 +21440,7 @@
       <c r="M26" s="1747" t="n"/>
       <c r="N26" s="1748" t="n"/>
       <c r="O26" s="1739">
-        <f>IF('Recept-voorblad'!I94="-","-",'Recept-voorblad'!E94&amp;" "&amp;'Recept-voorblad'!A94&amp;" @"&amp;'Recept-voorblad'!I94)</f>
+        <f>IF('Recipe Sheet'!I94="-","-",'Recipe Sheet'!E94&amp;" "&amp;'Recipe Sheet'!A94&amp;" @"&amp;'Recipe Sheet'!I94)</f>
         <v/>
       </c>
       <c r="P26" s="1747" t="n"/>
@@ -21479,7 +21479,7 @@
       <c r="M27" s="1747" t="n"/>
       <c r="N27" s="1748" t="n"/>
       <c r="O27" s="1739">
-        <f>IF('Recept-voorblad'!I95="-","-",'Recept-voorblad'!E95&amp;" "&amp;'Recept-voorblad'!A95&amp;" @"&amp;'Recept-voorblad'!I95)</f>
+        <f>IF('Recipe Sheet'!I95="-","-",'Recipe Sheet'!E95&amp;" "&amp;'Recipe Sheet'!A95&amp;" @"&amp;'Recipe Sheet'!I95)</f>
         <v/>
       </c>
       <c r="P27" s="1747" t="n"/>
@@ -21890,7 +21890,7 @@
       <c r="Z38" s="1342" t="n"/>
       <c r="AB38" s="1756" t="inlineStr">
         <is>
-          <t>datum</t>
+          <t xml:space="preserve">date</t>
         </is>
       </c>
     </row>
@@ -22027,7 +22027,7 @@
       <c r="Y41" s="1342" t="n"/>
       <c r="Z41" s="1342" t="inlineStr">
         <is>
-          <t>dryhopping</t>
+          <t xml:space="preserve">dry hopping</t>
         </is>
       </c>
       <c r="AA41" s="1342" t="n"/>
@@ -22118,7 +22118,7 @@
       <c r="Y43" s="1342" t="n"/>
       <c r="Z43" s="1342" t="inlineStr">
         <is>
-          <t>koelen</t>
+          <t xml:space="preserve">cooling</t>
         </is>
       </c>
       <c r="AA43" s="1342" t="n"/>
@@ -22209,7 +22209,7 @@
       <c r="Y45" s="1342" t="n"/>
       <c r="Z45" s="1342" t="inlineStr">
         <is>
-          <t>toevoeging</t>
+          <t xml:space="preserve">addition</t>
         </is>
       </c>
       <c r="AA45" s="1342" t="n"/>
@@ -22300,7 +22300,7 @@
       <c r="Y47" s="1342" t="n"/>
       <c r="Z47" s="1342" t="inlineStr">
         <is>
-          <t>sample naar lab</t>
+          <t xml:space="preserve">sample to lab</t>
         </is>
       </c>
       <c r="AA47" s="1342" t="n"/>
@@ -22557,7 +22557,7 @@
       <c r="Y53" s="1602" t="n"/>
       <c r="Z53" s="1763" t="n"/>
       <c r="AA53" s="1763">
-        <f>'Recept-voorblad'!G7*'Recept-voorblad'!C9*100</f>
+        <f>'Recipe Sheet'!G7*'Recipe Sheet'!C9*100</f>
         <v/>
       </c>
       <c r="AB53" s="1159" t="inlineStr">
@@ -22611,7 +22611,7 @@
       <c r="Y54" s="1159" t="n"/>
       <c r="Z54" s="1761" t="n"/>
       <c r="AA54" s="1764">
-        <f>VLOOKUP("*Nagardo*",'Recept-voorblad'!A91:H93,5,FALSE())</f>
+        <f>VLOOKUP("*Nagardo*",'Recipe Sheet'!A91:H93,5,FALSE())</f>
         <v/>
       </c>
       <c r="AB54" s="1159" t="inlineStr">
@@ -22924,7 +22924,7 @@
       <c r="Y60" s="1602" t="n"/>
       <c r="Z60" s="1763" t="n"/>
       <c r="AA60" s="1763">
-        <f>'Recept-voorblad'!E92*(AA53/100)</f>
+        <f>'Recipe Sheet'!E92*(AA53/100)</f>
         <v/>
       </c>
       <c r="AB60" s="1159" t="inlineStr">
@@ -23882,11 +23882,11 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="L14:N63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"24h purge,purge,purge,spond,purge,dry warm,spond,proeven,proeven,purge,koelen,toevoeging,pomp start,pomp stop,overdrukken,verwerken,sample naar lab,purge,verwerken,samenvoegen,dryhopping,anders"</formula1>
+      <formula1>"24h purge,purge,spund,dry warm,tasting,cooling,addition,pump start,pump stop,transfer,processing,sample to lab,blending,dry hopping,other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="L13:N13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"24h purge,purge,purge,spond,purge,dry warm,spond,proeven,proeven,purge,koelen,toevoeging,pomp start,pomp stop,overdrukken,verwerken,sample naar lab,purge,verwerken,samenvoegen,dryhopping,purge,transport,anders"</formula1>
+      <formula1>"24h purge,purge,spund,dry warm,tasting,cooling,addition,pump start,pump stop,transfer,processing,sample to lab,blending,dry hopping,transport,other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -23932,7 +23932,7 @@
     <row r="1" ht="15" customHeight="1" s="1339">
       <c r="A1" s="1826" t="inlineStr">
         <is>
-          <t>Verwerking</t>
+          <t xml:space="preserve">Processing</t>
         </is>
       </c>
       <c r="B1" s="1106" t="n"/>
@@ -23997,19 +23997,19 @@
       </c>
       <c r="B3" s="1078" t="n"/>
       <c r="C3" s="1829">
-        <f>'Gistkaart Invoer'!A4</f>
+        <f>'Fermentation Chart'!A4</f>
         <v/>
       </c>
       <c r="H3" s="1083" t="n"/>
       <c r="I3" s="1830" t="inlineStr">
         <is>
-          <t>Batchnummer:</t>
+          <t xml:space="preserve">Batch No.:</t>
         </is>
       </c>
       <c r="J3" s="1078" t="n"/>
       <c r="K3" s="1078" t="n"/>
       <c r="L3" s="1831">
-        <f>'Recept-voorblad'!K3</f>
+        <f>'Recipe Sheet'!K3</f>
         <v/>
       </c>
       <c r="P3" s="1832" t="n"/>
@@ -24053,7 +24053,7 @@
     <row r="5" ht="15.75" customHeight="1" s="1339">
       <c r="A5" s="1838" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specificaties </t>
+          <t xml:space="preserve">Specifications</t>
         </is>
       </c>
       <c r="B5" s="1315" t="n"/>
@@ -24072,7 +24072,7 @@
       <c r="O5" s="1315" t="n"/>
       <c r="P5" s="1839" t="inlineStr">
         <is>
-          <t>Beer risk category</t>
+          <t xml:space="preserve">Beer Risk Category</t>
         </is>
       </c>
       <c r="Q5" s="1315" t="n"/>
@@ -24102,7 +24102,7 @@
       </c>
       <c r="E6" s="1844" t="inlineStr">
         <is>
-          <t>spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="F6" s="1316" t="n"/>
@@ -24127,7 +24127,7 @@
       </c>
       <c r="N6" s="1844" t="inlineStr">
         <is>
-          <t>spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="O6" s="1846" t="inlineStr">
@@ -24136,7 +24136,7 @@
         </is>
       </c>
       <c r="P6" s="1847">
-        <f>'Recept-voorblad'!N17</f>
+        <f>'Recipe Sheet'!N17</f>
         <v/>
       </c>
       <c r="Q6" s="1075" t="n"/>
@@ -24165,12 +24165,12 @@
         </is>
       </c>
       <c r="E7" s="1124">
-        <f>'Recept-voorblad'!M25</f>
+        <f>'Recipe Sheet'!M25</f>
         <v/>
       </c>
       <c r="F7" s="1076" t="n"/>
       <c r="G7" s="1852">
-        <f>'Recept-voorblad'!L25</f>
+        <f>'Recipe Sheet'!L25</f>
         <v/>
       </c>
       <c r="H7" s="1853" t="inlineStr">
@@ -24188,11 +24188,11 @@
         </is>
       </c>
       <c r="N7" s="1122">
-        <f>'Recept-voorblad'!M13</f>
+        <f>'Recipe Sheet'!M13</f>
         <v/>
       </c>
       <c r="O7" s="1855">
-        <f>'Recept-voorblad'!L13-0.1</f>
+        <f>'Recipe Sheet'!L13-0.1</f>
         <v/>
       </c>
       <c r="P7" s="1160" t="n"/>
@@ -24221,7 +24221,7 @@
         </is>
       </c>
       <c r="E8" s="1129">
-        <f>'Recept-voorblad'!M24</f>
+        <f>'Recipe Sheet'!M24</f>
         <v/>
       </c>
       <c r="F8" s="1083" t="n"/>
@@ -24243,11 +24243,11 @@
         </is>
       </c>
       <c r="N8" s="1127">
-        <f>'Recept-voorblad'!M15</f>
+        <f>'Recipe Sheet'!M15</f>
         <v/>
       </c>
       <c r="O8" s="1855">
-        <f>'Recept-voorblad'!L15+0.2</f>
+        <f>'Recipe Sheet'!L15+0.2</f>
         <v/>
       </c>
       <c r="P8" s="1160" t="n"/>
@@ -24295,11 +24295,11 @@
       <c r="L9" s="1087" t="n"/>
       <c r="M9" s="1854" t="n"/>
       <c r="N9" s="1862">
-        <f>'Recept-voorblad'!M14</f>
+        <f>'Recipe Sheet'!M14</f>
         <v/>
       </c>
       <c r="O9" s="1863">
-        <f>'Recept-voorblad'!L14-0.1</f>
+        <f>'Recipe Sheet'!L14-0.1</f>
         <v/>
       </c>
       <c r="P9" s="1079" t="n"/>
@@ -24432,7 +24432,7 @@
     <row r="13" ht="15.75" customHeight="1" s="1339">
       <c r="A13" s="1839" t="inlineStr">
         <is>
-          <t>Verwerking</t>
+          <t xml:space="preserve">Processing</t>
         </is>
       </c>
       <c r="B13" s="1315" t="n"/>
@@ -24560,7 +24560,7 @@
       <c r="R16" s="1115" t="n"/>
       <c r="S16" s="1602" t="inlineStr">
         <is>
-          <t>Volume Mooie Nel</t>
+          <t xml:space="preserve">Volume Current Batch</t>
         </is>
       </c>
       <c r="T16" s="1602" t="n"/>
@@ -24599,7 +24599,7 @@
       <c r="R17" s="1316" t="n"/>
       <c r="S17" s="1159" t="inlineStr">
         <is>
-          <t>Alcohol Mooie Nel - batch</t>
+          <t xml:space="preserve">Alcohol Current Batch</t>
         </is>
       </c>
       <c r="T17" s="1159" t="n"/>
@@ -24629,7 +24629,7 @@
       <c r="F18" s="1094" t="n"/>
       <c r="G18" s="1879" t="inlineStr">
         <is>
-          <t>Standpijp</t>
+          <t xml:space="preserve">Standpipe</t>
         </is>
       </c>
       <c r="H18" s="1093" t="n"/>
@@ -24649,7 +24649,7 @@
       <c r="R18" s="1094" t="n"/>
       <c r="S18" s="1159" t="inlineStr">
         <is>
-          <t>Gewenste alcohol Super Dupa --&gt;</t>
+          <t xml:space="preserve">Target Alcohol After Dilution --&gt;</t>
         </is>
       </c>
       <c r="T18" s="1159" t="n"/>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="J21" s="1871" t="inlineStr">
         <is>
-          <t>Flow [hl/u]</t>
+          <t xml:space="preserve">Flow [hl/h]</t>
         </is>
       </c>
       <c r="K21" s="1315" t="n"/>
@@ -24853,7 +24853,7 @@
       <c r="R22" s="1890" t="n"/>
       <c r="S22" s="1159" t="inlineStr">
         <is>
-          <t>Made from batch Mooie Nel</t>
+          <t xml:space="preserve">Made From Batch</t>
         </is>
       </c>
       <c r="T22" s="1159" t="n"/>
@@ -25376,13 +25376,13 @@
       <c r="R36" s="1892" t="n"/>
       <c r="S36" s="1602" t="inlineStr">
         <is>
-          <t>Dosing  (from recept-voorblad)</t>
+          <t xml:space="preserve">Dosing (from Recipe Sheet)</t>
         </is>
       </c>
       <c r="T36" s="1602" t="n"/>
       <c r="U36" s="1939" t="n"/>
       <c r="V36" s="1763">
-        <f>VLOOKUP("*Nagardo*",'Recept-voorblad'!$A$91:$H$93,5,FALSE())</f>
+        <f>VLOOKUP("*Nagardo*",'Recipe Sheet'!$A$91:$H$93,5,FALSE())</f>
         <v/>
       </c>
       <c r="W36" s="1602" t="inlineStr">
@@ -25926,7 +25926,7 @@
       <c r="T46" s="1954" t="n"/>
       <c r="U46" s="1955" t="n"/>
       <c r="V46" s="1955">
-        <f>'Recept-voorblad'!$E$92*(V35/100*100)</f>
+        <f>'Recipe Sheet'!$E$92*(V35/100*100)</f>
         <v/>
       </c>
       <c r="W46" s="1954" t="inlineStr">
@@ -26127,13 +26127,13 @@
       <c r="R50" s="1892" t="n"/>
       <c r="S50" s="1602" t="inlineStr">
         <is>
-          <t>Dosing  (from recept-voorblad)</t>
+          <t xml:space="preserve">Dosing (from Recipe Sheet)</t>
         </is>
       </c>
       <c r="T50" s="1602" t="n"/>
       <c r="U50" s="1602" t="n"/>
       <c r="V50" s="1763">
-        <f>VLOOKUP("*Nagardo*",'Recept-voorblad'!$A$91:$H$93,5,FALSE())</f>
+        <f>VLOOKUP("*Nagardo*",'Recipe Sheet'!$A$91:$H$93,5,FALSE())</f>
         <v/>
       </c>
       <c r="W50" s="1602" t="inlineStr">
@@ -26620,7 +26620,7 @@
       <c r="T60" s="1602" t="n"/>
       <c r="U60" s="1763" t="n"/>
       <c r="V60" s="1763">
-        <f>'Recept-voorblad'!$E$92*(V49/100*100)</f>
+        <f>'Recipe Sheet'!$E$92*(V49/100*100)</f>
         <v/>
       </c>
       <c r="W60" s="1602" t="inlineStr">
@@ -27192,7 +27192,7 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="G18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Bodemklep,Standpijp"</formula1>
+      <formula1>"Bottom Valve,Standpipe"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="R62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -27254,7 +27254,7 @@
     <row r="1" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A1" s="1826" t="inlineStr">
         <is>
-          <t>Afvullen</t>
+          <t xml:space="preserve">Filling</t>
         </is>
       </c>
       <c r="B1" s="1106" t="n"/>
@@ -27298,21 +27298,21 @@
     <row r="3" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A3" s="1981" t="inlineStr">
         <is>
-          <t>Naam bier</t>
+          <t xml:space="preserve">Beer Name</t>
         </is>
       </c>
       <c r="B3" s="1076" t="n"/>
       <c r="C3" s="1355">
-        <f>Verwerking!C3</f>
+        <f>Processing!C3</f>
         <v/>
       </c>
       <c r="D3" s="1981" t="inlineStr">
         <is>
-          <t>Batchnummer:</t>
+          <t xml:space="preserve">Batch No.:</t>
         </is>
       </c>
       <c r="E3" s="1982">
-        <f>'Recept-voorblad'!K3</f>
+        <f>'Recipe Sheet'!K3</f>
         <v/>
       </c>
       <c r="F3" s="1075" t="n"/>
@@ -27320,7 +27320,7 @@
       <c r="H3" s="1983" t="n"/>
       <c r="I3" s="1984" t="inlineStr">
         <is>
-          <t>Afvullingen</t>
+          <t xml:space="preserve">Filling Runs</t>
         </is>
       </c>
       <c r="J3" s="1075" t="n"/>
@@ -27356,19 +27356,19 @@
     <row r="5" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A5" s="1985" t="inlineStr">
         <is>
-          <t>Productie opdracht specificaties</t>
+          <t xml:space="preserve">Production Order Specifications</t>
         </is>
       </c>
       <c r="B5" s="1986" t="n"/>
       <c r="C5" s="1986" t="n"/>
       <c r="D5" s="1987" t="inlineStr">
         <is>
-          <t>controleur</t>
+          <t xml:space="preserve">Checked By</t>
         </is>
       </c>
       <c r="E5" s="1988" t="inlineStr">
         <is>
-          <t>Bier risico</t>
+          <t xml:space="preserve">Beer Risk Category</t>
         </is>
       </c>
       <c r="F5" s="1114" t="n"/>
@@ -27380,46 +27380,46 @@
       <c r="L5" s="1076" t="n"/>
       <c r="M5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="N5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="O5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="P5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="Q5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="R5" s="1991" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A6" s="1992" t="inlineStr">
         <is>
-          <t>EAN doos fles 24x33cl:</t>
+          <t xml:space="preserve">EAN Box Bottle 24x33cl:</t>
         </is>
       </c>
       <c r="B6" s="1115" t="n"/>
       <c r="C6" s="1993" t="n"/>
       <c r="D6" s="1994" t="n"/>
       <c r="E6" s="1995">
-        <f>'Recept-voorblad'!N17</f>
+        <f>'Recipe Sheet'!N17</f>
         <v/>
       </c>
       <c r="F6" s="1106" t="n"/>
@@ -27437,7 +27437,7 @@
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A7" s="1992" t="inlineStr">
         <is>
-          <t>EAN doos fles 12x33cl:</t>
+          <t xml:space="preserve">EAN Box Bottle 12x33cl:</t>
         </is>
       </c>
       <c r="B7" s="1115" t="n"/>
@@ -27451,39 +27451,39 @@
       <c r="L7" s="1083" t="n"/>
       <c r="M7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="N7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="O7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="P7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="Q7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="R7" s="1991" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A8" s="1992" t="inlineStr">
         <is>
-          <t>EAN doos blik 24x33cl:</t>
+          <t xml:space="preserve">EAN Box Can 24x33cl:</t>
         </is>
       </c>
       <c r="B8" s="1115" t="n"/>
@@ -27505,7 +27505,7 @@
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A9" s="1992" t="inlineStr">
         <is>
-          <t>EAN doos blik 12x33cl:</t>
+          <t xml:space="preserve">EAN Box Can 12x33cl:</t>
         </is>
       </c>
       <c r="B9" s="1115" t="n"/>
@@ -27519,39 +27519,39 @@
       <c r="L9" s="1083" t="n"/>
       <c r="M9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
       <c r="N9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
       <c r="O9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
       <c r="P9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
       <c r="Q9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
       <c r="R9" s="1291" t="inlineStr">
         <is>
-          <t>Start Afvul</t>
+          <t xml:space="preserve">Start Filling</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A10" s="1992" t="inlineStr">
         <is>
-          <t>Codering fles:</t>
+          <t xml:space="preserve">Bottle Coding:</t>
         </is>
       </c>
       <c r="B10" s="1115" t="n"/>
@@ -27585,7 +27585,7 @@
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A11" s="1992" t="inlineStr">
         <is>
-          <t>Codering blik:</t>
+          <t xml:space="preserve">Can Coding:</t>
         </is>
       </c>
       <c r="B11" s="1115" t="n"/>
@@ -27596,39 +27596,39 @@
       <c r="L11" s="1083" t="n"/>
       <c r="M11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
       <c r="N11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
       <c r="O11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
       <c r="P11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
       <c r="Q11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
       <c r="R11" s="2002" t="inlineStr">
         <is>
-          <t>Einde Afvul</t>
+          <t xml:space="preserve">End Filling</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A12" s="1992" t="inlineStr">
         <is>
-          <t>Codering vat:</t>
+          <t xml:space="preserve">Keg Coding:</t>
         </is>
       </c>
       <c r="B12" s="1115" t="n"/>
@@ -27657,7 +27657,7 @@
     <row r="13" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A13" s="1099" t="inlineStr">
         <is>
-          <t>Dag nummer</t>
+          <t xml:space="preserve">Day Number</t>
         </is>
       </c>
       <c r="C13" s="2003">
@@ -27668,7 +27668,7 @@
       <c r="H13" s="1217" t="n"/>
       <c r="I13" s="2005" t="inlineStr">
         <is>
-          <t>Afgevuld door:</t>
+          <t xml:space="preserve">Filled By:</t>
         </is>
       </c>
       <c r="J13" s="1114" t="n"/>
@@ -27684,7 +27684,7 @@
     <row r="14" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A14" s="1988" t="inlineStr">
         <is>
-          <t>Productie opdracht</t>
+          <t xml:space="preserve">Production Order</t>
         </is>
       </c>
       <c r="B14" s="1114" t="n"/>
@@ -27713,7 +27713,7 @@
     <row r="15" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A15" s="2010" t="inlineStr">
         <is>
-          <t>Fles Afvul 1,</t>
+          <t xml:space="preserve">Bottle Filling 1</t>
         </is>
       </c>
       <c r="B15" s="1114" t="n"/>
@@ -27737,14 +27737,14 @@
     <row r="16" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A16" s="2012" t="inlineStr">
         <is>
-          <t>Flessoort:</t>
+          <t xml:space="preserve">Bottle Type:</t>
         </is>
       </c>
       <c r="B16" s="2012" t="n"/>
       <c r="C16" s="1904" t="n"/>
       <c r="D16" s="2013" t="inlineStr">
         <is>
-          <t>Doossoort:</t>
+          <t xml:space="preserve">Box Type:</t>
         </is>
       </c>
       <c r="E16" s="1904" t="n"/>
@@ -27753,7 +27753,7 @@
       <c r="H16" s="1095" t="n"/>
       <c r="I16" s="2014" t="inlineStr">
         <is>
-          <t>Monstername door:</t>
+          <t xml:space="preserve">Sampled By:</t>
         </is>
       </c>
       <c r="J16" s="1114" t="n"/>
@@ -27769,14 +27769,14 @@
     <row r="17" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A17" s="2012" t="inlineStr">
         <is>
-          <t>Etiketten:</t>
+          <t xml:space="preserve">Labels:</t>
         </is>
       </c>
       <c r="B17" s="2012" t="n"/>
       <c r="C17" s="1904" t="n"/>
       <c r="D17" s="2013" t="inlineStr">
         <is>
-          <t>Codering doos:</t>
+          <t xml:space="preserve">Box Coding:</t>
         </is>
       </c>
       <c r="E17" s="1904" t="n"/>
@@ -27785,7 +27785,7 @@
       <c r="H17" s="2004" t="n"/>
       <c r="I17" s="2015" t="inlineStr">
         <is>
-          <t>Controle 1e verpakking (twee operators):</t>
+          <t xml:space="preserve">First Pack Check (two operators):</t>
         </is>
       </c>
       <c r="J17" s="1114" t="n"/>
@@ -27801,14 +27801,14 @@
     <row r="18" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A18" s="2012" t="inlineStr">
         <is>
-          <t>Codering fles:</t>
+          <t xml:space="preserve">Bottle Coding:</t>
         </is>
       </c>
       <c r="B18" s="2012" t="n"/>
       <c r="C18" s="1904" t="n"/>
       <c r="D18" s="2013" t="inlineStr">
         <is>
-          <t>Ean code doos:</t>
+          <t xml:space="preserve">Box EAN:</t>
         </is>
       </c>
       <c r="E18" s="1904" t="n"/>
@@ -27817,7 +27817,7 @@
       <c r="H18" s="1217" t="n"/>
       <c r="I18" s="2014" t="inlineStr">
         <is>
-          <t>Vulpijp-detectiecontrole 1e verpakking:</t>
+          <t xml:space="preserve">Filling Tube Detection Check First Pack:</t>
         </is>
       </c>
       <c r="J18" s="1114" t="n"/>
@@ -27833,14 +27833,14 @@
     <row r="19" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A19" s="2015" t="inlineStr">
         <is>
-          <t>Kroonkurk:</t>
+          <t xml:space="preserve">Crown Cap:</t>
         </is>
       </c>
       <c r="B19" s="2015" t="n"/>
       <c r="C19" s="1904" t="n"/>
       <c r="D19" s="2016" t="inlineStr">
         <is>
-          <t>Logo doos:</t>
+          <t xml:space="preserve">Box Logo:</t>
         </is>
       </c>
       <c r="E19" s="2017" t="n"/>
@@ -27849,7 +27849,7 @@
       <c r="H19" s="1217" t="n"/>
       <c r="I19" s="2015" t="inlineStr">
         <is>
-          <t>Vulpijp-detectiecontrole einde batch:</t>
+          <t xml:space="preserve">Filling Tube Detection Check End Of Batch:</t>
         </is>
       </c>
       <c r="J19" s="1114" t="n"/>
@@ -27865,7 +27865,7 @@
     <row r="20" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A20" s="2010" t="inlineStr">
         <is>
-          <t>Fles Afvul 2,</t>
+          <t xml:space="preserve">Bottle Filling 2</t>
         </is>
       </c>
       <c r="B20" s="2010" t="n"/>
@@ -27877,7 +27877,7 @@
       <c r="H20" s="1217" t="n"/>
       <c r="I20" s="2014" t="inlineStr">
         <is>
-          <t>Klapflessen</t>
+          <t xml:space="preserve">Bursting Bottles</t>
         </is>
       </c>
       <c r="J20" s="1114" t="n"/>
@@ -27893,14 +27893,14 @@
     <row r="21" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A21" s="2012" t="inlineStr">
         <is>
-          <t>Flessoort:</t>
+          <t xml:space="preserve">Bottle Type:</t>
         </is>
       </c>
       <c r="B21" s="2012" t="n"/>
       <c r="C21" s="1904" t="n"/>
       <c r="D21" s="2013" t="inlineStr">
         <is>
-          <t>Doossoort:</t>
+          <t xml:space="preserve">Box Type:</t>
         </is>
       </c>
       <c r="E21" s="2018" t="n"/>
@@ -27909,7 +27909,7 @@
       <c r="H21" s="1095" t="n"/>
       <c r="I21" s="2020" t="inlineStr">
         <is>
-          <t>Klapfles beheerst?</t>
+          <t xml:space="preserve">Bottle Bursts Under Control?</t>
         </is>
       </c>
       <c r="J21" s="1114" t="n"/>
@@ -27964,14 +27964,14 @@
     <row r="22" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A22" s="2012" t="inlineStr">
         <is>
-          <t>Etiketten:</t>
+          <t xml:space="preserve">Labels:</t>
         </is>
       </c>
       <c r="B22" s="2012" t="n"/>
       <c r="C22" s="1904" t="n"/>
       <c r="D22" s="2013" t="inlineStr">
         <is>
-          <t>Codering doos:</t>
+          <t xml:space="preserve">Box Coding:</t>
         </is>
       </c>
       <c r="E22" s="1904" t="n"/>
@@ -27997,14 +27997,14 @@
     <row r="23" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A23" s="2012" t="inlineStr">
         <is>
-          <t>Codering fles:</t>
+          <t xml:space="preserve">Bottle Coding:</t>
         </is>
       </c>
       <c r="B23" s="2012" t="n"/>
       <c r="C23" s="1904" t="n"/>
       <c r="D23" s="2013" t="inlineStr">
         <is>
-          <t>Ean code doos:</t>
+          <t xml:space="preserve">Box EAN:</t>
         </is>
       </c>
       <c r="E23" s="1904" t="n"/>
@@ -28023,7 +28023,7 @@
       </c>
       <c r="K23" s="2023" t="inlineStr">
         <is>
-          <t>spec,</t>
+          <t xml:space="preserve">Spec</t>
         </is>
       </c>
       <c r="L23" s="2024" t="inlineStr">
@@ -28033,32 +28033,32 @@
       </c>
       <c r="M23" s="2025" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="N23" s="2026" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="O23" s="2026" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="P23" s="2026" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="Q23" s="2026" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="R23" s="2026" t="inlineStr">
         <is>
-          <t>waarde</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="T23" s="1343" t="inlineStr">
@@ -28080,14 +28080,14 @@
     <row r="24" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A24" s="2015" t="inlineStr">
         <is>
-          <t>Kroonkurk:</t>
+          <t xml:space="preserve">Crown Cap:</t>
         </is>
       </c>
       <c r="B24" s="2015" t="n"/>
       <c r="C24" s="1904" t="n"/>
       <c r="D24" s="2016" t="inlineStr">
         <is>
-          <t>Logo doos:</t>
+          <t xml:space="preserve">Box Logo:</t>
         </is>
       </c>
       <c r="E24" s="2017" t="n"/>
@@ -28096,7 +28096,7 @@
       <c r="H24" s="1095" t="n"/>
       <c r="I24" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J24" s="2028" t="n"/>
@@ -28123,7 +28123,7 @@
     <row r="25" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A25" s="2010" t="inlineStr">
         <is>
-          <t>Fles Afvul 3,</t>
+          <t xml:space="preserve">Bottle Filling 3</t>
         </is>
       </c>
       <c r="B25" s="2010" t="n"/>
@@ -28135,7 +28135,7 @@
       <c r="H25" s="2004" t="n"/>
       <c r="I25" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 1</t>
+          <t xml:space="preserve">TPO Bottle / Can 1</t>
         </is>
       </c>
       <c r="J25" s="1983" t="inlineStr">
@@ -28144,7 +28144,7 @@
         </is>
       </c>
       <c r="K25" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L25" s="2033" t="inlineStr">
@@ -28173,14 +28173,14 @@
     <row r="26" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A26" s="2012" t="inlineStr">
         <is>
-          <t>Flessoort:</t>
+          <t xml:space="preserve">Bottle Type:</t>
         </is>
       </c>
       <c r="B26" s="2012" t="n"/>
       <c r="C26" s="1904" t="n"/>
       <c r="D26" s="2013" t="inlineStr">
         <is>
-          <t>Doossoort:</t>
+          <t xml:space="preserve">Box Type:</t>
         </is>
       </c>
       <c r="E26" s="2018" t="n"/>
@@ -28189,7 +28189,7 @@
       <c r="H26" s="2036" t="n"/>
       <c r="I26" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 1</t>
+          <t xml:space="preserve">HSO Bottle / Can 1</t>
         </is>
       </c>
       <c r="J26" s="1983" t="inlineStr">
@@ -28198,11 +28198,11 @@
         </is>
       </c>
       <c r="K26" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L26" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M26" s="2034" t="n"/>
@@ -28226,14 +28226,14 @@
     <row r="27" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A27" s="2012" t="inlineStr">
         <is>
-          <t>Etiketten:</t>
+          <t xml:space="preserve">Labels:</t>
         </is>
       </c>
       <c r="B27" s="2012" t="n"/>
       <c r="C27" s="1904" t="n"/>
       <c r="D27" s="2013" t="inlineStr">
         <is>
-          <t>Codering doos:</t>
+          <t xml:space="preserve">Box Coding:</t>
         </is>
       </c>
       <c r="E27" s="1904" t="n"/>
@@ -28242,7 +28242,7 @@
       <c r="H27" s="2036" t="n"/>
       <c r="I27" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 1</t>
+          <t xml:space="preserve">DO Bottle / Can 1</t>
         </is>
       </c>
       <c r="J27" s="1983" t="inlineStr">
@@ -28251,7 +28251,7 @@
         </is>
       </c>
       <c r="K27" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L27" s="2033" t="n"/>
@@ -28276,14 +28276,14 @@
     <row r="28" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A28" s="2012" t="inlineStr">
         <is>
-          <t>Codering fles:</t>
+          <t xml:space="preserve">Bottle Coding:</t>
         </is>
       </c>
       <c r="B28" s="2012" t="n"/>
       <c r="C28" s="1904" t="n"/>
       <c r="D28" s="2013" t="inlineStr">
         <is>
-          <t>Ean code doos:</t>
+          <t xml:space="preserve">Box EAN:</t>
         </is>
       </c>
       <c r="E28" s="1904" t="n"/>
@@ -28319,14 +28319,14 @@
     <row r="29" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A29" s="2015" t="inlineStr">
         <is>
-          <t>Kroonkurk:</t>
+          <t xml:space="preserve">Crown Cap:</t>
         </is>
       </c>
       <c r="B29" s="2015" t="n"/>
       <c r="C29" s="1904" t="n"/>
       <c r="D29" s="2016" t="inlineStr">
         <is>
-          <t>Logo doos:</t>
+          <t xml:space="preserve">Box Logo:</t>
         </is>
       </c>
       <c r="E29" s="2017" t="n"/>
@@ -28335,7 +28335,7 @@
       <c r="H29" s="2039" t="n"/>
       <c r="I29" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J29" s="1983" t="n"/>
@@ -28362,7 +28362,7 @@
     <row r="30" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A30" s="2010" t="inlineStr">
         <is>
-          <t>Blik Afvul 1,</t>
+          <t xml:space="preserve">Can Filling 1</t>
         </is>
       </c>
       <c r="B30" s="2010" t="n"/>
@@ -28374,7 +28374,7 @@
       <c r="H30" s="2039" t="n"/>
       <c r="I30" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J30" s="1983" t="n"/>
@@ -28401,14 +28401,14 @@
     <row r="31" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A31" s="2012" t="inlineStr">
         <is>
-          <t>bliksoort:</t>
+          <t xml:space="preserve">Can Type:</t>
         </is>
       </c>
       <c r="B31" s="2012" t="n"/>
       <c r="C31" s="1904" t="n"/>
       <c r="D31" s="2013" t="inlineStr">
         <is>
-          <t>Doossoort:</t>
+          <t xml:space="preserve">Box Type:</t>
         </is>
       </c>
       <c r="E31" s="2018" t="n"/>
@@ -28417,7 +28417,7 @@
       <c r="H31" s="2039" t="n"/>
       <c r="I31" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 1 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 1 (20°C)</t>
         </is>
       </c>
       <c r="J31" s="1983" t="inlineStr">
@@ -28426,11 +28426,11 @@
         </is>
       </c>
       <c r="K31" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L31" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M31" s="2034" t="n"/>
@@ -28454,14 +28454,14 @@
     <row r="32" ht="15.75" customFormat="1" customHeight="1" s="1099">
       <c r="A32" s="2012" t="inlineStr">
         <is>
-          <t>Etiketten:</t>
+          <t xml:space="preserve">Labels:</t>
         </is>
       </c>
       <c r="B32" s="2012" t="n"/>
       <c r="C32" s="1904" t="n"/>
       <c r="D32" s="2013" t="inlineStr">
         <is>
-          <t>Codering doos:</t>
+          <t xml:space="preserve">Box Coding:</t>
         </is>
       </c>
       <c r="E32" s="1904" t="n"/>
@@ -28470,7 +28470,7 @@
       <c r="H32" s="2041" t="n"/>
       <c r="I32" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 1</t>
+          <t xml:space="preserve">CO2 Keg 1</t>
         </is>
       </c>
       <c r="J32" s="2043" t="inlineStr">
@@ -28479,11 +28479,11 @@
         </is>
       </c>
       <c r="K32" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L32" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M32" s="2044" t="n"/>
@@ -28507,14 +28507,14 @@
     <row r="33" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A33" s="2012" t="inlineStr">
         <is>
-          <t>Codering blik:</t>
+          <t xml:space="preserve">Can Coding:</t>
         </is>
       </c>
       <c r="B33" s="2012" t="n"/>
       <c r="C33" s="1904" t="n"/>
       <c r="D33" s="2013" t="inlineStr">
         <is>
-          <t>Ean code doos:</t>
+          <t xml:space="preserve">Box EAN:</t>
         </is>
       </c>
       <c r="E33" s="1904" t="n"/>
@@ -28523,7 +28523,7 @@
       <c r="H33" s="2045" t="n"/>
       <c r="I33" s="2046" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 1</t>
+          <t xml:space="preserve">O2 Keg 1</t>
         </is>
       </c>
       <c r="J33" s="2047" t="inlineStr">
@@ -28532,11 +28532,11 @@
         </is>
       </c>
       <c r="K33" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L33" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M33" s="2050" t="n"/>
@@ -28560,14 +28560,14 @@
     <row r="34" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A34" s="2015" t="inlineStr">
         <is>
-          <t>deksel:</t>
+          <t xml:space="preserve">Can End:</t>
         </is>
       </c>
       <c r="B34" s="2015" t="n"/>
       <c r="C34" s="1904" t="n"/>
       <c r="D34" s="2016" t="inlineStr">
         <is>
-          <t>Logo doos:</t>
+          <t xml:space="preserve">Box Logo:</t>
         </is>
       </c>
       <c r="E34" s="2017" t="n"/>
@@ -28576,7 +28576,7 @@
       <c r="H34" s="2051" t="n"/>
       <c r="I34" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J34" s="2028" t="n"/>
@@ -28603,7 +28603,7 @@
     <row r="35" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A35" s="2010" t="inlineStr">
         <is>
-          <t>Blik Afvul 2,</t>
+          <t xml:space="preserve">Can Filling 2</t>
         </is>
       </c>
       <c r="B35" s="2010" t="n"/>
@@ -28615,7 +28615,7 @@
       <c r="H35" s="2051" t="n"/>
       <c r="I35" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 2</t>
+          <t xml:space="preserve">TPO Bottle / Can 2</t>
         </is>
       </c>
       <c r="J35" s="1983" t="inlineStr">
@@ -28624,7 +28624,7 @@
         </is>
       </c>
       <c r="K35" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L35" s="2033" t="inlineStr">
@@ -28653,14 +28653,14 @@
     <row r="36" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A36" s="2012" t="inlineStr">
         <is>
-          <t>bliksoort:</t>
+          <t xml:space="preserve">Can Type:</t>
         </is>
       </c>
       <c r="B36" s="2012" t="n"/>
       <c r="C36" s="1904" t="n"/>
       <c r="D36" s="2013" t="inlineStr">
         <is>
-          <t>Doossoort:</t>
+          <t xml:space="preserve">Box Type:</t>
         </is>
       </c>
       <c r="E36" s="2018" t="n"/>
@@ -28669,7 +28669,7 @@
       <c r="H36" s="2052" t="n"/>
       <c r="I36" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 2</t>
+          <t xml:space="preserve">HSO Bottle / Can 2</t>
         </is>
       </c>
       <c r="J36" s="1983" t="inlineStr">
@@ -28678,11 +28678,11 @@
         </is>
       </c>
       <c r="K36" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L36" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M36" s="2034" t="n"/>
@@ -28706,14 +28706,14 @@
     <row r="37" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A37" s="2012" t="inlineStr">
         <is>
-          <t>Etiketten:</t>
+          <t xml:space="preserve">Labels:</t>
         </is>
       </c>
       <c r="B37" s="2012" t="n"/>
       <c r="C37" s="1904" t="n"/>
       <c r="D37" s="2013" t="inlineStr">
         <is>
-          <t>Codering doos:</t>
+          <t xml:space="preserve">Box Coding:</t>
         </is>
       </c>
       <c r="E37" s="1904" t="n"/>
@@ -28722,7 +28722,7 @@
       <c r="H37" s="2052" t="n"/>
       <c r="I37" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 2</t>
+          <t xml:space="preserve">DO Bottle / Can 2</t>
         </is>
       </c>
       <c r="J37" s="1983" t="inlineStr">
@@ -28731,7 +28731,7 @@
         </is>
       </c>
       <c r="K37" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L37" s="2033" t="n"/>
@@ -28756,14 +28756,14 @@
     <row r="38" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A38" s="2012" t="inlineStr">
         <is>
-          <t>Codering blik:</t>
+          <t xml:space="preserve">Can Coding:</t>
         </is>
       </c>
       <c r="B38" s="2012" t="n"/>
       <c r="C38" s="1904" t="n"/>
       <c r="D38" s="2013" t="inlineStr">
         <is>
-          <t>Ean code doos:</t>
+          <t xml:space="preserve">Box EAN:</t>
         </is>
       </c>
       <c r="E38" s="1904" t="n"/>
@@ -28798,14 +28798,14 @@
     <row r="39" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A39" s="2015" t="inlineStr">
         <is>
-          <t>deksel:</t>
+          <t xml:space="preserve">Can End:</t>
         </is>
       </c>
       <c r="B39" s="2015" t="n"/>
       <c r="C39" s="1904" t="n"/>
       <c r="D39" s="2016" t="inlineStr">
         <is>
-          <t>Logo doos:</t>
+          <t xml:space="preserve">Box Logo:</t>
         </is>
       </c>
       <c r="E39" s="2017" t="n"/>
@@ -28813,7 +28813,7 @@
       <c r="G39" s="2017" t="n"/>
       <c r="I39" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J39" s="1983" t="n"/>
@@ -28840,7 +28840,7 @@
     <row r="40" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A40" s="2010" t="inlineStr">
         <is>
-          <t>Fust Afvul 1,</t>
+          <t xml:space="preserve">Keg Filling 1</t>
         </is>
       </c>
       <c r="B40" s="2010" t="n"/>
@@ -28851,7 +28851,7 @@
       <c r="G40" s="2010" t="n"/>
       <c r="I40" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J40" s="1983" t="n"/>
@@ -28878,7 +28878,7 @@
     <row r="41" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A41" s="2012" t="inlineStr">
         <is>
-          <t>Fustmaat:</t>
+          <t xml:space="preserve">Keg Size:</t>
         </is>
       </c>
       <c r="B41" s="2012" t="n"/>
@@ -28893,7 +28893,7 @@
       <c r="G41" s="2017" t="n"/>
       <c r="I41" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 2 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 2 (20°C)</t>
         </is>
       </c>
       <c r="J41" s="1983" t="inlineStr">
@@ -28902,11 +28902,11 @@
         </is>
       </c>
       <c r="K41" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L41" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M41" s="2034" t="n"/>
@@ -28930,7 +28930,7 @@
     <row r="42" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A42" s="2012" t="inlineStr">
         <is>
-          <t>Ean code:</t>
+          <t xml:space="preserve">EAN:</t>
         </is>
       </c>
       <c r="B42" s="2012" t="n"/>
@@ -28941,7 +28941,7 @@
       <c r="G42" s="2053" t="n"/>
       <c r="I42" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 2</t>
+          <t xml:space="preserve">CO2 Keg 2</t>
         </is>
       </c>
       <c r="J42" s="2043" t="inlineStr">
@@ -28950,11 +28950,11 @@
         </is>
       </c>
       <c r="K42" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L42" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M42" s="2044" t="n"/>
@@ -28978,7 +28978,7 @@
     <row r="43" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A43" s="2010" t="inlineStr">
         <is>
-          <t>Fust Afvul 2,</t>
+          <t xml:space="preserve">Keg Filling 2</t>
         </is>
       </c>
       <c r="B43" s="2010" t="n"/>
@@ -28989,7 +28989,7 @@
       <c r="G43" s="2010" t="n"/>
       <c r="I43" s="2046" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 2</t>
+          <t xml:space="preserve">O2 Keg 2</t>
         </is>
       </c>
       <c r="J43" s="2047" t="inlineStr">
@@ -28998,11 +28998,11 @@
         </is>
       </c>
       <c r="K43" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L43" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M43" s="2050" t="n"/>
@@ -29026,7 +29026,7 @@
     <row r="44" ht="18.75" customFormat="1" customHeight="1" s="1099">
       <c r="A44" s="2012" t="inlineStr">
         <is>
-          <t>Fustmaat:</t>
+          <t xml:space="preserve">Keg Size:</t>
         </is>
       </c>
       <c r="B44" s="2012" t="n"/>
@@ -29041,7 +29041,7 @@
       <c r="G44" s="2017" t="n"/>
       <c r="I44" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J44" s="2028" t="n"/>
@@ -29068,7 +29068,7 @@
     <row r="45" ht="18.75" customFormat="1" customHeight="1" s="1099">
       <c r="A45" s="2012" t="inlineStr">
         <is>
-          <t>Ean code:</t>
+          <t xml:space="preserve">EAN:</t>
         </is>
       </c>
       <c r="B45" s="2012" t="n"/>
@@ -29079,7 +29079,7 @@
       <c r="G45" s="2053" t="n"/>
       <c r="I45" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 3</t>
+          <t xml:space="preserve">TPO Bottle / Can 3</t>
         </is>
       </c>
       <c r="J45" s="1983" t="inlineStr">
@@ -29088,7 +29088,7 @@
         </is>
       </c>
       <c r="K45" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L45" s="2033" t="inlineStr">
@@ -29121,7 +29121,7 @@
     <row r="46" ht="18.75" customFormat="1" customHeight="1" s="1099">
       <c r="I46" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 3</t>
+          <t xml:space="preserve">HSO Bottle / Can 3</t>
         </is>
       </c>
       <c r="J46" s="1983" t="inlineStr">
@@ -29130,11 +29130,11 @@
         </is>
       </c>
       <c r="K46" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L46" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M46" s="2034" t="n"/>
@@ -29160,7 +29160,7 @@
     <row r="47" ht="18.75" customFormat="1" customHeight="1" s="1099">
       <c r="A47" s="2058" t="inlineStr">
         <is>
-          <t>Opmerkingen productie opdracht:</t>
+          <t xml:space="preserve">Production Order Comments:</t>
         </is>
       </c>
       <c r="B47" s="1106" t="n"/>
@@ -29171,7 +29171,7 @@
       <c r="G47" s="2060" t="n"/>
       <c r="I47" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 3</t>
+          <t xml:space="preserve">DO Bottle / Can 3</t>
         </is>
       </c>
       <c r="J47" s="1983" t="inlineStr">
@@ -29180,7 +29180,7 @@
         </is>
       </c>
       <c r="K47" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L47" s="2033" t="n"/>
@@ -29206,7 +29206,7 @@
     </row>
     <row r="48" ht="18.75" customFormat="1" customHeight="1" s="1099">
       <c r="A48" s="2063">
-        <f>IF(Verwerking!N7=5.6," ","LET OP The CO2 concentration can/bottle is " &amp;K31 &amp; " g/l ")</f>
+        <f>IF(Processing!N7=5.6," ","ATTENTION: The CO2 concentration can/bottle is " &amp;K31 &amp; " g/l ")</f>
         <v/>
       </c>
       <c r="B48" s="1078" t="n"/>
@@ -29253,7 +29253,7 @@
       <c r="G49" s="1087" t="n"/>
       <c r="I49" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J49" s="1983" t="n"/>
@@ -29286,7 +29286,7 @@
       <c r="G50" s="1094" t="n"/>
       <c r="I50" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J50" s="1983" t="n"/>
@@ -29309,7 +29309,7 @@
     <row r="51" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I51" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 3 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 3 (20°C)</t>
         </is>
       </c>
       <c r="J51" s="1983" t="inlineStr">
@@ -29318,11 +29318,11 @@
         </is>
       </c>
       <c r="K51" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L51" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M51" s="2034" t="n"/>
@@ -29353,17 +29353,17 @@
       <c r="B52" s="2065" t="n"/>
       <c r="C52" s="2066" t="inlineStr">
         <is>
-          <t>beschibaarheid</t>
+          <t xml:space="preserve">Availability</t>
         </is>
       </c>
       <c r="D52" s="2066" t="inlineStr">
         <is>
-          <t>prestatie</t>
+          <t xml:space="preserve">Performance</t>
         </is>
       </c>
       <c r="E52" s="2066" t="inlineStr">
         <is>
-          <t>kwaliteit</t>
+          <t xml:space="preserve">Quality</t>
         </is>
       </c>
       <c r="F52" s="2066" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="I52" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 3</t>
+          <t xml:space="preserve">CO2 Keg 3</t>
         </is>
       </c>
       <c r="J52" s="2043" t="inlineStr">
@@ -29382,11 +29382,11 @@
         </is>
       </c>
       <c r="K52" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L52" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M52" s="2044" t="n"/>
@@ -29411,7 +29411,7 @@
     <row r="53" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A53" s="1384" t="inlineStr">
         <is>
-          <t>fles</t>
+          <t xml:space="preserve">bottle</t>
         </is>
       </c>
       <c r="B53" s="2067" t="n"/>
@@ -29421,7 +29421,7 @@
       <c r="F53" s="2068" t="n"/>
       <c r="I53" s="2046" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 3</t>
+          <t xml:space="preserve">O2 Keg 3</t>
         </is>
       </c>
       <c r="J53" s="2047" t="inlineStr">
@@ -29430,11 +29430,11 @@
         </is>
       </c>
       <c r="K53" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L53" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M53" s="2050" t="n"/>
@@ -29470,7 +29470,7 @@
       <c r="F54" s="2070" t="n"/>
       <c r="I54" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J54" s="2028" t="n"/>
@@ -29499,7 +29499,7 @@
     <row r="55" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A55" s="1402" t="inlineStr">
         <is>
-          <t>vat</t>
+          <t xml:space="preserve">keg</t>
         </is>
       </c>
       <c r="B55" s="2069" t="n"/>
@@ -29509,7 +29509,7 @@
       <c r="F55" s="2070" t="n"/>
       <c r="I55" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 4</t>
+          <t xml:space="preserve">TPO Bottle / Can 4</t>
         </is>
       </c>
       <c r="J55" s="1983" t="inlineStr">
@@ -29518,7 +29518,7 @@
         </is>
       </c>
       <c r="K55" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L55" s="2033" t="inlineStr">
@@ -29555,7 +29555,7 @@
       <c r="F56" s="2073" t="n"/>
       <c r="I56" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 4</t>
+          <t xml:space="preserve">HSO Bottle / Can 4</t>
         </is>
       </c>
       <c r="J56" s="1983" t="inlineStr">
@@ -29564,11 +29564,11 @@
         </is>
       </c>
       <c r="K56" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L56" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M56" s="2034" t="n"/>
@@ -29594,7 +29594,7 @@
     <row r="57" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I57" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 4</t>
+          <t xml:space="preserve">DO Bottle / Can 4</t>
         </is>
       </c>
       <c r="J57" s="1983" t="inlineStr">
@@ -29603,7 +29603,7 @@
         </is>
       </c>
       <c r="K57" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L57" s="2033" t="n"/>
@@ -29627,28 +29627,28 @@
     <row r="58" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A58" s="2065" t="inlineStr">
         <is>
-          <t>Verbruiken</t>
+          <t xml:space="preserve">Consumption</t>
         </is>
       </c>
       <c r="B58" s="2065" t="n"/>
       <c r="C58" s="2066" t="inlineStr">
         <is>
-          <t>leeg goed</t>
+          <t xml:space="preserve">Empties</t>
         </is>
       </c>
       <c r="D58" s="2066" t="inlineStr">
         <is>
-          <t>underfills</t>
+          <t xml:space="preserve">Underfills</t>
         </is>
       </c>
       <c r="E58" s="2066" t="inlineStr">
         <is>
-          <t>ongelabelled</t>
+          <t xml:space="preserve">Unlabelled</t>
         </is>
       </c>
       <c r="F58" s="2066" t="inlineStr">
         <is>
-          <t>verlies</t>
+          <t xml:space="preserve">Loss</t>
         </is>
       </c>
       <c r="I58" s="2040" t="inlineStr">
@@ -29684,23 +29684,23 @@
     <row r="59" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A59" s="1384" t="inlineStr">
         <is>
-          <t>fles</t>
+          <t xml:space="preserve">bottle</t>
         </is>
       </c>
       <c r="B59" s="2067" t="n"/>
       <c r="C59" s="2074">
-        <f>Afvulverslag!M48</f>
+        <f>'Filling Report'!M48</f>
         <v/>
       </c>
       <c r="D59" s="2068" t="n"/>
       <c r="E59" s="2068" t="n"/>
       <c r="F59" s="2075">
-        <f>Afvulverslag!R9</f>
+        <f>'Filling Report'!R9</f>
         <v/>
       </c>
       <c r="I59" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J59" s="1983" t="n"/>
@@ -29737,18 +29737,18 @@
       </c>
       <c r="B60" s="2069" t="n"/>
       <c r="C60" s="2076">
-        <f>Afvulverslag!M76</f>
+        <f>'Filling Report'!M76</f>
         <v/>
       </c>
       <c r="D60" s="2070" t="n"/>
       <c r="E60" s="2077">
-        <f>IFERROR(Afvulverslag!M81/Afvulverslag!K81,"")</f>
+        <f>IFERROR('Filling Report'!M81/'Filling Report'!K81,"")</f>
         <v/>
       </c>
       <c r="F60" s="2070" t="n"/>
       <c r="I60" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J60" s="1983" t="n"/>
@@ -29779,12 +29779,12 @@
     <row r="61" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A61" s="1402" t="inlineStr">
         <is>
-          <t>vat</t>
+          <t xml:space="preserve">keg</t>
         </is>
       </c>
       <c r="B61" s="2069" t="n"/>
       <c r="C61" s="2078">
-        <f>SUM(Afvulverslag!M85:M87,Afvulverslag!M89:M92)</f>
+        <f>SUM('Filling Report'!M85:M87,'Filling Report'!M89:M92)</f>
         <v/>
       </c>
       <c r="D61" s="2070" t="n"/>
@@ -29792,7 +29792,7 @@
       <c r="F61" s="2070" t="n"/>
       <c r="I61" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 4 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 4 (20°C)</t>
         </is>
       </c>
       <c r="J61" s="1983" t="inlineStr">
@@ -29801,11 +29801,11 @@
         </is>
       </c>
       <c r="K61" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L61" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M61" s="2034" t="n"/>
@@ -29827,7 +29827,7 @@
       <c r="F62" s="2073" t="n"/>
       <c r="I62" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 4</t>
+          <t xml:space="preserve">CO2 Keg 4</t>
         </is>
       </c>
       <c r="J62" s="2043" t="inlineStr">
@@ -29836,11 +29836,11 @@
         </is>
       </c>
       <c r="K62" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L62" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M62" s="2044" t="n"/>
@@ -29853,7 +29853,7 @@
     <row r="63" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="I63" s="2046" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 4</t>
+          <t xml:space="preserve">O2 Keg 4</t>
         </is>
       </c>
       <c r="J63" s="2047" t="inlineStr">
@@ -29862,11 +29862,11 @@
         </is>
       </c>
       <c r="K63" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L63" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M63" s="2050" t="n"/>
@@ -29906,7 +29906,7 @@
       <c r="G64" s="1340" t="n"/>
       <c r="I64" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J64" s="2028" t="n"/>
@@ -29922,7 +29922,7 @@
     <row r="65" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A65" s="1384" t="inlineStr">
         <is>
-          <t>CO2 fles/can</t>
+          <t xml:space="preserve">CO2 bottle/can</t>
         </is>
       </c>
       <c r="B65" s="2067" t="n"/>
@@ -29945,7 +29945,7 @@
       <c r="G65" s="1340" t="n"/>
       <c r="I65" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 5</t>
+          <t xml:space="preserve">TPO Bottle / Can 5</t>
         </is>
       </c>
       <c r="J65" s="1983" t="inlineStr">
@@ -29954,7 +29954,7 @@
         </is>
       </c>
       <c r="K65" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L65" s="2033" t="inlineStr">
@@ -29972,7 +29972,7 @@
     <row r="66" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A66" s="1402" t="inlineStr">
         <is>
-          <t>HSO fles/can</t>
+          <t xml:space="preserve">HSO bottle/can</t>
         </is>
       </c>
       <c r="B66" s="2069" t="n"/>
@@ -29995,7 +29995,7 @@
       <c r="G66" s="1340" t="n"/>
       <c r="I66" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 5</t>
+          <t xml:space="preserve">HSO Bottle / Can 5</t>
         </is>
       </c>
       <c r="J66" s="1983" t="inlineStr">
@@ -30004,11 +30004,11 @@
         </is>
       </c>
       <c r="K66" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L66" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M66" s="2084" t="n"/>
@@ -30021,7 +30021,7 @@
     <row r="67" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A67" s="1402" t="inlineStr">
         <is>
-          <t>DO fles/can</t>
+          <t xml:space="preserve">DO bottle/can</t>
         </is>
       </c>
       <c r="B67" s="2069" t="n"/>
@@ -30044,7 +30044,7 @@
       <c r="G67" s="1340" t="n"/>
       <c r="I67" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 5</t>
+          <t xml:space="preserve">DO Bottle / Can 5</t>
         </is>
       </c>
       <c r="J67" s="1983" t="inlineStr">
@@ -30053,7 +30053,7 @@
         </is>
       </c>
       <c r="K67" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L67" s="2033" t="n"/>
@@ -30067,7 +30067,7 @@
     <row r="68" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A68" s="1402" t="inlineStr">
         <is>
-          <t>TPO fles/can</t>
+          <t xml:space="preserve">TPO bottle/can</t>
         </is>
       </c>
       <c r="B68" s="2069" t="n"/>
@@ -30106,7 +30106,7 @@
     <row r="69" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="A69" s="2088" t="inlineStr">
         <is>
-          <t>CO2 fust</t>
+          <t xml:space="preserve">CO2 keg</t>
         </is>
       </c>
       <c r="B69" s="2089" t="n"/>
@@ -30129,7 +30129,7 @@
       <c r="G69" s="1340" t="n"/>
       <c r="I69" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J69" s="1983" t="n"/>
@@ -30145,7 +30145,7 @@
     <row r="70" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="A70" s="2088" t="inlineStr">
         <is>
-          <t>DO fust</t>
+          <t xml:space="preserve">DO keg</t>
         </is>
       </c>
       <c r="B70" s="2089" t="n"/>
@@ -30168,7 +30168,7 @@
       <c r="G70" s="1340" t="n"/>
       <c r="I70" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J70" s="1983" t="n"/>
@@ -30184,7 +30184,7 @@
     <row r="71" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I71" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 5 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 5 (20°C)</t>
         </is>
       </c>
       <c r="J71" s="1983" t="inlineStr">
@@ -30193,11 +30193,11 @@
         </is>
       </c>
       <c r="K71" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L71" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M71" s="2084" t="n"/>
@@ -30210,7 +30210,7 @@
     <row r="72" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I72" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 5</t>
+          <t xml:space="preserve">CO2 Keg 5</t>
         </is>
       </c>
       <c r="J72" s="2043" t="inlineStr">
@@ -30219,11 +30219,11 @@
         </is>
       </c>
       <c r="K72" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L72" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M72" s="2044" t="n"/>
@@ -30236,7 +30236,7 @@
     <row r="73" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I73" s="2042" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 5</t>
+          <t xml:space="preserve">O2 Keg 5</t>
         </is>
       </c>
       <c r="J73" s="2047" t="inlineStr">
@@ -30245,11 +30245,11 @@
         </is>
       </c>
       <c r="K73" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L73" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M73" s="2050" t="n"/>
@@ -30262,7 +30262,7 @@
     <row r="74" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I74" s="1383" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J74" s="2028" t="n"/>
@@ -30278,7 +30278,7 @@
     <row r="75" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I75" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 6</t>
+          <t xml:space="preserve">TPO Bottle / Can 6</t>
         </is>
       </c>
       <c r="J75" s="1983" t="inlineStr">
@@ -30287,7 +30287,7 @@
         </is>
       </c>
       <c r="K75" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L75" s="2033" t="inlineStr">
@@ -30305,7 +30305,7 @@
     <row r="76" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I76" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 6</t>
+          <t xml:space="preserve">HSO Bottle / Can 6</t>
         </is>
       </c>
       <c r="J76" s="1983" t="inlineStr">
@@ -30314,11 +30314,11 @@
         </is>
       </c>
       <c r="K76" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L76" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M76" s="2084" t="n"/>
@@ -30331,7 +30331,7 @@
     <row r="77" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I77" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 6</t>
+          <t xml:space="preserve">DO Bottle / Can 6</t>
         </is>
       </c>
       <c r="J77" s="1983" t="inlineStr">
@@ -30340,7 +30340,7 @@
         </is>
       </c>
       <c r="K77" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L77" s="2033" t="n"/>
@@ -30370,7 +30370,7 @@
     <row r="79" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I79" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J79" s="1983" t="n"/>
@@ -30386,7 +30386,7 @@
     <row r="80" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="I80" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J80" s="1983" t="n"/>
@@ -30402,7 +30402,7 @@
     <row r="81" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I81" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 6 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 6 (20°C)</t>
         </is>
       </c>
       <c r="J81" s="1983" t="inlineStr">
@@ -30411,11 +30411,11 @@
         </is>
       </c>
       <c r="K81" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L81" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M81" s="2084" t="n"/>
@@ -30428,7 +30428,7 @@
     <row r="82" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I82" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 6</t>
+          <t xml:space="preserve">CO2 Keg 6</t>
         </is>
       </c>
       <c r="J82" s="2043" t="inlineStr">
@@ -30437,11 +30437,11 @@
         </is>
       </c>
       <c r="K82" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L82" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M82" s="2044" t="n"/>
@@ -30454,7 +30454,7 @@
     <row r="83" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I83" s="2046" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 6</t>
+          <t xml:space="preserve">O2 Keg 6</t>
         </is>
       </c>
       <c r="J83" s="2047" t="inlineStr">
@@ -30463,11 +30463,11 @@
         </is>
       </c>
       <c r="K83" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L83" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M83" s="2050" t="n"/>
@@ -30480,7 +30480,7 @@
     <row r="84" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I84" s="1401" t="inlineStr">
         <is>
-          <t>time</t>
+          <t xml:space="preserve">Time</t>
         </is>
       </c>
       <c r="J84" s="2028" t="n"/>
@@ -30496,7 +30496,7 @@
     <row r="85" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I85" s="1401" t="inlineStr">
         <is>
-          <t>TPO Fles / Can 7</t>
+          <t xml:space="preserve">TPO Bottle / Can 7</t>
         </is>
       </c>
       <c r="J85" s="1983" t="inlineStr">
@@ -30505,7 +30505,7 @@
         </is>
       </c>
       <c r="K85" s="1131">
-        <f>'Recept-voorblad'!$M$16+'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$16+'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L85" s="2033" t="inlineStr">
@@ -30523,7 +30523,7 @@
     <row r="86" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I86" s="1401" t="inlineStr">
         <is>
-          <t>HSO Fles / Can 7</t>
+          <t xml:space="preserve">HSO Bottle / Can 7</t>
         </is>
       </c>
       <c r="J86" s="1983" t="inlineStr">
@@ -30532,11 +30532,11 @@
         </is>
       </c>
       <c r="K86" s="1131">
-        <f>'Recept-voorblad'!$M$16</f>
+        <f>'Recipe Sheet'!$M$16</f>
         <v/>
       </c>
       <c r="L86" s="2033">
-        <f>'Recept-voorblad'!$L$16</f>
+        <f>'Recipe Sheet'!$L$16</f>
         <v/>
       </c>
       <c r="M86" s="2084" t="n"/>
@@ -30549,7 +30549,7 @@
     <row r="87" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I87" s="1401" t="inlineStr">
         <is>
-          <t>DO Fles / Can 7</t>
+          <t xml:space="preserve">DO Bottle / Can 7</t>
         </is>
       </c>
       <c r="J87" s="1983" t="inlineStr">
@@ -30558,7 +30558,7 @@
         </is>
       </c>
       <c r="K87" s="1131">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L87" s="2033" t="n"/>
@@ -30588,7 +30588,7 @@
     <row r="89" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I89" s="2040" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J89" s="1983" t="n"/>
@@ -30604,7 +30604,7 @@
     <row r="90" ht="17.25" customFormat="1" customHeight="1" s="1099">
       <c r="I90" s="2040" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J90" s="1983" t="n"/>
@@ -30620,7 +30620,7 @@
     <row r="91" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I91" s="1401" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 7 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 7 (20°C)</t>
         </is>
       </c>
       <c r="J91" s="1983" t="inlineStr">
@@ -30629,11 +30629,11 @@
         </is>
       </c>
       <c r="K91" s="1127">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L91" s="2033">
-        <f>'Recept-voorblad'!$L$13</f>
+        <f>'Recipe Sheet'!$L$13</f>
         <v/>
       </c>
       <c r="M91" s="2084" t="n"/>
@@ -30646,7 +30646,7 @@
     <row r="92" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I92" s="2042" t="inlineStr">
         <is>
-          <t>CO2 Fust 7</t>
+          <t xml:space="preserve">CO2 Keg 7</t>
         </is>
       </c>
       <c r="J92" s="2043" t="inlineStr">
@@ -30655,11 +30655,11 @@
         </is>
       </c>
       <c r="K92" s="1127">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
       <c r="L92" s="2033">
-        <f>'Recept-voorblad'!$L$15</f>
+        <f>'Recipe Sheet'!$L$15</f>
         <v/>
       </c>
       <c r="M92" s="2044" t="n"/>
@@ -30672,7 +30672,7 @@
     <row r="93" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I93" s="2042" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 7</t>
+          <t xml:space="preserve">O2 Keg 7</t>
         </is>
       </c>
       <c r="J93" s="2047" t="inlineStr">
@@ -30681,11 +30681,11 @@
         </is>
       </c>
       <c r="K93" s="2048">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
       <c r="L93" s="2049">
-        <f>'Recept-voorblad'!$L$17</f>
+        <f>'Recipe Sheet'!$L$17</f>
         <v/>
       </c>
       <c r="M93" s="2050" t="n"/>
@@ -30702,7 +30702,7 @@
     <row r="98" ht="15" customFormat="1" customHeight="1" s="1099">
       <c r="I98" s="1425" t="inlineStr">
         <is>
-          <t>DO Fles / Can 1</t>
+          <t xml:space="preserve">DO Bottle / Can 1</t>
         </is>
       </c>
       <c r="J98" s="1521" t="inlineStr">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="K98" s="2092">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
     <row r="100" hidden="1" ht="13.5" customHeight="1" s="1339">
       <c r="I100" s="1099" t="inlineStr">
         <is>
-          <t>Druk</t>
+          <t xml:space="preserve">Pressure</t>
         </is>
       </c>
       <c r="J100" s="1521" t="n"/>
@@ -30736,7 +30736,7 @@
     <row r="101" hidden="1" ht="13.5" customHeight="1" s="1339">
       <c r="I101" s="1099" t="inlineStr">
         <is>
-          <t>Temp(00C)</t>
+          <t xml:space="preserve">Temp (°C)</t>
         </is>
       </c>
       <c r="J101" s="1521" t="n"/>
@@ -30745,7 +30745,7 @@
     <row r="102" hidden="1" ht="13.5" customHeight="1" s="1339">
       <c r="I102" s="1425" t="inlineStr">
         <is>
-          <t>CO2 Fles / Can 1 (200C)</t>
+          <t xml:space="preserve">CO2 Bottle / Can 1 (20°C)</t>
         </is>
       </c>
       <c r="J102" s="1521" t="inlineStr">
@@ -30754,14 +30754,14 @@
         </is>
       </c>
       <c r="K102" s="2093">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
     </row>
     <row r="103" hidden="1" ht="13.5" customHeight="1" s="1339">
       <c r="I103" s="1425" t="inlineStr">
         <is>
-          <t>CO2 Fust 1</t>
+          <t xml:space="preserve">CO2 Keg 1</t>
         </is>
       </c>
       <c r="J103" s="1521" t="inlineStr">
@@ -30770,14 +30770,14 @@
         </is>
       </c>
       <c r="K103" s="2093">
-        <f>'Recept-voorblad'!$M$15</f>
+        <f>'Recipe Sheet'!$M$15</f>
         <v/>
       </c>
     </row>
     <row r="104" hidden="1" ht="13.5" customHeight="1" s="1339">
       <c r="I104" s="1425" t="inlineStr">
         <is>
-          <t>Zuurstof Fust 1</t>
+          <t xml:space="preserve">O2 Keg 1</t>
         </is>
       </c>
       <c r="J104" s="1521" t="inlineStr">
@@ -30786,7 +30786,7 @@
         </is>
       </c>
       <c r="K104" s="2093">
-        <f>'Recept-voorblad'!$M$17</f>
+        <f>'Recipe Sheet'!$M$17</f>
         <v/>
       </c>
     </row>
@@ -31033,47 +31033,47 @@
   </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation sqref="E19 E24 E29 E34 E39 E41 E44 H16 H21 H23 H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Geen logo,Logo (zie voorblad)"</formula1>
+      <formula1>"No Logo,Logo (see Recipe Sheet)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C18 C23 C28 C33 C38 E17 E22 E27 E32 E37 H14 H19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Standaard,Afwijkend (zie opmerkingen)"</formula1>
+      <formula1>"Standard,Deviating (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C42 C45 E18 E23 E28 E33 E38 H15 H20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Geen EAN Code,EAN code toevoegen (zie specificaties)"</formula1>
+      <formula1>"No EAN Code,Add EAN Code (see specifications)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C16 C21 C26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"33cl Jopen LN,33cl LN,30cl BNR,75cl,Anders (zie opmerkingen)"</formula1>
+      <formula1>"33cl Jopen LN,33cl LN,30cl BNR,75cl,Other (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C17 C22 C27 C32 C37" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"NL,Cat 1,Cat 2,Cat 3,Blanco,Anders (zie opmerkingen)"</formula1>
+      <formula1>"NL,Cat 1,Cat 2,Cat 3,Blanco,Other (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C19 C24 C29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Jopen KK,Blauw KK,Zilver KK,Zwart KK"</formula1>
+      <formula1>"Jopen KK,Blue KK,Silver KK,Black KK"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="E16:G16 E21:G21 E26:G26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Blanco 12x33cl,Jopen 12x33cl,Blanco 24x33cl,Jopen 24x33cl,Jopen 6x75cl,Anders (zie opmerkingen)"</formula1>
+      <formula1>"Blanco 12x33cl,Jopen 12x33cl,Blanco 24x33cl,Jopen 24x33cl,Jopen 6x75cl,Other (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="E31:G31 E36:G36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Blanco 12x33cl,Jopen 12x33cl,Blanco 24x33cl,Jopen 24x33cl,Anders (zie opmerkingen)"</formula1>
+      <formula1>"Blanco 12x33cl,Jopen 12x33cl,Blanco 24x33cl,Jopen 24x33cl,Other (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C41 C44" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Fust 20 liter,Fust 30 liter,Fust 50 liter,Keykeg 20 liter,Keykeg 30 liter,Polykeg 20L A,Polykeg 20L S,Anders (zie opmerkingen)"</formula1>
+      <formula1>"20L KU Keg,30L Jopen Keg,50L Jopen Keg,20L Gebr. Door Vrouwen Keg,20L Other Keg,20L KeyKeg,30L KeyKeg,Other (see comments)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C31 C36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"labelled,silver bullet"</formula1>
+      <formula1>"Labelled,Silver Bullet"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="C34 C39" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Zilver,Zwart"</formula1>
+      <formula1>"Silver,Black"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="U23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -31118,7 +31118,7 @@
       <c r="A1" s="1425" t="n"/>
       <c r="B1" s="1826" t="inlineStr">
         <is>
-          <t>Afvulverslag</t>
+          <t xml:space="preserve">Filling Report</t>
         </is>
       </c>
       <c r="C1" s="1106" t="n"/>
@@ -31130,7 +31130,7 @@
       <c r="I1" s="1106" t="n"/>
       <c r="M1" s="2099" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="N1" s="2100" t="n"/>
@@ -31158,39 +31158,39 @@
       <c r="A3" s="1425" t="n"/>
       <c r="B3" s="2013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naam Bier </t>
+          <t xml:space="preserve">Beer Name</t>
         </is>
       </c>
       <c r="C3" s="2105">
-        <f>Afvullen!C3</f>
+        <f>Filling!C3</f>
         <v/>
       </c>
       <c r="D3" s="1075" t="n"/>
       <c r="E3" s="1076" t="n"/>
       <c r="F3" s="2026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch </t>
+          <t xml:space="preserve">Batch No.</t>
         </is>
       </c>
       <c r="G3" s="1076" t="n"/>
       <c r="H3" s="2105">
-        <f>'Recept-voorblad'!K3</f>
+        <f>'Recipe Sheet'!K3</f>
         <v/>
       </c>
       <c r="I3" s="1076" t="n"/>
       <c r="M3" s="2106" t="inlineStr">
         <is>
-          <t>Totaal HL's van Verwer- king (Liters)</t>
+          <t xml:space="preserve">Total From Processing (Litres)</t>
         </is>
       </c>
       <c r="O3" s="2010" t="inlineStr">
         <is>
-          <t>Totaal Afgevuld</t>
+          <t xml:space="preserve">Total Filled</t>
         </is>
       </c>
       <c r="Q3" s="2107" t="inlineStr">
         <is>
-          <t>Nog te doen / restant / verlies</t>
+          <t xml:space="preserve">To Do / Remaining / Loss</t>
         </is>
       </c>
       <c r="R3" s="2108" t="n"/>
@@ -31214,7 +31214,7 @@
       <c r="A5" s="1425" t="n"/>
       <c r="B5" s="2111" t="inlineStr">
         <is>
-          <t>Opmerkingen bij afvullen</t>
+          <t xml:space="preserve">Filling Comments</t>
         </is>
       </c>
       <c r="C5" s="2112" t="n"/>
@@ -31227,12 +31227,12 @@
       <c r="M5" s="2114" t="n"/>
       <c r="O5" s="2115" t="inlineStr">
         <is>
-          <t>(liters)</t>
+          <t xml:space="preserve">(litres)</t>
         </is>
       </c>
       <c r="Q5" s="2116" t="inlineStr">
         <is>
-          <t>(liters)</t>
+          <t xml:space="preserve">(litres)</t>
         </is>
       </c>
       <c r="R5" s="2117" t="inlineStr">
@@ -31247,39 +31247,39 @@
       <c r="C6" s="1076" t="n"/>
       <c r="D6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="E6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="F6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="G6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="H6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="I6" s="2023" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="J6" s="1521" t="n"/>
       <c r="K6" s="1521" t="n"/>
       <c r="L6" s="1521" t="n"/>
       <c r="M6" s="2119">
-        <f>Verwerking!D63*100</f>
+        <f>Processing!D63*100</f>
         <v/>
       </c>
       <c r="N6" s="1531" t="n"/>
@@ -31323,32 +31323,32 @@
       <c r="C8" s="1083" t="n"/>
       <c r="D8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="E8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="F8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="G8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="H8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="I8" s="2128" t="inlineStr">
         <is>
-          <t>HBT nr</t>
+          <t xml:space="preserve">HBT No.</t>
         </is>
       </c>
       <c r="J8" s="1521" t="n"/>
@@ -31356,7 +31356,7 @@
       <c r="L8" s="1521" t="n"/>
       <c r="M8" s="2129" t="inlineStr">
         <is>
-          <t>Totaal Liters Fles</t>
+          <t xml:space="preserve">Total Litres Bottle</t>
         </is>
       </c>
       <c r="N8" s="1114" t="n"/>
@@ -31364,7 +31364,7 @@
       <c r="P8" s="1521" t="n"/>
       <c r="Q8" s="2130" t="inlineStr">
         <is>
-          <t>Totaal Liters Blik</t>
+          <t xml:space="preserve">Total Litres Can</t>
         </is>
       </c>
       <c r="R8" s="1114" t="n"/>
@@ -31401,32 +31401,32 @@
       <c r="C10" s="1083" t="n"/>
       <c r="D10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="E10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="F10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="G10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="H10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="I10" s="2134" t="inlineStr">
         <is>
-          <t>Volume (HL)</t>
+          <t xml:space="preserve">Volume (hl)</t>
         </is>
       </c>
       <c r="J10" s="1521" t="n"/>
@@ -31434,7 +31434,7 @@
       <c r="L10" s="1521" t="n"/>
       <c r="M10" s="2129" t="inlineStr">
         <is>
-          <t>Totaal Liters Fust</t>
+          <t xml:space="preserve">Total Litres Keg</t>
         </is>
       </c>
       <c r="N10" s="1114" t="n"/>
@@ -31479,7 +31479,7 @@
       <c r="L12" s="1521" t="n"/>
       <c r="M12" s="2129" t="inlineStr">
         <is>
-          <t>Totaal samengevoegd</t>
+          <t xml:space="preserve">Total Blended</t>
         </is>
       </c>
       <c r="N12" s="1114" t="n"/>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="B13" s="2136" t="inlineStr">
         <is>
-          <t>Ingevuld door</t>
+          <t xml:space="preserve">Filled In By</t>
         </is>
       </c>
       <c r="C13" s="2026" t="inlineStr">
         <is>
-          <t>Naam</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="D13" s="2137" t="n"/>
@@ -31544,7 +31544,7 @@
       <c r="J15" s="1521" t="n"/>
       <c r="K15" s="2145" t="inlineStr">
         <is>
-          <t>OPBOEKEN (+)</t>
+          <t xml:space="preserve">BOOK IN (+)</t>
         </is>
       </c>
       <c r="L15" s="1114" t="n"/>
@@ -31557,7 +31557,7 @@
     <row r="16" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B16" s="2146" t="inlineStr">
         <is>
-          <t>AFVUL FLESSEN</t>
+          <t xml:space="preserve">FILLED BOTTLES</t>
         </is>
       </c>
       <c r="C16" s="2147" t="inlineStr">
@@ -31567,44 +31567,44 @@
       </c>
       <c r="D16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I16" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J16" s="2112" t="n"/>
       <c r="K16" s="2148" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L16" s="1521" t="n"/>
       <c r="M16" s="2148" t="inlineStr">
         <is>
-          <t>LITERS</t>
+          <t xml:space="preserve">LITRES</t>
         </is>
       </c>
       <c r="N16" s="1521" t="n"/>
@@ -31615,11 +31615,11 @@
     <row r="17" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B17" s="2013" t="inlineStr">
         <is>
-          <t>Doos 24x33cl</t>
+          <t xml:space="preserve">Box 24x33cl</t>
         </is>
       </c>
       <c r="C17" s="2149">
-        <f>Afvullen!C6</f>
+        <f>Filling!C6</f>
         <v/>
       </c>
       <c r="D17" s="2150" t="n"/>
@@ -31642,7 +31642,7 @@
     <row r="18" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B18" s="2013" t="inlineStr">
         <is>
-          <t>Doos 24x33cl - BLANCO</t>
+          <t xml:space="preserve">Box 24x33cl - BLANCO</t>
         </is>
       </c>
       <c r="C18" s="2149">
@@ -31683,11 +31683,11 @@
     <row r="20" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B20" s="2013" t="inlineStr">
         <is>
-          <t>Doos 12x33cl</t>
+          <t xml:space="preserve">Box 12x33cl</t>
         </is>
       </c>
       <c r="C20" s="2149">
-        <f>Afvullen!C7</f>
+        <f>Filling!C7</f>
         <v/>
       </c>
       <c r="D20" s="2150" t="n"/>
@@ -31710,7 +31710,7 @@
     <row r="21" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B21" s="2013" t="inlineStr">
         <is>
-          <t>Doos 12x33cl - BLANCO</t>
+          <t xml:space="preserve">Box 12x33cl - BLANCO</t>
         </is>
       </c>
       <c r="C21" s="2149">
@@ -31751,7 +31751,7 @@
     <row r="23" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B23" s="2013" t="inlineStr">
         <is>
-          <t>Doos 6x75cl</t>
+          <t xml:space="preserve">Box 6x75cl</t>
         </is>
       </c>
       <c r="C23" s="2149" t="n"/>
@@ -31775,7 +31775,7 @@
     <row r="24" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B24" s="2013" t="inlineStr">
         <is>
-          <t>Doos 6x75cl - BLANCO</t>
+          <t xml:space="preserve">Box 6x75cl - BLANCO</t>
         </is>
       </c>
       <c r="C24" s="2149">
@@ -31802,7 +31802,7 @@
     <row r="25" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B25" s="2013" t="inlineStr">
         <is>
-          <t>Krat 12x75cl - BLANCO</t>
+          <t xml:space="preserve">Crate 12x75cl - BLANCO</t>
         </is>
       </c>
       <c r="C25" s="2158" t="n"/>
@@ -31834,7 +31834,7 @@
       <c r="I26" s="2157" t="n"/>
       <c r="J26" s="1521" t="n"/>
       <c r="K26" s="2152">
-        <f>'Recept-voorblad'!$M$13</f>
+        <f>'Recipe Sheet'!$M$13</f>
         <v/>
       </c>
       <c r="L26" s="2112" t="n"/>
@@ -31843,65 +31843,65 @@
     <row r="27" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B27" s="2146" t="inlineStr">
         <is>
-          <t>AFVUL BLIKKEN</t>
+          <t xml:space="preserve">FILLED CANS</t>
         </is>
       </c>
       <c r="C27" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I27" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J27" s="1521" t="n"/>
       <c r="K27" s="2010" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L27" s="1521" t="n"/>
       <c r="M27" s="2010" t="inlineStr">
         <is>
-          <t>LITERS</t>
+          <t xml:space="preserve">LITRES</t>
         </is>
       </c>
     </row>
     <row r="28" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B28" s="2159" t="inlineStr">
         <is>
-          <t>Doos 12x33cl Blik</t>
+          <t xml:space="preserve">Box 12x33cl Can</t>
         </is>
       </c>
       <c r="C28" s="2149">
-        <f>Afvullen!C9</f>
+        <f>Filling!C9</f>
         <v/>
       </c>
       <c r="D28" s="2150" t="n"/>
@@ -31924,11 +31924,11 @@
     <row r="29" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B29" s="2159" t="inlineStr">
         <is>
-          <t>Doos 24x33cl Blik</t>
+          <t xml:space="preserve">Box 24x33cl Can</t>
         </is>
       </c>
       <c r="C29" s="2149">
-        <f>Afvullen!C8</f>
+        <f>Filling!C8</f>
         <v/>
       </c>
       <c r="D29" s="2150" t="n"/>
@@ -31951,11 +31951,11 @@
     <row r="30" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B30" s="2159" t="inlineStr">
         <is>
-          <t>Doos 12x44cl Blik</t>
+          <t xml:space="preserve">Box 12x44cl Can</t>
         </is>
       </c>
       <c r="C30" s="2149">
-        <f>Afvullen!C9</f>
+        <f>Filling!C9</f>
         <v/>
       </c>
       <c r="D30" s="2150" t="n"/>
@@ -31978,11 +31978,11 @@
     <row r="31" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B31" s="2159" t="inlineStr">
         <is>
-          <t>Doos 24x44cl Blik</t>
+          <t xml:space="preserve">Box 24x44cl Can</t>
         </is>
       </c>
       <c r="C31" s="2149">
-        <f>Afvullen!C10</f>
+        <f>Filling!C10</f>
         <v/>
       </c>
       <c r="D31" s="2150" t="n"/>
@@ -32006,61 +32006,61 @@
     <row r="33" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B33" s="2146" t="inlineStr">
         <is>
-          <t>AFVUL FUSTEN &amp; KEYKEGS</t>
+          <t xml:space="preserve">FILLED KEGS &amp; KEYKEGS</t>
         </is>
       </c>
       <c r="C33" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I33" s="2010" t="inlineStr">
         <is>
-          <t>Aantallen</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J33" s="1521" t="n"/>
       <c r="K33" s="2010" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L33" s="1521" t="n"/>
       <c r="M33" s="2010" t="inlineStr">
         <is>
-          <t>LITERS</t>
+          <t xml:space="preserve">LITRES</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B34" s="2013" t="inlineStr">
         <is>
-          <t>20L KU Fust</t>
+          <t xml:space="preserve">20L KU Keg</t>
         </is>
       </c>
       <c r="C34" s="2149" t="n"/>
@@ -32084,7 +32084,7 @@
     <row r="35" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B35" s="2013" t="inlineStr">
         <is>
-          <t>30L Jopen Fust</t>
+          <t xml:space="preserve">30L Jopen Keg</t>
         </is>
       </c>
       <c r="C35" s="2149" t="n"/>
@@ -32108,7 +32108,7 @@
     <row r="36" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B36" s="2013" t="inlineStr">
         <is>
-          <t>50L Jopen Fust</t>
+          <t xml:space="preserve">50L Jopen Keg</t>
         </is>
       </c>
       <c r="C36" s="2149" t="n"/>
@@ -32146,7 +32146,7 @@
     <row r="38" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B38" s="2013" t="inlineStr">
         <is>
-          <t>20L Gebr. Door Vrouwen Fust</t>
+          <t xml:space="preserve">20L Gebr. Door Vrouwen Keg</t>
         </is>
       </c>
       <c r="C38" s="1521" t="n"/>
@@ -32170,7 +32170,7 @@
     <row r="39" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B39" s="2013" t="inlineStr">
         <is>
-          <t>20L Other Fust</t>
+          <t xml:space="preserve">20L Other Keg</t>
         </is>
       </c>
       <c r="C39" s="1521" t="n"/>
@@ -32256,48 +32256,48 @@
     <row r="43" outlineLevel="1" ht="55.5" customFormat="1" customHeight="1" s="1425">
       <c r="B43" s="2172" t="inlineStr">
         <is>
-          <t>GEBRUIKT TBV SAMENVOEGEN / BARREL AGING</t>
+          <t xml:space="preserve">USED FOR BLENDING / BARREL AGING</t>
         </is>
       </c>
       <c r="C43" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="E43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="F43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="G43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="H43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="I43" s="2010" t="inlineStr">
         <is>
-          <t>Liters</t>
+          <t xml:space="preserve">Litres</t>
         </is>
       </c>
       <c r="J43" s="1521" t="n"/>
       <c r="K43" s="2010" t="inlineStr">
         <is>
-          <t>TOTALEN Liters</t>
+          <t xml:space="preserve">TOTAL Litres</t>
         </is>
       </c>
       <c r="L43" s="1114" t="n"/>
@@ -32306,7 +32306,7 @@
     <row r="44" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B44" s="2013" t="inlineStr">
         <is>
-          <t>TBV BATCH …,</t>
+          <t xml:space="preserve">FOR BATCH …</t>
         </is>
       </c>
       <c r="C44" s="2150" t="n"/>
@@ -32330,7 +32330,7 @@
     <row r="45" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B45" s="2013" t="inlineStr">
         <is>
-          <t>TBV BARREL AGING BATCH…</t>
+          <t xml:space="preserve">FOR BARREL AGING BATCH …</t>
         </is>
       </c>
       <c r="C45" s="2150" t="n"/>
@@ -32372,7 +32372,7 @@
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="1425">
       <c r="B48" s="2173" t="inlineStr">
         <is>
-          <t>VERBRUIKEN :</t>
+          <t xml:space="preserve">CONSUMPTION:</t>
         </is>
       </c>
       <c r="C48" s="1114" t="n"/>
@@ -32385,7 +32385,7 @@
       <c r="J48" s="1521" t="n"/>
       <c r="K48" s="2145" t="inlineStr">
         <is>
-          <t>UITSCHRIJVEN (-)</t>
+          <t xml:space="preserve">BOOK OUT (-)</t>
         </is>
       </c>
       <c r="L48" s="1114" t="n"/>
@@ -32398,54 +32398,54 @@
     <row r="49" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B49" s="2174" t="inlineStr">
         <is>
-          <t>VERBRUIKEN FLES</t>
+          <t xml:space="preserve">CONSUMPTION BOTTLE</t>
         </is>
       </c>
       <c r="C49" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I49" s="1137" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J49" s="1521" t="n"/>
       <c r="K49" s="2175" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L49" s="2036" t="n"/>
       <c r="M49" s="2148" t="inlineStr">
         <is>
-          <t>VERLIES</t>
+          <t xml:space="preserve">LOSS</t>
         </is>
       </c>
       <c r="N49" s="1521" t="n"/>
@@ -32456,7 +32456,7 @@
     <row r="50" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B50" s="2016" t="inlineStr">
         <is>
-          <t>Fles 33cl</t>
+          <t xml:space="preserve">Bottle 33cl</t>
         </is>
       </c>
       <c r="C50" s="2176" t="n"/>
@@ -32502,7 +32502,7 @@
     <row r="52" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B52" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 33cl - Main</t>
+          <t xml:space="preserve">Label 33cl - Main</t>
         </is>
       </c>
       <c r="C52" s="2179" t="n"/>
@@ -32530,7 +32530,7 @@
     <row r="53" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B53" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 33cl - Neck</t>
+          <t xml:space="preserve">Label 33cl - Neck</t>
         </is>
       </c>
       <c r="C53" s="2161" t="n"/>
@@ -32576,7 +32576,7 @@
     <row r="55" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B55" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 24x33cl - Bedrukt:</t>
+          <t xml:space="preserve">Outer Box 24x33cl - Printed</t>
         </is>
       </c>
       <c r="C55" s="2179" t="n"/>
@@ -32604,7 +32604,7 @@
     <row r="56" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B56" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 24x33cl - Blanco</t>
+          <t xml:space="preserve">Outer Box 24x33cl - Blank</t>
         </is>
       </c>
       <c r="C56" s="2180" t="n"/>
@@ -32650,7 +32650,7 @@
     <row r="58" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B58" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 12x33cl - Bedrukt:</t>
+          <t xml:space="preserve">Outer Box 12x33cl - Printed</t>
         </is>
       </c>
       <c r="C58" s="2179" t="n"/>
@@ -32678,7 +32678,7 @@
     <row r="59" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B59" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 12x33cl - Blanco</t>
+          <t xml:space="preserve">Outer Box 12x33cl - Blank</t>
         </is>
       </c>
       <c r="C59" s="2180" t="n"/>
@@ -32724,7 +32724,7 @@
     <row r="61" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B61" s="2016" t="inlineStr">
         <is>
-          <t>Kroonkurk:</t>
+          <t xml:space="preserve">Crown Cap:</t>
         </is>
       </c>
       <c r="C61" s="2181" t="n"/>
@@ -32747,7 +32747,7 @@
       <c r="N61" s="1521" t="n"/>
       <c r="O61" s="1521" t="inlineStr">
         <is>
-          <t>Doos á</t>
+          <t xml:space="preserve">Box of</t>
         </is>
       </c>
       <c r="P61" s="1521" t="n"/>
@@ -32775,14 +32775,14 @@
       <c r="N62" s="1521" t="n"/>
       <c r="O62" s="2182" t="inlineStr">
         <is>
-          <t>Inhoud doos kan variëren!</t>
+          <t xml:space="preserve">Box contents may vary!</t>
         </is>
       </c>
     </row>
     <row r="63" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B63" s="2016" t="inlineStr">
         <is>
-          <t>Fles 75cl</t>
+          <t xml:space="preserve">Bottle 75cl</t>
         </is>
       </c>
       <c r="C63" s="2179" t="n"/>
@@ -32810,7 +32810,7 @@
     <row r="64" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B64" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 75cl - Main</t>
+          <t xml:space="preserve">Label 75cl - Main</t>
         </is>
       </c>
       <c r="C64" s="2183" t="n"/>
@@ -32838,7 +32838,7 @@
     <row r="65" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B65" s="2016" t="inlineStr">
         <is>
-          <t>Stickerlabel 75cl - Neck</t>
+          <t xml:space="preserve">Label 75cl - Neck</t>
         </is>
       </c>
       <c r="C65" s="2183" t="n"/>
@@ -32884,7 +32884,7 @@
     <row r="67" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B67" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 6x75cl - Bedrukt:</t>
+          <t xml:space="preserve">Outer Box 6x75cl - Printed</t>
         </is>
       </c>
       <c r="C67" s="2179" t="n"/>
@@ -32912,7 +32912,7 @@
     <row r="68" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B68" s="2016" t="inlineStr">
         <is>
-          <t>Omdozen 6x75cl - Blanco</t>
+          <t xml:space="preserve">Outer Box 6x75cl - Blank</t>
         </is>
       </c>
       <c r="C68" s="2188" t="n"/>
@@ -32958,7 +32958,7 @@
     <row r="70" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B70" s="2016" t="inlineStr">
         <is>
-          <t>Kurk:</t>
+          <t xml:space="preserve">Cork:</t>
         </is>
       </c>
       <c r="C70" s="2179" t="n"/>
@@ -32981,7 +32981,7 @@
       <c r="N70" s="1521" t="n"/>
       <c r="O70" s="1521" t="inlineStr">
         <is>
-          <t>Doos á</t>
+          <t xml:space="preserve">Box of</t>
         </is>
       </c>
       <c r="P70" s="1521" t="n"/>
@@ -32996,7 +32996,7 @@
     <row r="71" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B71" s="2016" t="inlineStr">
         <is>
-          <t>Musseletten:</t>
+          <t xml:space="preserve">Muselets:</t>
         </is>
       </c>
       <c r="C71" s="2188" t="n"/>
@@ -33019,7 +33019,7 @@
       <c r="N71" s="1521" t="n"/>
       <c r="O71" s="1521" t="inlineStr">
         <is>
-          <t>Doos á</t>
+          <t xml:space="preserve">Box of</t>
         </is>
       </c>
       <c r="P71" s="1521" t="n"/>
@@ -33053,54 +33053,54 @@
     <row r="73" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B73" s="2172" t="inlineStr">
         <is>
-          <t>VERBRUIKEN BLIK-artikelen</t>
+          <t xml:space="preserve">CONSUMPTION CAN ITEMS</t>
         </is>
       </c>
       <c r="C73" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I73" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J73" s="2112" t="n"/>
       <c r="K73" s="2010" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L73" s="2191" t="n"/>
       <c r="M73" s="2010" t="inlineStr">
         <is>
-          <t>VERLIES</t>
+          <t xml:space="preserve">LOSS</t>
         </is>
       </c>
       <c r="N73" s="1521" t="n"/>
@@ -33112,7 +33112,7 @@
     <row r="74" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B74" s="2192" t="inlineStr">
         <is>
-          <t>Blik 33cl</t>
+          <t xml:space="preserve">Can 33cl</t>
         </is>
       </c>
       <c r="C74" s="2176" t="n"/>
@@ -33141,7 +33141,7 @@
     <row r="75" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B75" s="2192" t="inlineStr">
         <is>
-          <t>Blik 44cl</t>
+          <t xml:space="preserve">Can 44cl</t>
         </is>
       </c>
       <c r="C75" s="2195" t="n"/>
@@ -33167,7 +33167,7 @@
     <row r="76" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B76" s="2192" t="inlineStr">
         <is>
-          <t>Blik Deksel</t>
+          <t xml:space="preserve">Can End</t>
         </is>
       </c>
       <c r="C76" s="1615" t="n"/>
@@ -33196,7 +33196,7 @@
     <row r="77" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B77" s="2192" t="inlineStr">
         <is>
-          <t>Stickerlabel 33cl blik</t>
+          <t xml:space="preserve">Label 33cl Can</t>
         </is>
       </c>
       <c r="C77" s="1615" t="n"/>
@@ -33225,7 +33225,7 @@
     <row r="78" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B78" s="2192" t="inlineStr">
         <is>
-          <t>Stickerlabel 44cl blik</t>
+          <t xml:space="preserve">Label 44cl Can</t>
         </is>
       </c>
       <c r="C78" s="1615" t="n"/>
@@ -33251,7 +33251,7 @@
     <row r="79" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B79" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 12x33cl blik - Blanco</t>
+          <t xml:space="preserve">Outer Box 12x33cl Can - Blank</t>
         </is>
       </c>
       <c r="C79" s="1615" t="n"/>
@@ -33280,7 +33280,7 @@
     <row r="80" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B80" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 24x33cl blik - Blanco</t>
+          <t xml:space="preserve">Outer Box 24x33cl Can - Blank</t>
         </is>
       </c>
       <c r="C80" s="1615" t="n"/>
@@ -33301,7 +33301,7 @@
     <row r="81" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B81" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 12x44cl blik - Blanco</t>
+          <t xml:space="preserve">Outer Box 12x44cl Can - Blank</t>
         </is>
       </c>
       <c r="C81" s="1615" t="n"/>
@@ -33322,7 +33322,7 @@
     <row r="82" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B82" s="2192" t="inlineStr">
         <is>
-          <t>Omdozen 24x44cl blik - Blanco</t>
+          <t xml:space="preserve">Outer Box 24x44cl Can - Blank</t>
         </is>
       </c>
       <c r="C82" s="1615" t="n"/>
@@ -33357,61 +33357,61 @@
     <row r="84" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B84" s="2172" t="inlineStr">
         <is>
-          <t>VERBRUIKEN FUST-artikelen</t>
+          <t xml:space="preserve">CONSUMPTION KEG ITEMS</t>
         </is>
       </c>
       <c r="C84" s="2147" t="inlineStr">
         <is>
-          <t>Opmerkingen</t>
+          <t xml:space="preserve">Comments</t>
         </is>
       </c>
       <c r="D84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="E84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="F84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="G84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="H84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="I84" s="2010" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t xml:space="preserve">Quantity</t>
         </is>
       </c>
       <c r="J84" s="2112" t="n"/>
       <c r="K84" s="2010" t="inlineStr">
         <is>
-          <t>TOTALEN</t>
+          <t xml:space="preserve">TOTALS</t>
         </is>
       </c>
       <c r="L84" s="2191" t="n"/>
       <c r="M84" s="2010" t="inlineStr">
         <is>
-          <t>VERLIES</t>
+          <t xml:space="preserve">LOSS</t>
         </is>
       </c>
     </row>
     <row r="85" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B85" s="2016" t="inlineStr">
         <is>
-          <t>20L KU Fust</t>
+          <t xml:space="preserve">20L KU Keg</t>
         </is>
       </c>
       <c r="C85" s="1615" t="n"/>
@@ -33435,7 +33435,7 @@
     <row r="86" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B86" s="2016" t="inlineStr">
         <is>
-          <t>30L Jopen Fust</t>
+          <t xml:space="preserve">30L Jopen Keg</t>
         </is>
       </c>
       <c r="C86" s="1615" t="n"/>
@@ -33459,7 +33459,7 @@
     <row r="87" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B87" s="2016" t="inlineStr">
         <is>
-          <t>50L Jopen Fust</t>
+          <t xml:space="preserve">50L Jopen Keg</t>
         </is>
       </c>
       <c r="C87" s="1615" t="n"/>
@@ -33497,7 +33497,7 @@
     <row r="89" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B89" s="2016" t="inlineStr">
         <is>
-          <t>20L Gebr. Door Vrouwen Fust</t>
+          <t xml:space="preserve">20L Gebr. Door Vrouwen Keg</t>
         </is>
       </c>
       <c r="C89" s="1615" t="n"/>
@@ -33521,7 +33521,7 @@
     <row r="90" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B90" s="2016" t="inlineStr">
         <is>
-          <t>20L Other Fust</t>
+          <t xml:space="preserve">20L Other Keg</t>
         </is>
       </c>
       <c r="C90" s="1615" t="n"/>
@@ -33607,7 +33607,7 @@
     <row r="94" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B94" s="2016" t="inlineStr">
         <is>
-          <t>Fustdop:</t>
+          <t xml:space="preserve">Keg Cap:</t>
         </is>
       </c>
       <c r="C94" s="1615" t="n"/>
@@ -33631,7 +33631,7 @@
     <row r="95" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B95" s="2016" t="inlineStr">
         <is>
-          <t>KeyKegFustdop:</t>
+          <t xml:space="preserve">KeyKeg Cap:</t>
         </is>
       </c>
       <c r="C95" s="2204" t="n"/>
@@ -33657,12 +33657,12 @@
     <row r="98" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B98" s="2013" t="inlineStr">
         <is>
-          <t>Ingevoerd in Mdrank</t>
+          <t xml:space="preserve">Entered In Mdrank</t>
         </is>
       </c>
       <c r="C98" s="2026" t="inlineStr">
         <is>
-          <t>door:</t>
+          <t xml:space="preserve">by:</t>
         </is>
       </c>
       <c r="D98" s="2205" t="n"/>
@@ -33672,7 +33672,7 @@
       <c r="B99" s="2206" t="n"/>
       <c r="C99" s="2026" t="inlineStr">
         <is>
-          <t>datum:</t>
+          <t xml:space="preserve">date:</t>
         </is>
       </c>
       <c r="D99" s="2215" t="n"/>

--- a/batchrapport-generator/Batchrapport_sjabloon.xlsx
+++ b/batchrapport-generator/Batchrapport_sjabloon.xlsx
@@ -32604,7 +32604,7 @@
     <row r="56" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B56" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 24x33cl - Blank</t>
+          <t xml:space="preserve">Outer Box 24x33cl - Blanco</t>
         </is>
       </c>
       <c r="C56" s="2180" t="n"/>
@@ -32678,7 +32678,7 @@
     <row r="59" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B59" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 12x33cl - Blank</t>
+          <t xml:space="preserve">Outer Box 12x33cl - Blanco</t>
         </is>
       </c>
       <c r="C59" s="2180" t="n"/>
@@ -32912,7 +32912,7 @@
     <row r="68" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B68" s="2016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 6x75cl - Blank</t>
+          <t xml:space="preserve">Outer Box 6x75cl - Blanco</t>
         </is>
       </c>
       <c r="C68" s="2188" t="n"/>
@@ -33251,7 +33251,7 @@
     <row r="79" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B79" s="2192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 12x33cl Can - Blank</t>
+          <t xml:space="preserve">Outer Box 12x33cl Can - Blanco</t>
         </is>
       </c>
       <c r="C79" s="1615" t="n"/>
@@ -33280,7 +33280,7 @@
     <row r="80" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B80" s="2192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 24x33cl Can - Blank</t>
+          <t xml:space="preserve">Outer Box 24x33cl Can - Blanco</t>
         </is>
       </c>
       <c r="C80" s="1615" t="n"/>
@@ -33301,7 +33301,7 @@
     <row r="81" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B81" s="2192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 12x44cl Can - Blank</t>
+          <t xml:space="preserve">Outer Box 12x44cl Can - Blanco</t>
         </is>
       </c>
       <c r="C81" s="1615" t="n"/>
@@ -33322,7 +33322,7 @@
     <row r="82" outlineLevel="1" ht="15" customFormat="1" customHeight="1" s="1425">
       <c r="B82" s="2192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outer Box 24x44cl Can - Blank</t>
+          <t xml:space="preserve">Outer Box 24x44cl Can - Blanco</t>
         </is>
       </c>
       <c r="C82" s="1615" t="n"/>
